--- a/revision tracker/Revision_Tracker.xlsx
+++ b/revision tracker/Revision_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/948b5d172b360b34/Python Stuff/revision tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="211" documentId="8_{18D838B1-020D-4004-8F3D-127CEC12EAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{061CFA63-D077-4CA6-836D-9C1035D22F3C}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{5178CA06-C00C-4B3B-A12B-47A30CE74603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AE76C4B-9B81-46E7-83F7-5FB84B8F39B0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revision Timetable" sheetId="13" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="125">
   <si>
     <t xml:space="preserve">  GCSE Revision Tracker — Dashboard</t>
   </si>
@@ -122,199 +122,274 @@
     <t>Green</t>
   </si>
   <si>
+    <t>🧭  How to choose what to revise</t>
+  </si>
+  <si>
+    <t>•  Slots 1–3 of the day: your timetable tells you the subject. Open that subject tab and pick the topic.</t>
+  </si>
+  <si>
+    <t>•  Slot 4 (maintenance): use this Dashboard. Pick 3 subjects with Red/Amber/overdue topics, 15 min each.</t>
+  </si>
+  <si>
+    <t>•  Anything overdue? Do those first.  Then Red.  Then Amber.  Then oldest Last Revised.</t>
+  </si>
+  <si>
+    <t>•  A subject with lots of Red or Overdue = focus there. A subject with lots of Green = leave it longer.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Biology</t>
   </si>
   <si>
+    <t>&lt; Return to Dashboard</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Confidence</t>
+  </si>
+  <si>
+    <t>Last Revised</t>
+  </si>
+  <si>
+    <t>Next Action</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group 2:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Movements of molecules
+Biological molecules
+Movement fo substances</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Transport in plants
+Nutrition in plants
+Gas exchange in plants
+Reproduction in plants</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group 4:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Respiration
+Gas exchange in humans</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+Excretion
+Human Reproduction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group 6:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Co-ordination and response
+Transport in Humans
+Nutrition in humans</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Group 8: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Organisms in the environment
+Human Influences
+Feeding relationships
+Cycles within ecosystems</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">  Chemistry</t>
   </si>
   <si>
+    <t>Principals of Chemistry  1a - 1e</t>
+  </si>
+  <si>
+    <t>Bonding  1f - 1h</t>
+  </si>
+  <si>
+    <t>Inorganic Chem part 1 - 1a - 1d</t>
+  </si>
+  <si>
+    <t>Inorganic Chem part 2 - 1e - 1g</t>
+  </si>
+  <si>
+    <t>Energetics</t>
+  </si>
+  <si>
+    <t>Rates of Reaction</t>
+  </si>
+  <si>
+    <t>Reversible reaction and equilbria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y10 Organics </t>
+  </si>
+  <si>
+    <t>y11 Organics</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Physics</t>
   </si>
   <si>
+    <t>9.1 Measuring waves + 10.1 Properties of waves &amp; EM Spectrum</t>
+  </si>
+  <si>
+    <t>9.2 Electrostatics and electrical current</t>
+  </si>
+  <si>
+    <t>9.3 Mains electricity + 10.4 Electrical circuits</t>
+  </si>
+  <si>
+    <t>9.4 Astronomy</t>
+  </si>
+  <si>
+    <t>9.5 Measuring motion + 10.3 Unbalanced forces and acceleration</t>
+  </si>
+  <si>
+    <t>9.6 Magnetism and electromagnets + 10.6 Electromagnetism</t>
+  </si>
+  <si>
+    <t>9.7 Energy types and energy resources + 10.2 Energy transfer, work and power</t>
+  </si>
+  <si>
+    <t>9.8 Density and pressure + 10.5 Pressure in Liquids and Ideal Gases</t>
+  </si>
+  <si>
+    <t>10.7 Thermal energy and Change of State</t>
+  </si>
+  <si>
+    <t>11.1 Radioactivity</t>
+  </si>
+  <si>
+    <t>11.2 Forces, Momentum &amp; Moments</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Mathematics</t>
   </si>
   <si>
+    <t>Do Lots of Past Papers</t>
+  </si>
+  <si>
+    <t>Do the reasoning and problem solving question papers on firefly</t>
+  </si>
+  <si>
     <t xml:space="preserve">  English Language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  English Literature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Geography</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  History</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Spanish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Computer Science</t>
-  </si>
-  <si>
-    <t>🧭  How to choose what to revise</t>
-  </si>
-  <si>
-    <t>•  Slots 1–3 of the day: your timetable tells you the subject. Open that subject tab and pick the topic.</t>
-  </si>
-  <si>
-    <t>•  Slot 4 (maintenance): use this Dashboard. Pick 3 subjects with Red/Amber/overdue topics, 15 min each.</t>
-  </si>
-  <si>
-    <t>•  Anything overdue? Do those first.  Then Red.  Then Amber.  Then oldest Last Revised.</t>
-  </si>
-  <si>
-    <t>•  A subject with lots of Red or Overdue = focus there. A subject with lots of Green = leave it longer.</t>
-  </si>
-  <si>
-    <t>Topic</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Confidence</t>
-  </si>
-  <si>
-    <t>Last Revised</t>
-  </si>
-  <si>
-    <t>Next Action</t>
-  </si>
-  <si>
-    <t>Movements of molecules</t>
-  </si>
-  <si>
-    <t>Excretion</t>
-  </si>
-  <si>
-    <t>Human Reproduction</t>
-  </si>
-  <si>
-    <t>Organisms in the environment</t>
-  </si>
-  <si>
-    <t>Co-ordination and response</t>
-  </si>
-  <si>
-    <t>Transport in Humans</t>
-  </si>
-  <si>
-    <t>Transport in plants</t>
-  </si>
-  <si>
-    <t>Inheritance</t>
-  </si>
-  <si>
-    <t>Human Influences</t>
-  </si>
-  <si>
-    <t>Characteristics of living organisms</t>
-  </si>
-  <si>
-    <t>Variety of living organisms</t>
-  </si>
-  <si>
-    <t>Levels of organisation</t>
-  </si>
-  <si>
-    <t>Cell structure</t>
-  </si>
-  <si>
-    <t>Biological Molecules</t>
-  </si>
-  <si>
-    <t>Movement of substances</t>
-  </si>
-  <si>
-    <t>Nutrition in humans</t>
-  </si>
-  <si>
-    <t>Nutrition in plants</t>
-  </si>
-  <si>
-    <t>Respiration</t>
-  </si>
-  <si>
-    <t>Gas exchange in humans</t>
-  </si>
-  <si>
-    <t>Gas exchange in plants</t>
-  </si>
-  <si>
-    <t>Reproduction in plants</t>
-  </si>
-  <si>
-    <t>Feeding relationships</t>
-  </si>
-  <si>
-    <t>Cycles within ecosystems</t>
-  </si>
-  <si>
-    <t>Principals of Chemistry  1a - 1e</t>
-  </si>
-  <si>
-    <t>Bonding  1f - 1h</t>
-  </si>
-  <si>
-    <t>Inorganic Chem part 1 - 1a - 1d</t>
-  </si>
-  <si>
-    <t>Inorganic Chem part 2 - 1e - 1g</t>
-  </si>
-  <si>
-    <t>Energetics</t>
-  </si>
-  <si>
-    <t>Rates of Reaction</t>
-  </si>
-  <si>
-    <t>Reversible reaction and equilbria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">y10 Organics </t>
-  </si>
-  <si>
-    <t>y11 Organics</t>
-  </si>
-  <si>
-    <t>9.1 Measuring waves + 10.1 Properties of waves &amp; EM Spectrum</t>
-  </si>
-  <si>
-    <t>9.2 Electrostatics and electrical current</t>
-  </si>
-  <si>
-    <t>9.3 Mains electricity + 10.4 Electrical circuits</t>
-  </si>
-  <si>
-    <t>9.4 Astronomy</t>
-  </si>
-  <si>
-    <t>9.5 Measuring motion + 10.3 Unbalanced forces and acceleration</t>
-  </si>
-  <si>
-    <t>9.6 Magnetism and electromagnets + 10.6 Electromagnetism</t>
-  </si>
-  <si>
-    <t>9.7 Energy types and energy resources + 10.2 Energy transfer, work and power</t>
-  </si>
-  <si>
-    <t>9.8 Density and pressure + 10.5 Pressure in Liquids and Ideal Gases</t>
-  </si>
-  <si>
-    <t>10.7 Thermal energy and Change of State</t>
-  </si>
-  <si>
-    <t>11.1 Radioactivity</t>
-  </si>
-  <si>
-    <t>11.2 Forces, Momentum &amp; Moments</t>
-  </si>
-  <si>
-    <t>Do Lots of Past Papers</t>
-  </si>
-  <si>
-    <t>Do the reasoning and problem solving question papers on firefly</t>
   </si>
   <si>
     <t>Between A Rock &amp; Hard Place Annotation and practise questions</t>
@@ -473,126 +548,210 @@
     <t>Transactional Writing Practise: Guide</t>
   </si>
   <si>
+    <t xml:space="preserve">  English Literature</t>
+  </si>
+  <si>
     <t>Quotations and meaning for VFAB Characters - Eddie, Alfieri, Catherine, Rodolfo</t>
   </si>
   <si>
-    <t>VFAB - Themes:  Loyalty and honour
-Justice
-Transition and change</t>
-  </si>
-  <si>
-    <t>do a recap on sme. get quotations about themes and then analyse quotations</t>
-  </si>
-  <si>
     <t>Practise planning and writing essays for VFAB</t>
   </si>
   <si>
     <t>Quotations and meaning for Romeo &amp; Juliet characters - Eddie, Alfieri, Catherine, Rodolfo</t>
   </si>
   <si>
-    <t>Romeo and Juliet: Revise themes: ❤️ Love and romance
+    <t>Practise planning and writing essays for R&amp;J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Geography</t>
+  </si>
+  <si>
+    <t>Hazards</t>
+  </si>
+  <si>
+    <t>Economic Activity &amp; energy</t>
+  </si>
+  <si>
+    <t>Coasts</t>
+  </si>
+  <si>
+    <t>Coastal Fieldwork</t>
+  </si>
+  <si>
+    <t>Urban Environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  History</t>
+  </si>
+  <si>
+    <t>America 1918 - 1941</t>
+  </si>
+  <si>
+    <t>US Civil Rights</t>
+  </si>
+  <si>
+    <t>History of Medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Spanish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Computer Science</t>
+  </si>
+  <si>
+    <t>1.1 - Systems Architecture</t>
+  </si>
+  <si>
+    <t>1.2 - Memory and storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3 - Computer networks, connections and protocols </t>
+  </si>
+  <si>
+    <t>1.4 - Network security</t>
+  </si>
+  <si>
+    <t>1.5 - Systems software</t>
+  </si>
+  <si>
+    <t>1.6 - Ethical, legal, cultural and environmental impacts of digital technology</t>
+  </si>
+  <si>
+    <t>Do exam questions on PMT then mark it. Look at the 8 marker as well. If time do exam questions on chatgpt</t>
+  </si>
+  <si>
+    <t>2.1 - Algorithms</t>
+  </si>
+  <si>
+    <t>2.2 - Producing robust programs</t>
+  </si>
+  <si>
+    <t>⚙  Settings</t>
+  </si>
+  <si>
+    <t>Review intervals — how many days until a topic comes back</t>
+  </si>
+  <si>
+    <t>Interval (days)</t>
+  </si>
+  <si>
+    <t>Not Assessed</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Edit the interval numbers in column C to change how often topics come back.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Group 7: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Inheritance
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+Characteristics of living organisms
+Levels of organisation
+Cell structure
+Variety of living organisms</t>
+    </r>
+  </si>
+  <si>
+    <t>Alright we are done. First Bit of bio revision done :)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Do field work questions on firefly. 
+2.Do practise quesitons which are on that firefly page. </t>
+  </si>
+  <si>
+    <t>Romeo and Juliet: Revise themes:
+ ❤️ Love and romance
 👑 Power and control
 🕊️ Hope and forgiveness</t>
   </si>
   <si>
-    <t>Practise planning and writing essays for R&amp;J</t>
-  </si>
-  <si>
-    <t>Hazards</t>
-  </si>
-  <si>
-    <t>Economic Activity &amp; energy</t>
-  </si>
-  <si>
-    <t>Coasts</t>
-  </si>
-  <si>
-    <t>Coastal Fieldwork</t>
-  </si>
-  <si>
-    <t>Urban Environments</t>
-  </si>
-  <si>
-    <t>Continue Chatgpt quiz. Finish the entire thing then make flashcards for key things I need to know. Its looking good tho. :)</t>
-  </si>
-  <si>
-    <t>America 1918 - 1941</t>
-  </si>
-  <si>
-    <t>Do practise questions on chapters 3,4,5</t>
-  </si>
-  <si>
-    <t>US Civil Rights</t>
-  </si>
-  <si>
-    <t>History of Medicine</t>
-  </si>
-  <si>
-    <t>New Vocab + Oral practise</t>
-  </si>
-  <si>
-    <t>Grammer + Writing</t>
-  </si>
-  <si>
-    <t>Exam paper practise</t>
-  </si>
-  <si>
-    <t>Listening practise + New Vocab</t>
-  </si>
-  <si>
-    <t>1.1 - Systems Architecture</t>
-  </si>
-  <si>
-    <t>1.2 - Memory and storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3 - Computer networks, connections and protocols </t>
-  </si>
-  <si>
-    <t>1.4 - Network security</t>
-  </si>
-  <si>
-    <t>1.5 - Systems software</t>
-  </si>
-  <si>
-    <t>1.6 - Ethical, legal, cultural and environmental impacts of digital technology</t>
-  </si>
-  <si>
-    <t>Do exam questions on PMT then mark it. Look at the 8 marker as well. If time do exam questions on chatgpt</t>
-  </si>
-  <si>
-    <t>2.1 - Algorithms</t>
-  </si>
-  <si>
-    <t>2.2 - Producing robust programs</t>
-  </si>
-  <si>
-    <t>⚙  Settings</t>
-  </si>
-  <si>
-    <t>Review intervals — how many days until a topic comes back</t>
-  </si>
-  <si>
-    <t>Interval (days)</t>
-  </si>
-  <si>
-    <t>Not Assessed</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>Edit the interval numbers in column C to change how often topics come back.</t>
-  </si>
-  <si>
-    <t>&lt; Return to Dashboard</t>
+    <t>VFAB - Themes:  
+1. Different views of loyalty and honour
+2. Different views of justice
+3. Transition and change</t>
+  </si>
+  <si>
+    <t>Very tough and bad session. Next time just get this section finished. use chatgpt to teach you anything man. We have to do something different cuz it was really hard. Chatgpt is going to have to save me</t>
+  </si>
+  <si>
+    <t>When doing a review session just do a little chatgpt quiz to finish up the rest of this topic.</t>
+  </si>
+  <si>
+    <t>1. Do that 16 marker i didn't do last time
+2. read up on the whole of Section 3
+3. If time start doing the 6,8,16 mark questions on that section (I highly doubt you will get to this tho you will probably do it next session)</t>
+  </si>
+  <si>
+    <t>Do reading papers</t>
+  </si>
+  <si>
+    <t>Do writing papers</t>
+  </si>
+  <si>
+    <t>practise for oral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next session do this (should be a chill session):
+1. revise all tenses on thisisschool/conjugemos
+2. Keep on going with the reading paper, putting words you don't know in the quizlet
+3. In the last 10 mins do the quizlet. </t>
+  </si>
+  <si>
+    <t>Do listening papers</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+  </numFmts>
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -710,22 +869,44 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF808080"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFDC3232"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFDC3232"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -787,6 +968,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFE2F3"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -860,9 +1047,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -925,20 +1112,38 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -966,15 +1171,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -982,7 +1193,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="116">
+  <dxfs count="177">
     <dxf>
       <font>
         <b/>
@@ -1595,6 +1806,433 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEBEBEB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8B6B6"/>
         </patternFill>
@@ -1613,6 +2251,31 @@
           <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
@@ -1754,31 +2417,6 @@
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1848,22 +2486,25 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>17241</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
+        <xdr:cNvPr id="2" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB10268D-91A7-3149-B61A-51B8BF7412C3}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{70D1EF11-EB8C-E4B3-A3FB-8501B9969DDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1885,7 +2526,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="647700" y="6096000"/>
+          <a:off x="866775" y="10668000"/>
           <a:ext cx="11811000" cy="5351241"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1899,28 +2540,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:E27" headerRowDxfId="107" dataDxfId="106" totalsRowDxfId="105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:E27" headerRowDxfId="176" dataDxfId="175" totalsRowDxfId="174">
   <autoFilter ref="A3:E27" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="104"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="103"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="102"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="101"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="100"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="173"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="172"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="171"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="170"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="169"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="ComputerScienceTbl" displayName="ComputerScienceTbl" ref="A3:E18" headerRowDxfId="115" dataDxfId="114" totalsRowDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="ComputerScienceTbl" displayName="ComputerScienceTbl" ref="A3:E18" headerRowDxfId="131" dataDxfId="130" totalsRowDxfId="129">
   <autoFilter ref="A3:E18" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Topic" dataDxfId="112"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Status" dataDxfId="111"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Confidence" dataDxfId="110"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Last Revised" dataDxfId="109"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Next Action" dataDxfId="108"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Topic" dataDxfId="128"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Status" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Confidence" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Last Revised" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Next Action" dataDxfId="124"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1933,7 +2574,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="99"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="168"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Next Action"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
@@ -1941,70 +2582,70 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PhysicsTbl" displayName="PhysicsTbl" ref="A3:E18" dataDxfId="98">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PhysicsTbl" displayName="PhysicsTbl" ref="A3:E18" dataDxfId="167">
   <autoFilter ref="A3:E18" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Topic" dataDxfId="97"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Status" dataDxfId="96"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Confidence" dataDxfId="95"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Last Revised" dataDxfId="94"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Next Action" dataDxfId="93"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Topic" dataDxfId="166"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Status" dataDxfId="165"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Confidence" dataDxfId="164"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Last Revised" dataDxfId="163"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Next Action" dataDxfId="162"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="MathematicsTbl" displayName="MathematicsTbl" ref="A3:E18" headerRowDxfId="92" dataDxfId="91" totalsRowDxfId="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="MathematicsTbl" displayName="MathematicsTbl" ref="A3:E18" headerRowDxfId="161" dataDxfId="160" totalsRowDxfId="159">
   <autoFilter ref="A3:E18" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Topic" dataDxfId="89"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status" dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Confidence" dataDxfId="87"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Last Revised" dataDxfId="86"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Next Action" dataDxfId="85"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Topic" dataDxfId="158"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status" dataDxfId="157"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Confidence" dataDxfId="156"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Last Revised" dataDxfId="155"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Next Action" dataDxfId="154"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EnglishLanguageTbl" displayName="EnglishLanguageTbl" ref="A3:E18" dataDxfId="84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EnglishLanguageTbl" displayName="EnglishLanguageTbl" ref="A3:E18" dataDxfId="153">
   <autoFilter ref="A3:E18" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Topic" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Status" dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Confidence" dataDxfId="81"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Last Revised" dataDxfId="80"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Next Action" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Topic" dataDxfId="152"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Status" dataDxfId="151"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Confidence" dataDxfId="150"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Last Revised" dataDxfId="149"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Next Action" dataDxfId="148"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="EnglishLiteratureTbl" displayName="EnglishLiteratureTbl" ref="A3:E18" headerRowDxfId="78" dataDxfId="77" totalsRowDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="EnglishLiteratureTbl" displayName="EnglishLiteratureTbl" ref="A3:E18" headerRowDxfId="147" dataDxfId="146" totalsRowDxfId="145">
   <autoFilter ref="A3:E18" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Topic" dataDxfId="75"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Status" dataDxfId="74"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Confidence" dataDxfId="73"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Last Revised" dataDxfId="72"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Next Action" dataDxfId="71"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Topic" dataDxfId="144"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Status" dataDxfId="143"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Confidence" dataDxfId="142"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Last Revised" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Next Action" dataDxfId="140"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="GeographyTbl" displayName="GeographyTbl" ref="A3:E18" dataDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="GeographyTbl" displayName="GeographyTbl" ref="A3:E18" dataDxfId="139">
   <autoFilter ref="A3:E18" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Topic" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Status" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Confidence" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Last Revised" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Next Action" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Topic" dataDxfId="138"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Status" dataDxfId="137"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Confidence" dataDxfId="136"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Last Revised" dataDxfId="135"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Next Action" dataDxfId="134"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2017,7 +2658,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Last Revised" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Last Revised" dataDxfId="133"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Next Action"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
@@ -2031,7 +2672,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Last Revised" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Last Revised" dataDxfId="132"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Next Action"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
@@ -2338,44 +2979,44 @@
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15" style="19" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="19" customWidth="1"/>
+    <col min="5" max="5" width="43.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="A1" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>136</v>
+      <c r="A2" s="50" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
@@ -2384,15 +3025,15 @@
         <v>22</v>
       </c>
       <c r="D4" s="4">
-        <v>46308</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>114</v>
+        <v>46314</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2401,7 +3042,7 @@
     </row>
     <row r="6" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -2545,72 +3186,81 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15" style="19" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" style="19" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="A1" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>136</v>
+      <c r="A2" s="50" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46314</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -2753,39 +3403,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="A1" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>136</v>
+      <c r="A2" s="50" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2794,7 +3444,7 @@
     </row>
     <row r="5" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -2803,7 +3453,7 @@
     </row>
     <row r="6" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -2812,7 +3462,7 @@
     </row>
     <row r="7" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -2821,7 +3471,7 @@
     </row>
     <row r="8" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -2830,7 +3480,7 @@
     </row>
     <row r="9" spans="1:5" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -2842,12 +3492,12 @@
         <v>46310</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -2856,7 +3506,7 @@
     </row>
     <row r="11" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -2971,25 +3621,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
+      <c r="B2" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
     </row>
     <row r="4" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
+      <c r="B4" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
     </row>
     <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
@@ -3018,18 +3668,18 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
+      <c r="B12" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3046,28 +3696,26 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="8" width="11" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="13" max="13" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
       <c r="M1" t="s">
         <v>1</v>
       </c>
@@ -3078,14 +3726,14 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
       <c r="M3" t="s">
         <v>4</v>
       </c>
@@ -3113,26 +3761,26 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35">
+      <c r="A6" s="41">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*"))</f>
-        <v>81</v>
-      </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="37">
+        <v>66</v>
+      </c>
+      <c r="B6" s="38"/>
+      <c r="C6" s="43">
         <f ca="1">A6-E6-G6</f>
-        <v>75</v>
-      </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="36">
+        <v>57</v>
+      </c>
+      <c r="D6" s="38"/>
+      <c r="E6" s="42">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"In Progress"))</f>
-        <v>5</v>
-      </c>
-      <c r="F6" s="32"/>
-      <c r="G6" s="31">
+        <v>6</v>
+      </c>
+      <c r="F6" s="38"/>
+      <c r="G6" s="37">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"Completed"))</f>
-        <v>1</v>
-      </c>
-      <c r="H6" s="32"/>
+        <v>3</v>
+      </c>
+      <c r="H6" s="38"/>
       <c r="M6" t="s">
         <v>11</v>
       </c>
@@ -3154,16 +3802,16 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34">
+      <c r="A9" s="40">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Amber"))</f>
-        <v>1</v>
-      </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="33">
+        <v>0</v>
+      </c>
+      <c r="B9" s="38"/>
+      <c r="C9" s="39">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Red"))</f>
-        <v>1</v>
-      </c>
-      <c r="D9" s="32"/>
+        <v>2</v>
+      </c>
+      <c r="D9" s="38"/>
       <c r="M9" t="s">
         <v>16</v>
       </c>
@@ -3179,432 +3827,475 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-    </row>
-    <row r="13" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="42" t="s">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+    </row>
+    <row r="13" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="28" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="I13" s="31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*"))</f>
-        <v>23</v>
-      </c>
-      <c r="C14" s="3">
+        <v>8</v>
+      </c>
+      <c r="C14" s="24">
         <f t="shared" ref="C14:C23" ca="1" si="0">B14-D14-E14</f>
-        <v>23</v>
-      </c>
-      <c r="D14" s="3">
+        <v>7</v>
+      </c>
+      <c r="D14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!B4:B1000"),"In Progress"))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!B4:B1000"),"Completed"))</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Green"))</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="29" t="str">
+        <f ca="1">IF(MAX(Biology!D4:D1000)=0, "-", IF(MAX(Biology!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Biology!D4:D1000)=1, "Yesterday", TODAY()-MAX(Biology!D4:D1000) &amp; " days ago")))</f>
+        <v>2 days ago</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*"))</f>
         <v>9</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="26">
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!B4:B1000"),"In Progress"))</f>
         <v>0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Green"))</f>
         <v>0</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="I15" s="30" t="str">
+        <f ca="1">IF(MAX(Chemistry!D4:D1000)=0, "N/A", IF(MAX(Chemistry!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Chemistry!D4:D1000)=1, "Yesterday", TODAY()-MAX(Chemistry!D4:D1000) &amp; " days ago")))</f>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*"))</f>
         <v>11</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="24">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="D16" s="3">
+        <v>10</v>
+      </c>
+      <c r="D16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!B4:B1000"),"In Progress"))</f>
         <v>0</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!B4:B1000"),"Completed"))</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="F16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Green"))</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I16" s="29" t="str">
+        <f ca="1">IF(MAX(Physics!D4:D1000)=0, "-", IF(MAX(Physics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Physics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Physics!D4:D1000) &amp; " days ago")))</f>
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*"))</f>
         <v>1</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="26">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!C4:C1000"),"Green"))</f>
         <v>1</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="I17" s="30" t="str">
+        <f ca="1">IF(MAX(Mathematics!D4:D1000)=0, "-", IF(MAX(Mathematics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Mathematics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Mathematics!D4:D1000) &amp; " days ago")))</f>
+        <v>3 days ago</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*"))</f>
         <v>11</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="24">
         <f t="shared" ca="1" si="0"/>
         <v>10</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!B4:B1000"),"In Progress"))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!B4:B1000"),"Completed"))</f>
         <v>1</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Green"))</f>
         <v>0</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Red"))</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I18" s="29" t="str">
+        <f ca="1">IF(MAX('English Language'!D4:D1000)=0, "-", IF(MAX('English Language'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Language'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Language'!D4:D1000) &amp; " days ago")))</f>
+        <v>4 days ago</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*"))</f>
         <v>6</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="26">
         <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Green"))</f>
         <v>0</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Amber"))</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="26">
+        <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Red"))</f>
         <v>1</v>
       </c>
-      <c r="H19" s="3">
-        <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Red"))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+      <c r="I19" s="30" t="str">
+        <f ca="1">IF(MAX('English Literature'!D4:D1000)=0, "-", IF(MAX('English Literature'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Literature'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Literature'!D4:D1000) &amp; " days ago")))</f>
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*"))</f>
         <v>5</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="24">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Green"))</f>
         <v>1</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I20" s="29" t="str">
+        <f ca="1">IF(MAX(Geography!D4:D1000)=0, "-", IF(MAX(Geography!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Geography!D4:D1000)=1, "Yesterday", TODAY()-MAX(Geography!D4:D1000) &amp; " days ago")))</f>
+        <v>5 days ago</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*"))</f>
         <v>3</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="26">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!C4:C1000"),"Green"))</f>
         <v>1</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="I21" s="30" t="str">
+        <f ca="1">IF(MAX(History!D4:D1000)=0, "-", IF(MAX(History!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(History!D4:D1000)=1, "Yesterday", TODAY()-MAX(History!D4:D1000) &amp; " days ago")))</f>
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*"))</f>
         <v>4</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="24">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D22" s="3">
+        <v>3</v>
+      </c>
+      <c r="D22" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!B4:B1000"),"In Progress"))</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!C4:C1000"),"Green"))</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="29" t="str">
+        <f ca="1">IF(MAX(Spanish!D4:D1000)=0, "-", IF(MAX(Spanish!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Spanish!D4:D1000)=1, "Yesterday", TODAY()-MAX(Spanish!D4:D1000) &amp; " days ago")))</f>
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*"))</f>
         <v>8</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="26">
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Green"))</f>
         <v>1</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
+      <c r="I23" s="30" t="str">
+        <f ca="1">IF(MAX('Computer Science'!D4:D1000)=0, "-", IF(MAX('Computer Science'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('Computer Science'!D4:D1000)=1, "Yesterday", TODAY()-MAX('Computer Science'!D4:D1000) &amp; " days ago")))</f>
+        <v>5 days ago</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3624,18 +4315,203 @@
     <mergeCell ref="C6:D6"/>
   </mergeCells>
   <conditionalFormatting sqref="F14:F23">
-    <cfRule type="cellIs" dxfId="62" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="123" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:G23">
-    <cfRule type="cellIs" dxfId="61" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="122" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H23">
-    <cfRule type="cellIs" dxfId="60" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="121" priority="3" operator="greaterThan">
       <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I14:I23">
+    <cfRule type="cellIs" dxfId="120" priority="4" stopIfTrue="1" operator="equal">
+      <formula>"Today"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="119" priority="5" stopIfTrue="1" operator="equal">
+      <formula>"Yesterday"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="6" stopIfTrue="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="7" stopIfTrue="1" operator="equal">
+      <formula>"4 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="116" priority="8" stopIfTrue="1" operator="equal">
+      <formula>"5 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="9" stopIfTrue="1" operator="equal">
+      <formula>"6 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="10" stopIfTrue="1" operator="equal">
+      <formula>"7 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="113" priority="11" stopIfTrue="1" operator="equal">
+      <formula>"8 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="12" stopIfTrue="1" operator="equal">
+      <formula>"9 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="13" stopIfTrue="1" operator="equal">
+      <formula>"10 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="110" priority="14" stopIfTrue="1" operator="equal">
+      <formula>"11 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="15" stopIfTrue="1" operator="equal">
+      <formula>"12 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="16" stopIfTrue="1" operator="equal">
+      <formula>"13 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="107" priority="17" stopIfTrue="1" operator="equal">
+      <formula>"14 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="18" stopIfTrue="1" operator="equal">
+      <formula>"15 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="19" stopIfTrue="1" operator="equal">
+      <formula>"16 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="20" stopIfTrue="1" operator="equal">
+      <formula>"17 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="21" stopIfTrue="1" operator="equal">
+      <formula>"18 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="22" stopIfTrue="1" operator="equal">
+      <formula>"19 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="101" priority="23" stopIfTrue="1" operator="equal">
+      <formula>"20 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="24" stopIfTrue="1" operator="equal">
+      <formula>"21 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="25" stopIfTrue="1" operator="equal">
+      <formula>"22 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="26" stopIfTrue="1" operator="equal">
+      <formula>"23 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="27" stopIfTrue="1" operator="equal">
+      <formula>"24 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="28" stopIfTrue="1" operator="equal">
+      <formula>"25 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="95" priority="29" stopIfTrue="1" operator="equal">
+      <formula>"26 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="30" stopIfTrue="1" operator="equal">
+      <formula>"27 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="31" stopIfTrue="1" operator="equal">
+      <formula>"28 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="92" priority="32" stopIfTrue="1" operator="equal">
+      <formula>"29 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="33" stopIfTrue="1" operator="equal">
+      <formula>"30 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="34" stopIfTrue="1" operator="equal">
+      <formula>"31 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="89" priority="35" stopIfTrue="1" operator="equal">
+      <formula>"32 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="36" stopIfTrue="1" operator="equal">
+      <formula>"33 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="37" stopIfTrue="1" operator="equal">
+      <formula>"34 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="86" priority="38" stopIfTrue="1" operator="equal">
+      <formula>"35 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="39" stopIfTrue="1" operator="equal">
+      <formula>"36 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="40" stopIfTrue="1" operator="equal">
+      <formula>"37 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="41" stopIfTrue="1" operator="equal">
+      <formula>"38 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="42" stopIfTrue="1" operator="equal">
+      <formula>"39 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="43" stopIfTrue="1" operator="equal">
+      <formula>"40 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="44" stopIfTrue="1" operator="equal">
+      <formula>"41 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="45" stopIfTrue="1" operator="equal">
+      <formula>"42 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="46" stopIfTrue="1" operator="equal">
+      <formula>"43 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="77" priority="47" stopIfTrue="1" operator="equal">
+      <formula>"44 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="48" stopIfTrue="1" operator="equal">
+      <formula>"45 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="49" stopIfTrue="1" operator="equal">
+      <formula>"46 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="50" stopIfTrue="1" operator="equal">
+      <formula>"47 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="51" stopIfTrue="1" operator="equal">
+      <formula>"48 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="52" stopIfTrue="1" operator="equal">
+      <formula>"49 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="53" stopIfTrue="1" operator="equal">
+      <formula>"50 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="54" stopIfTrue="1" operator="equal">
+      <formula>"51 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="55" stopIfTrue="1" operator="equal">
+      <formula>"52 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="68" priority="56" stopIfTrue="1" operator="equal">
+      <formula>"53 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="57" stopIfTrue="1" operator="equal">
+      <formula>"54 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="58" stopIfTrue="1" operator="equal">
+      <formula>"55 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="59" stopIfTrue="1" operator="equal">
+      <formula>"56 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="60" stopIfTrue="1" operator="equal">
+      <formula>"57 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="61" stopIfTrue="1" operator="equal">
+      <formula>"58 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="62" stopIfTrue="1" operator="equal">
+      <formula>"59 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="63" stopIfTrue="1" operator="equal">
+      <formula>"2 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="64" stopIfTrue="1" operator="equal">
+      <formula>"3 days ago"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -3667,17 +4543,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="A1" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
-        <v>136</v>
+      <c r="A2" s="48" t="s">
+        <v>29</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3686,87 +4562,95 @@
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46313</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="11"/>
       <c r="E5" s="9"/>
     </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="11"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="11"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="11"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -3774,135 +4658,105 @@
       <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="11"/>
       <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>52</v>
-      </c>
+      <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
       <c r="E13" s="9"/>
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>53</v>
-      </c>
+      <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
       <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>54</v>
-      </c>
+      <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
       <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>55</v>
-      </c>
+      <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
       <c r="E16" s="9"/>
     </row>
     <row r="17" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>56</v>
-      </c>
+      <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11"/>
       <c r="E17" s="9"/>
     </row>
     <row r="18" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>57</v>
-      </c>
+      <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="11"/>
       <c r="E18" s="9"/>
     </row>
     <row r="19" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>59</v>
-      </c>
+      <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="4"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="4"/>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>62</v>
-      </c>
+      <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="4"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>63</v>
-      </c>
+      <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="4"/>
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="4"/>
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="4"/>
@@ -3974,39 +4828,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="A1" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>136</v>
+      <c r="A2" s="49" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -4015,7 +4869,7 @@
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -4024,7 +4878,7 @@
     </row>
     <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4033,7 +4887,7 @@
     </row>
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -4042,7 +4896,7 @@
     </row>
     <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4051,7 +4905,7 @@
     </row>
     <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4060,7 +4914,7 @@
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -4069,7 +4923,7 @@
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -4078,7 +4932,7 @@
     </row>
     <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -4186,48 +5040,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="A1" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>136</v>
+      <c r="A2" s="50" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="9"/>
+        <v>52</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46314</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -4236,7 +5098,7 @@
     </row>
     <row r="6" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -4245,7 +5107,7 @@
     </row>
     <row r="7" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -4254,7 +5116,7 @@
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -4263,7 +5125,7 @@
     </row>
     <row r="9" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -4272,7 +5134,7 @@
     </row>
     <row r="10" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -4281,7 +5143,7 @@
     </row>
     <row r="11" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -4290,7 +5152,7 @@
     </row>
     <row r="12" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -4299,7 +5161,7 @@
     </row>
     <row r="13" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -4308,7 +5170,7 @@
     </row>
     <row r="14" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -4403,39 +5265,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="A1" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>136</v>
+      <c r="A2" s="50" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>8</v>
@@ -4447,7 +5309,7 @@
         <v>46312</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4608,39 +5470,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="A1" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>136</v>
+      <c r="A2" s="50" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -4649,7 +5511,7 @@
     </row>
     <row r="5" spans="1:5" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -4658,7 +5520,7 @@
     </row>
     <row r="6" spans="1:5" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>9</v>
@@ -4670,12 +5532,12 @@
         <v>46311</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -4684,7 +5546,7 @@
     </row>
     <row r="8" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -4693,7 +5555,7 @@
     </row>
     <row r="9" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -4702,7 +5564,7 @@
     </row>
     <row r="10" spans="1:5" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -4711,7 +5573,7 @@
     </row>
     <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -4720,7 +5582,7 @@
     </row>
     <row r="12" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -4729,7 +5591,7 @@
     </row>
     <row r="13" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -4738,7 +5600,7 @@
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -4828,44 +5690,44 @@
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15" style="19" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" style="19" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="A1" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>136</v>
+      <c r="A2" s="50" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -4874,24 +5736,24 @@
     </row>
     <row r="5" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="11">
-        <v>46309</v>
+        <v>14</v>
+      </c>
+      <c r="D5" s="22">
+        <v>46314</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -4900,7 +5762,7 @@
     </row>
     <row r="7" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -4909,7 +5771,7 @@
     </row>
     <row r="8" spans="1:5" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -4918,7 +5780,7 @@
     </row>
     <row r="9" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -5047,39 +5909,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
         <v>29</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-    </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -5088,7 +5950,7 @@
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -5097,7 +5959,7 @@
     </row>
     <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -5106,7 +5968,7 @@
     </row>
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -5115,7 +5977,7 @@
     </row>
     <row r="8" spans="1:5" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>8</v>
@@ -5127,7 +5989,7 @@
         <v>46310</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">

--- a/revision tracker/Revision_Tracker.xlsx
+++ b/revision tracker/Revision_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/948b5d172b360b34/Python Stuff/revision tracker/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sevenoaksschool-my.sharepoint.com/personal/chil03_sevenoaksschool_org/Documents/year 11/Revision Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1872" documentId="8_{1E299D6C-A0CB-477B-8398-5EE539A6181E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B585214-C7B8-4A0D-B24B-FCFE17CEE829}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{612638F8-D48E-420C-A662-1F27EDA1CCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11565" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revision Timetable" sheetId="13" r:id="rId1"/>
@@ -30,7 +30,7 @@
   <definedNames>
     <definedName name="Subjects">Dashboard!$M$2:$M$11</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="134">
   <si>
     <t xml:space="preserve">  GCSE Revision Tracker — Dashboard</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>Next Action</t>
+  </si>
+  <si>
+    <t>General Notes</t>
   </si>
   <si>
     <r>
@@ -420,9 +423,15 @@
     <t>When doing a review session just do a little chatgpt quiz to finish up the rest of this topic.</t>
   </si>
   <si>
+    <t>Lets try do 9.5, 10.3, 10.7 next. All revise using chatgpt. Go over content then do big practise quiz with chatgtt. We are trying to get through all the content early so we can specialise later</t>
+  </si>
+  <si>
     <t>9.2 Electrostatics and electrical current</t>
   </si>
   <si>
+    <t>Practise examination questions</t>
+  </si>
+  <si>
     <t>9.3 Mains electricity + 10.4 Electrical circuits</t>
   </si>
   <si>
@@ -456,7 +465,12 @@
     <t>Do Lots of Past Papers</t>
   </si>
   <si>
-    <t>Do the reasoning and problem solving question papers on firefly</t>
+    <t xml:space="preserve">1. Finish of doing summer 2012 paper 1 on onenote
+2. Mark it
+</t>
+  </si>
+  <si>
+    <t>Your next task will to be a chatgpt test on all the topics using the list of topics here. This will be the task for the lesson after next lesson: https://sevenoaksschool.fireflycloud.net/resource.aspx?id=1354099</t>
   </si>
   <si>
     <t xml:space="preserve">  English Language</t>
@@ -487,7 +501,32 @@
 2. Do a past language paper on firefly. Go to the english page then go to paper 1 overviews</t>
   </si>
   <si>
-    <t>Transactional Writing Practise: Magazine article</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Explorers, or boys messing about: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> annotation and practise questions</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Next task:
+Do january 2022 paper on firefly:
+</t>
   </si>
   <si>
     <r>
@@ -548,7 +587,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Young and dyslexic</t>
+      <t>Young and dyslexic? You've got it going on</t>
     </r>
     <r>
       <rPr>
@@ -558,63 +597,20 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> and annotation and practise questions</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Explorers, or boys messing about: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> annotation and practise questions</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>You've got it going on</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: annotation and practise questions</t>
-    </r>
+    <t>Transactional Writing Practise: Leaflet text</t>
+  </si>
+  <si>
+    <t>Transactional Writing Practise: Magazine article</t>
   </si>
   <si>
     <t>Transactional Writing Practise: Guide</t>
   </si>
   <si>
     <t>Transactional Writing Practise: Letter</t>
-  </si>
-  <si>
-    <t>Transactional Writing Practise: Leaflet text</t>
   </si>
   <si>
     <t xml:space="preserve">  English Literature</t>
@@ -629,7 +625,7 @@
 3. Transition and change</t>
   </si>
   <si>
-    <t>Very tough and bad session. Next time just get this section finished. use chatgpt to teach you anything man. We have to do something different cuz it was really hard. Chatgpt is going to have to save me</t>
+    <t>finish the 2nd quotation for theme 1. Then do 2 quotations and anlysis for the other 2 themes. You really need to finish this topic in the next session spend an hour on this and just get it done.</t>
   </si>
   <si>
     <t>Practise planning and writing essays for VFAB</t>
@@ -677,9 +673,8 @@
     <t>America 1918 - 1941</t>
   </si>
   <si>
-    <t>1. Do that 16 marker i didn't do last time
-2. read up on the whole of Section 3
-3. If time start doing the 6,8,16 mark questions on that section (I highly doubt you will get to this tho you will probably do it next session)</t>
+    <t xml:space="preserve">read up on the whole of Section 3 and 4. Just spend the whole session catching up on that its very likely you won't do any questions on it
+</t>
   </si>
   <si>
     <t>US Civil Rights</t>
@@ -755,9 +750,6 @@
   </si>
   <si>
     <t>Edit the interval numbers in column C to change how often topics come back.</t>
-  </si>
-  <si>
-    <t>General Notes</t>
   </si>
 </sst>
 </file>
@@ -767,7 +759,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1256,19 +1248,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1285,13 +1270,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent5" xfId="2" builtinId="45"/>
@@ -1300,6 +1292,37 @@
   </cellStyles>
   <dxfs count="188">
     <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1361,6 +1384,9 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1422,6 +1448,9 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1483,6 +1512,28 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1544,6 +1595,37 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1605,6 +1687,28 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1666,6 +1770,37 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1727,6 +1862,28 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1788,6 +1945,9 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1849,6 +2009,37 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -2356,205 +2547,6 @@
           <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2666,30 +2658,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:F27" headerRowDxfId="187" dataDxfId="186" totalsRowDxfId="185">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:F27" headerRowDxfId="117" dataDxfId="116" totalsRowDxfId="115">
   <autoFilter ref="A3:F27" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="184"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="183"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="182"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="181"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="180"/>
-    <tableColumn id="5" xr3:uid="{F0BDA802-DA31-4BA7-81BA-FDB612DC37E1}" name="General Notes" dataDxfId="179" totalsRowDxfId="178"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="114"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="113"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="112"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="111"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="110"/>
+    <tableColumn id="5" xr3:uid="{F0BDA802-DA31-4BA7-81BA-FDB612DC37E1}" name="General Notes" dataDxfId="108" totalsRowDxfId="109"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="ComputerScienceTbl" displayName="ComputerScienceTbl" ref="A3:F18" headerRowDxfId="133" dataDxfId="132" totalsRowDxfId="131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="ComputerScienceTbl" displayName="ComputerScienceTbl" ref="A3:F18" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="7">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Topic" dataDxfId="130"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Status" dataDxfId="129"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Confidence" dataDxfId="128"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Last Revised" dataDxfId="127"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Next Action" dataDxfId="126"/>
-    <tableColumn id="5" xr3:uid="{63D6C4F6-C7E6-4663-AE70-5CFDFF770C29}" name="General Notes" dataDxfId="125" totalsRowDxfId="124"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Topic" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Status" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Confidence" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Last Revised" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Next Action" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{63D6C4F6-C7E6-4663-AE70-5CFDFF770C29}" name="General Notes" dataDxfId="0" totalsRowDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2702,7 +2694,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="177"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="101"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{DB8974C0-4423-4F62-8CA0-D4A3FA4693EA}" name="General Notes"/>
   </tableColumns>
@@ -2711,75 +2703,75 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PhysicsTbl" displayName="PhysicsTbl" ref="A3:F18" dataDxfId="176">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PhysicsTbl" displayName="PhysicsTbl" ref="A3:F18" dataDxfId="94">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Topic" dataDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Status" dataDxfId="174"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Confidence" dataDxfId="173"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Last Revised" dataDxfId="172"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Next Action" dataDxfId="171"/>
-    <tableColumn id="5" xr3:uid="{2C5860E0-C42D-447A-99E8-019207F1E49B}" name="General Notes" dataDxfId="170"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Topic" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Status" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Confidence" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Last Revised" dataDxfId="90"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Next Action" dataDxfId="89"/>
+    <tableColumn id="5" xr3:uid="{2C5860E0-C42D-447A-99E8-019207F1E49B}" name="General Notes" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="MathematicsTbl" displayName="MathematicsTbl" ref="A3:F18" headerRowDxfId="169" dataDxfId="168" totalsRowDxfId="167">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="MathematicsTbl" displayName="MathematicsTbl" ref="A3:F18" headerRowDxfId="81" dataDxfId="80" totalsRowDxfId="79">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Topic" dataDxfId="166"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status" dataDxfId="165"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Confidence" dataDxfId="164"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Last Revised" dataDxfId="163"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Next Action" dataDxfId="162"/>
-    <tableColumn id="5" xr3:uid="{902E25C2-558C-4568-81EE-02B6DDE3EEEE}" name="General Notes" dataDxfId="161" totalsRowDxfId="160"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Topic" dataDxfId="78"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status" dataDxfId="77"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Confidence" dataDxfId="76"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Last Revised" dataDxfId="75"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Next Action" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{902E25C2-558C-4568-81EE-02B6DDE3EEEE}" name="General Notes" dataDxfId="72" totalsRowDxfId="73"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EnglishLanguageTbl" displayName="EnglishLanguageTbl" ref="A3:F18" dataDxfId="159">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EnglishLanguageTbl" displayName="EnglishLanguageTbl" ref="A3:F18" dataDxfId="65">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Topic" dataDxfId="158"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Status" dataDxfId="157"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Confidence" dataDxfId="156"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Last Revised" dataDxfId="155"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Next Action" dataDxfId="154"/>
-    <tableColumn id="5" xr3:uid="{75D1410F-47BB-4A48-905A-25CF74BDB786}" name="General Notes" dataDxfId="153"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Topic" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Status" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Confidence" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Last Revised" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Next Action" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{75D1410F-47BB-4A48-905A-25CF74BDB786}" name="General Notes" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="EnglishLiteratureTbl" displayName="EnglishLiteratureTbl" ref="A3:F18" headerRowDxfId="152" dataDxfId="151" totalsRowDxfId="150">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="EnglishLiteratureTbl" displayName="EnglishLiteratureTbl" ref="A3:F18" headerRowDxfId="52" dataDxfId="51" totalsRowDxfId="50">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Topic" dataDxfId="149"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Status" dataDxfId="148"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Confidence" dataDxfId="147"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Last Revised" dataDxfId="146"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Next Action" dataDxfId="145"/>
-    <tableColumn id="5" xr3:uid="{930CE764-AB02-4790-8724-F5622F11644B}" name="General Notes" dataDxfId="144" totalsRowDxfId="143"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Topic" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Status" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Confidence" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Last Revised" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Next Action" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{930CE764-AB02-4790-8724-F5622F11644B}" name="General Notes" dataDxfId="43" totalsRowDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="GeographyTbl" displayName="GeographyTbl" ref="A3:F18" dataDxfId="142">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="GeographyTbl" displayName="GeographyTbl" ref="A3:F18" dataDxfId="36">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Topic" dataDxfId="141"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Status" dataDxfId="140"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Confidence" dataDxfId="139"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Last Revised" dataDxfId="138"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Next Action" dataDxfId="137"/>
-    <tableColumn id="5" xr3:uid="{27D2B179-C2A7-46A7-8BEB-752BF05A8E89}" name="General Notes" dataDxfId="136"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Topic" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Status" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Confidence" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Last Revised" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Next Action" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{27D2B179-C2A7-46A7-8BEB-752BF05A8E89}" name="General Notes" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2792,7 +2784,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Last Revised" dataDxfId="135"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Last Revised" dataDxfId="23"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{28A5B818-9271-4E86-B3A0-50B7055F910C}" name="General Notes"/>
   </tableColumns>
@@ -2807,7 +2799,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Last Revised" dataDxfId="134"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Last Revised" dataDxfId="16"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{7C8E7108-0749-49A2-855D-B734764E8E58}" name="General Notes"/>
   </tableColumns>
@@ -3101,7 +3093,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669FF182-A9DF-49CA-A197-60E29E93D9CE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3111,7 +3103,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -3120,21 +3112,21 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A1" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
@@ -3151,12 +3143,12 @@
         <v>34</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="115.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
@@ -3165,16 +3157,16 @@
         <v>22</v>
       </c>
       <c r="D4" s="4">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F4" s="39"/>
     </row>
-    <row r="5" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="42.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3182,9 +3174,9 @@
       <c r="E5" s="41"/>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="45.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3192,7 +3184,7 @@
       <c r="E6" s="41"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="24" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -3200,7 +3192,7 @@
       <c r="E7" s="41"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="24" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -3208,7 +3200,7 @@
       <c r="E8" s="41"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="24" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -3216,7 +3208,7 @@
       <c r="E9" s="41"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="24" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -3224,7 +3216,7 @@
       <c r="E10" s="41"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="24" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -3232,7 +3224,7 @@
       <c r="E11" s="41"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="24" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3240,7 +3232,7 @@
       <c r="E12" s="41"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3248,7 +3240,7 @@
       <c r="E13" s="41"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -3256,7 +3248,7 @@
       <c r="E14" s="41"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -3264,7 +3256,7 @@
       <c r="E15" s="41"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -3272,7 +3264,7 @@
       <c r="E16" s="41"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3280,7 +3272,7 @@
       <c r="E17" s="41"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -3293,24 +3285,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3338,7 +3330,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -3348,21 +3340,21 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A1" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
@@ -3379,12 +3371,12 @@
         <v>34</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="113.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
@@ -3396,13 +3388,13 @@
         <v>46314</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F4" s="39"/>
     </row>
-    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="45" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3410,9 +3402,9 @@
       <c r="E5" s="41"/>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="37.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3420,9 +3412,9 @@
       <c r="E6" s="41"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="40.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -3430,7 +3422,7 @@
       <c r="E7" s="41"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="24" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -3438,7 +3430,7 @@
       <c r="E8" s="41"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="24" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -3446,7 +3438,7 @@
       <c r="E9" s="41"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="24" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -3454,7 +3446,7 @@
       <c r="E10" s="41"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="24" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -3462,7 +3454,7 @@
       <c r="E11" s="41"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="24" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3470,7 +3462,7 @@
       <c r="E12" s="41"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3478,7 +3470,7 @@
       <c r="E13" s="41"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -3486,7 +3478,7 @@
       <c r="E14" s="41"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -3494,7 +3486,7 @@
       <c r="E15" s="41"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -3502,7 +3494,7 @@
       <c r="E16" s="41"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3510,7 +3502,7 @@
       <c r="E17" s="41"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -3523,24 +3515,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3568,7 +3560,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -3577,21 +3569,21 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A1" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>31</v>
       </c>
@@ -3608,12 +3600,12 @@
         <v>34</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="44.25" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -3621,9 +3613,9 @@
       <c r="E4" s="37"/>
       <c r="F4" s="39"/>
     </row>
-    <row r="5" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="43.5" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -3631,9 +3623,9 @@
       <c r="E5" s="37"/>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="48.75" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -3641,9 +3633,9 @@
       <c r="E6" s="37"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="45.75" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -3651,9 +3643,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="57" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -3661,9 +3653,9 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="90.75" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>9</v>
@@ -3675,13 +3667,13 @@
         <v>46315</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="42" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -3689,9 +3681,9 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="43.5" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -3699,7 +3691,7 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="24" customHeight="1">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -3707,7 +3699,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -3715,7 +3707,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -3723,7 +3715,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -3731,7 +3723,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -3739,7 +3731,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -3747,7 +3739,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -3760,24 +3752,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3805,7 +3797,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B2:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -3813,29 +3805,29 @@
     <col min="4" max="4" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="57" t="s">
-        <v>124</v>
-      </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-    </row>
-    <row r="4" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-    </row>
-    <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" ht="28.5" customHeight="1">
+      <c r="B2" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+    </row>
+    <row r="4" spans="2:4" ht="18.75" customHeight="1">
+      <c r="B4" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+    </row>
+    <row r="6" spans="2:4" ht="15.75" customHeight="1">
       <c r="B6" s="12" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
       <c r="B7" s="13" t="s">
         <v>14</v>
       </c>
@@ -3843,7 +3835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" s="14" t="s">
         <v>13</v>
       </c>
@@ -3851,7 +3843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" s="15" t="s">
         <v>22</v>
       </c>
@@ -3859,20 +3851,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4">
       <c r="B10" s="16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="56" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3887,7 +3879,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="8" width="14.7109375" customWidth="1"/>
@@ -3895,48 +3887,48 @@
     <col min="13" max="13" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:13" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
       <c r="M1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="8.1" customHeight="1">
       <c r="M2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+    <row r="3" spans="1:13" ht="26.1" customHeight="1">
+      <c r="A3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
       <c r="M3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="M4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
@@ -3953,37 +3945,37 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="51">
+    <row r="6" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A6" s="46">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*"))</f>
-        <v>66</v>
-      </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="53">
+        <v>65</v>
+      </c>
+      <c r="B6" s="54"/>
+      <c r="C6" s="48">
         <f ca="1">A6-E6-G6</f>
-        <v>52</v>
-      </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="52">
+        <v>48</v>
+      </c>
+      <c r="D6" s="54"/>
+      <c r="E6" s="47">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"In Progress"))</f>
         <v>4</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="47">
+      <c r="F6" s="54"/>
+      <c r="G6" s="43">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"Completed"))</f>
-        <v>10</v>
-      </c>
-      <c r="H6" s="48"/>
+        <v>13</v>
+      </c>
+      <c r="H6" s="54"/>
       <c r="M6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13">
       <c r="M7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
@@ -3994,44 +3986,44 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="50">
+    <row r="9" spans="1:13" ht="38.1" customHeight="1">
+      <c r="A9" s="45">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Amber"))</f>
         <v>4</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49">
+      <c r="B9" s="54"/>
+      <c r="C9" s="44">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Red"))</f>
         <v>2</v>
       </c>
-      <c r="D9" s="48"/>
+      <c r="D9" s="54"/>
       <c r="M9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13">
       <c r="M10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="9.9499999999999993" customHeight="1">
       <c r="M11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="44" t="s">
+    <row r="12" spans="1:13" ht="26.1" customHeight="1">
+      <c r="A12" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-    </row>
-    <row r="13" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+    </row>
+    <row r="13" spans="1:13" ht="30" customHeight="1">
       <c r="A13" s="27" t="s">
         <v>20</v>
       </c>
@@ -4060,7 +4052,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="24.95" customHeight="1">
       <c r="A14" s="23" t="s">
         <v>2</v>
       </c>
@@ -4094,10 +4086,10 @@
       </c>
       <c r="I14" s="29" t="str">
         <f ca="1">IF(MAX(Biology!D4:D1000)=0, "-", IF(MAX(Biology!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Biology!D4:D1000)=1, "Yesterday", TODAY()-MAX(Biology!D4:D1000) &amp; " days ago")))</f>
-        <v>Today</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="24.95" customHeight="1">
       <c r="A15" s="25" t="s">
         <v>4</v>
       </c>
@@ -4131,10 +4123,10 @@
       </c>
       <c r="I15" s="30" t="str">
         <f ca="1">IF(MAX(Chemistry!D4:D1000)=0, "N/A", IF(MAX(Chemistry!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Chemistry!D4:D1000)=1, "Yesterday", TODAY()-MAX(Chemistry!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2 days ago</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="24.95" customHeight="1">
       <c r="A16" s="23" t="s">
         <v>5</v>
       </c>
@@ -4144,7 +4136,7 @@
       </c>
       <c r="C16" s="24">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!B4:B1000"),"In Progress"))</f>
@@ -4152,11 +4144,11 @@
       </c>
       <c r="E16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!B4:B1000"),"Completed"))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Green"))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Amber"))</f>
@@ -4168,10 +4160,10 @@
       </c>
       <c r="I16" s="29" t="str">
         <f ca="1">IF(MAX(Physics!D4:D1000)=0, "-", IF(MAX(Physics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Physics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Physics!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="24.95" customHeight="1">
       <c r="A17" s="25" t="s">
         <v>10</v>
       </c>
@@ -4205,20 +4197,20 @@
       </c>
       <c r="I17" s="30" t="str">
         <f ca="1">IF(MAX(Mathematics!D4:D1000)=0, "-", IF(MAX(Mathematics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Mathematics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Mathematics!D4:D1000) &amp; " days ago")))</f>
-        <v>4 days ago</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="24.95" customHeight="1">
       <c r="A18" s="23" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*"))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="24">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!B4:B1000"),"In Progress"))</f>
@@ -4226,11 +4218,11 @@
       </c>
       <c r="E18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!B4:B1000"),"Completed"))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Green"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Amber"))</f>
@@ -4242,10 +4234,10 @@
       </c>
       <c r="I18" s="29" t="str">
         <f ca="1">IF(MAX('English Language'!D4:D1000)=0, "-", IF(MAX('English Language'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Language'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Language'!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Today</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="24.95" customHeight="1">
       <c r="A19" s="25" t="s">
         <v>12</v>
       </c>
@@ -4279,10 +4271,10 @@
       </c>
       <c r="I19" s="30" t="str">
         <f ca="1">IF(MAX('English Literature'!D4:D1000)=0, "-", IF(MAX('English Literature'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Literature'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Literature'!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="24.95" customHeight="1">
       <c r="A20" s="23" t="s">
         <v>15</v>
       </c>
@@ -4316,10 +4308,10 @@
       </c>
       <c r="I20" s="29" t="str">
         <f ca="1">IF(MAX(Geography!D4:D1000)=0, "-", IF(MAX(Geography!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Geography!D4:D1000)=1, "Yesterday", TODAY()-MAX(Geography!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2 days ago</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="24.95" customHeight="1">
       <c r="A21" s="25" t="s">
         <v>16</v>
       </c>
@@ -4353,10 +4345,10 @@
       </c>
       <c r="I21" s="30" t="str">
         <f ca="1">IF(MAX(History!D4:D1000)=0, "-", IF(MAX(History!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(History!D4:D1000)=1, "Yesterday", TODAY()-MAX(History!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Today</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="24.95" customHeight="1">
       <c r="A22" s="23" t="s">
         <v>17</v>
       </c>
@@ -4390,10 +4382,10 @@
       </c>
       <c r="I22" s="29" t="str">
         <f ca="1">IF(MAX(Spanish!D4:D1000)=0, "-", IF(MAX(Spanish!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Spanish!D4:D1000)=1, "Yesterday", TODAY()-MAX(Spanish!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3 days ago</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="24.95" customHeight="1">
       <c r="A23" s="25" t="s">
         <v>18</v>
       </c>
@@ -4427,68 +4419,68 @@
       </c>
       <c r="I23" s="30" t="str">
         <f ca="1">IF(MAX('Computer Science'!D4:D1000)=0, "-", IF(MAX('Computer Science'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('Computer Science'!D4:D1000)=1, "Yesterday", TODAY()-MAX('Computer Science'!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="44" t="s">
+        <v>2 days ago</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="18.75" customHeight="1">
+      <c r="A26" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="43"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="46" t="s">
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="46" t="s">
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="43"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="46" t="s">
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="46" t="s">
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -4508,202 +4500,202 @@
     <mergeCell ref="C6:D6"/>
   </mergeCells>
   <conditionalFormatting sqref="F14:F23">
-    <cfRule type="cellIs" dxfId="123" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="187" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:G23">
-    <cfRule type="cellIs" dxfId="122" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="186" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H23">
-    <cfRule type="cellIs" dxfId="121" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="185" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I23">
-    <cfRule type="cellIs" dxfId="120" priority="4" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="184" priority="4" stopIfTrue="1" operator="equal">
       <formula>"Today"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="5" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="183" priority="5" stopIfTrue="1" operator="equal">
       <formula>"Yesterday"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="6" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="182" priority="6" stopIfTrue="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="7" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="181" priority="7" stopIfTrue="1" operator="equal">
       <formula>"4 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="8" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="180" priority="8" stopIfTrue="1" operator="equal">
       <formula>"5 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="9" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="179" priority="9" stopIfTrue="1" operator="equal">
       <formula>"6 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="10" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="178" priority="10" stopIfTrue="1" operator="equal">
       <formula>"7 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="11" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="177" priority="11" stopIfTrue="1" operator="equal">
       <formula>"8 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="12" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="176" priority="12" stopIfTrue="1" operator="equal">
       <formula>"9 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="13" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="175" priority="13" stopIfTrue="1" operator="equal">
       <formula>"10 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="14" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="174" priority="14" stopIfTrue="1" operator="equal">
       <formula>"11 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="15" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="173" priority="15" stopIfTrue="1" operator="equal">
       <formula>"12 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="16" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="172" priority="16" stopIfTrue="1" operator="equal">
       <formula>"13 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="17" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="171" priority="17" stopIfTrue="1" operator="equal">
       <formula>"14 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="18" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="18" stopIfTrue="1" operator="equal">
       <formula>"15 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="19" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="169" priority="19" stopIfTrue="1" operator="equal">
       <formula>"16 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="20" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="20" stopIfTrue="1" operator="equal">
       <formula>"17 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="21" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="21" stopIfTrue="1" operator="equal">
       <formula>"18 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="22" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="166" priority="22" stopIfTrue="1" operator="equal">
       <formula>"19 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="23" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="23" stopIfTrue="1" operator="equal">
       <formula>"20 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="24" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="24" stopIfTrue="1" operator="equal">
       <formula>"21 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="25" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="163" priority="25" stopIfTrue="1" operator="equal">
       <formula>"22 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="26" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="26" stopIfTrue="1" operator="equal">
       <formula>"23 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="27" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="27" stopIfTrue="1" operator="equal">
       <formula>"24 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="28" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="160" priority="28" stopIfTrue="1" operator="equal">
       <formula>"25 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="29" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="29" stopIfTrue="1" operator="equal">
       <formula>"26 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="30" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="30" stopIfTrue="1" operator="equal">
       <formula>"27 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="31" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="157" priority="31" stopIfTrue="1" operator="equal">
       <formula>"28 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="32" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="156" priority="32" stopIfTrue="1" operator="equal">
       <formula>"29 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="33" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="155" priority="33" stopIfTrue="1" operator="equal">
       <formula>"30 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="34" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="34" stopIfTrue="1" operator="equal">
       <formula>"31 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="35" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="153" priority="35" stopIfTrue="1" operator="equal">
       <formula>"32 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="36" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="152" priority="36" stopIfTrue="1" operator="equal">
       <formula>"33 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="37" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="37" stopIfTrue="1" operator="equal">
       <formula>"34 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="38" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="150" priority="38" stopIfTrue="1" operator="equal">
       <formula>"35 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="39" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="149" priority="39" stopIfTrue="1" operator="equal">
       <formula>"36 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="40" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="40" stopIfTrue="1" operator="equal">
       <formula>"37 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="41" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="147" priority="41" stopIfTrue="1" operator="equal">
       <formula>"38 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="42" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="146" priority="42" stopIfTrue="1" operator="equal">
       <formula>"39 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="43" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="145" priority="43" stopIfTrue="1" operator="equal">
       <formula>"40 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="44" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="144" priority="44" stopIfTrue="1" operator="equal">
       <formula>"41 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="45" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="45" stopIfTrue="1" operator="equal">
       <formula>"42 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="46" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="46" stopIfTrue="1" operator="equal">
       <formula>"43 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="47" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="47" stopIfTrue="1" operator="equal">
       <formula>"44 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="48" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="48" stopIfTrue="1" operator="equal">
       <formula>"45 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="49" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="49" stopIfTrue="1" operator="equal">
       <formula>"46 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="50" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="50" stopIfTrue="1" operator="equal">
       <formula>"47 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="51" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="51" stopIfTrue="1" operator="equal">
       <formula>"48 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="52" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="52" stopIfTrue="1" operator="equal">
       <formula>"49 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="53" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="53" stopIfTrue="1" operator="equal">
       <formula>"50 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="54" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="54" stopIfTrue="1" operator="equal">
       <formula>"51 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="55" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="55" stopIfTrue="1" operator="equal">
       <formula>"52 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="56" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="56" stopIfTrue="1" operator="equal">
       <formula>"53 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="57" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="57" stopIfTrue="1" operator="equal">
       <formula>"54 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="58" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="58" stopIfTrue="1" operator="equal">
       <formula>"55 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="59" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="59" stopIfTrue="1" operator="equal">
       <formula>"56 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="60" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="60" stopIfTrue="1" operator="equal">
       <formula>"57 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="61" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="61" stopIfTrue="1" operator="equal">
       <formula>"58 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="62" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="62" stopIfTrue="1" operator="equal">
       <formula>"59 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="63" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="63" stopIfTrue="1" operator="equal">
       <formula>"2 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="64" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="64" stopIfTrue="1" operator="equal">
       <formula>"3 days ago"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4726,7 +4718,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.85546875" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4736,16 +4728,16 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A1" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="32" t="s">
         <v>30</v>
       </c>
@@ -4754,7 +4746,7 @@
       <c r="D2" s="17"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>31</v>
       </c>
@@ -4771,12 +4763,12 @@
         <v>34</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="99.75" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>9</v>
@@ -4788,13 +4780,13 @@
         <v>46313</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="39"/>
     </row>
-    <row r="5" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="71.25" customHeight="1">
       <c r="A5" s="35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>9</v>
@@ -4806,13 +4798,13 @@
         <v>46316</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="99" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -4820,9 +4812,9 @@
       <c r="E6" s="37"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="106.5" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -4830,9 +4822,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="108" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -4840,9 +4832,9 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="66" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -4850,9 +4842,9 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="75" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -4860,9 +4852,9 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="99" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -4870,7 +4862,7 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="45.75" customHeight="1">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -4878,7 +4870,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -4886,7 +4878,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -4894,7 +4886,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -4902,7 +4894,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -4910,7 +4902,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -4918,7 +4910,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -4926,7 +4918,7 @@
       <c r="E18" s="37"/>
       <c r="F18" s="38"/>
     </row>
-    <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="24" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -4934,7 +4926,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="24" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -4942,7 +4934,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="24" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -4950,7 +4942,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="24" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -4958,7 +4950,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="24" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -4966,7 +4958,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="24" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -4974,7 +4966,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="24" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -4982,7 +4974,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="24" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -4990,7 +4982,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="24" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -5003,24 +4995,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="56" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5048,7 +5040,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -5057,21 +5049,21 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A1" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="33" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
@@ -5088,12 +5080,12 @@
         <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="42.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -5105,25 +5097,25 @@
         <v>46315</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" s="39"/>
     </row>
-    <row r="5" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="84.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
       <c r="E5" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="35.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -5131,9 +5123,9 @@
       <c r="E6" s="41"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="39.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -5141,9 +5133,9 @@
       <c r="E7" s="41"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="37.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5151,9 +5143,9 @@
       <c r="E8" s="41"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="33" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -5161,9 +5153,9 @@
       <c r="E9" s="41"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="33" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -5171,9 +5163,9 @@
       <c r="E10" s="41"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="39" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -5181,9 +5173,9 @@
       <c r="E11" s="41"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="36.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -5191,9 +5183,9 @@
       <c r="E12" s="41"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -5201,7 +5193,7 @@
       <c r="E13" s="41"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -5209,7 +5201,7 @@
       <c r="E14" s="41"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5217,7 +5209,7 @@
       <c r="E15" s="41"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -5225,7 +5217,7 @@
       <c r="E16" s="41"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5233,7 +5225,7 @@
       <c r="E17" s="41"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -5246,24 +5238,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="53" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="50" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5291,7 +5283,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -5300,21 +5292,21 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A1" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
@@ -5331,12 +5323,12 @@
         <v>34</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="76.5" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>9</v>
@@ -5348,33 +5340,51 @@
         <v>46314</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="39"/>
-    </row>
-    <row r="5" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="50.25" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="37"/>
+        <v>63</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="11">
+        <v>46316</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>64</v>
+      </c>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="36.75" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="37"/>
+        <v>65</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="11">
+        <v>46316</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>64</v>
+      </c>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="37.5" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -5382,9 +5392,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="30" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -5392,9 +5402,9 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="37.5" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -5402,9 +5412,9 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="52.5" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -5412,9 +5422,9 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="35.25" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -5422,9 +5432,9 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="38.25" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -5432,9 +5442,9 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="30.75" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -5442,9 +5452,9 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="33.75" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -5452,7 +5462,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -5460,7 +5470,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -5468,7 +5478,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -5476,7 +5486,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -5489,24 +5499,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="47" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5534,31 +5544,31 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="20" style="19" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="55.7109375" customWidth="1"/>
+    <col min="6" max="6" width="73.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A1" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>31</v>
       </c>
@@ -5575,12 +5585,12 @@
         <v>34</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="130.5" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>8</v>
@@ -5589,14 +5599,16 @@
         <v>22</v>
       </c>
       <c r="D4" s="11">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="39"/>
-    </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="24" customHeight="1">
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -5604,7 +5616,7 @@
       <c r="E5" s="37"/>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="24" customHeight="1">
       <c r="A6" s="9"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -5612,7 +5624,7 @@
       <c r="E6" s="37"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="24" customHeight="1">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -5620,7 +5632,7 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="24" customHeight="1">
       <c r="A8" s="9"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -5628,7 +5640,7 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="24" customHeight="1">
       <c r="A9" s="9"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -5636,7 +5648,7 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="24" customHeight="1">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -5644,7 +5656,7 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="24" customHeight="1">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -5652,7 +5664,7 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="24" customHeight="1">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -5660,7 +5672,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -5668,7 +5680,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -5676,7 +5688,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -5684,7 +5696,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -5692,7 +5704,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -5700,7 +5712,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -5713,24 +5725,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="41" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5758,7 +5770,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
@@ -5768,21 +5780,21 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A1" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
@@ -5799,12 +5811,12 @@
         <v>34</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="85.5" customHeight="1">
       <c r="A4" s="35" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>9</v>
@@ -5816,23 +5828,31 @@
         <v>46315</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F4" s="39"/>
     </row>
-    <row r="5" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="74.25" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
+        <v>81</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="11">
+        <v>46317</v>
+      </c>
       <c r="E5" s="37"/>
-      <c r="F5" s="39"/>
-    </row>
-    <row r="6" spans="1:6" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="39" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="119.25" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>9</v>
@@ -5844,13 +5864,13 @@
         <v>46311</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="42.75" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>9</v>
@@ -5864,9 +5884,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="76.5" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>9</v>
@@ -5880,9 +5900,9 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="54.75" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -5890,9 +5910,9 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="62.25" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -5900,9 +5920,9 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="36" customHeight="1">
       <c r="A11" s="35" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -5910,9 +5930,9 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="39.75" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -5920,17 +5940,15 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>86</v>
-      </c>
+    <row r="13" spans="1:6" ht="42" customHeight="1">
+      <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="49.5" customHeight="1">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -5938,7 +5956,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -5946,7 +5964,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -5954,7 +5972,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -5962,7 +5980,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -5975,24 +5993,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="35" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6021,7 +6039,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -6030,21 +6048,21 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A1" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>31</v>
       </c>
@@ -6060,13 +6078,13 @@
       <c r="E3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="36" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="49.5" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -6074,9 +6092,9 @@
       <c r="E4" s="37"/>
       <c r="F4" s="39"/>
     </row>
-    <row r="5" spans="1:6" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="104.25" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>8</v>
@@ -6085,16 +6103,16 @@
         <v>14</v>
       </c>
       <c r="D5" s="22">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="41.25" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -6102,9 +6120,9 @@
       <c r="E6" s="37"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="71.25" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -6112,9 +6130,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="105.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -6122,9 +6140,9 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="48.75" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -6132,7 +6150,7 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="24" customHeight="1">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -6140,7 +6158,7 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="24" customHeight="1">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -6148,7 +6166,7 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="24" customHeight="1">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -6156,7 +6174,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -6164,7 +6182,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -6172,7 +6190,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -6180,7 +6198,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -6188,7 +6206,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -6196,7 +6214,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -6209,24 +6227,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6254,7 +6272,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -6263,21 +6281,21 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A1" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
@@ -6294,24 +6312,24 @@
         <v>34</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="24" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
       <c r="E4" s="37" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F4" s="39"/>
     </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="24" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -6319,9 +6337,9 @@
       <c r="E5" s="37"/>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="24" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -6329,9 +6347,9 @@
       <c r="E6" s="37"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="24" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -6339,9 +6357,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="154.5" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>9</v>
@@ -6353,11 +6371,11 @@
         <v>46315</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="24" customHeight="1">
       <c r="A9" s="9"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -6365,7 +6383,7 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="24" customHeight="1">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -6373,7 +6391,7 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="24" customHeight="1">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -6381,7 +6399,7 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="24" customHeight="1">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -6389,7 +6407,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -6397,7 +6415,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -6405,7 +6423,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -6413,7 +6431,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -6421,7 +6439,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -6429,7 +6447,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -6442,24 +6460,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6741,45 +6759,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2D1D04-17F3-4DB1-A413-D2712C8E335E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
-    <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2D1D04-17F3-4DB1-A413-D2712C8E335E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9169F2-DC6F-440D-AA51-2EA02192DC48}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9169F2-DC6F-440D-AA51-2EA02192DC48}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
-    <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}"/>
 </file>
--- a/revision tracker/Revision_Tracker.xlsx
+++ b/revision tracker/Revision_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sevenoaksschool-my.sharepoint.com/personal/chil03_sevenoaksschool_org/Documents/year 11/Revision Tracker/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/948b5d172b360b34/Python Stuff/revision tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{612638F8-D48E-420C-A662-1F27EDA1CCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="694" documentId="8_{44E14CDA-2C32-45B3-96A1-7C61FFBD3792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95403516-5279-4706-9A44-F53E00699725}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revision Timetable" sheetId="13" r:id="rId1"/>
@@ -30,7 +30,7 @@
   <definedNames>
     <definedName name="Subjects">Dashboard!$M$2:$M$11</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="150">
   <si>
     <t xml:space="preserve">  GCSE Revision Tracker — Dashboard</t>
   </si>
@@ -123,21 +123,6 @@
   </si>
   <si>
     <t>Last Revised</t>
-  </si>
-  <si>
-    <t>🧭  How to choose what to revise</t>
-  </si>
-  <si>
-    <t>•  Slots 1–3 of the day: your timetable tells you the subject. Open that subject tab and pick the topic.</t>
-  </si>
-  <si>
-    <t>•  Slot 4 (maintenance): use this Dashboard. Pick 3 subjects with Red/Amber/overdue topics, 15 min each.</t>
-  </si>
-  <si>
-    <t>•  Anything overdue? Do those first.  Then Red.  Then Amber.  Then oldest Last Revised.</t>
-  </si>
-  <si>
-    <t>•  A subject with lots of Red or Overdue = focus there. A subject with lots of Green = leave it longer.</t>
   </si>
   <si>
     <t xml:space="preserve">  Biology</t>
@@ -191,6 +176,9 @@
     <t>Alright we are done. First Bit of bio revision done :)</t>
   </si>
   <si>
+    <t>next up do a chatgpt go over of group 4 and group 7. Then do a chatgpt quiz</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -222,27 +210,28 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Group 3:</t>
+      <t xml:space="preserve">Group 3:
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">
-Transport in plants
+      <t>Transport in plants
 Nutrition in plants
 Gas exchange in plants
 Reproduction in plants</t>
     </r>
+  </si>
+  <si>
+    <t>Chill session. everything is chill</t>
   </si>
   <si>
     <r>
@@ -382,15 +371,19 @@
     <t>Complete</t>
   </si>
   <si>
+    <t>Next session you will complete inorganics part 2 and energetics</t>
+  </si>
+  <si>
     <t>Bonding  1f - 1h</t>
   </si>
   <si>
-    <t>1. Quick chatgpt go over on ionic, covalent and metallic bonding
-2. Do a ionic bonding PMT paper
-3. Do a covalent bonding PMT paper</t>
+    <t>SO easy very chill</t>
   </si>
   <si>
     <t>Inorganic Chem part 1 - 1a - 1d</t>
+  </si>
+  <si>
+    <t>calm. i know this stuff</t>
   </si>
   <si>
     <t>Inorganic Chem part 2 - 1e - 1g</t>
@@ -625,7 +618,8 @@
 3. Transition and change</t>
   </si>
   <si>
-    <t>finish the 2nd quotation for theme 1. Then do 2 quotations and anlysis for the other 2 themes. You really need to finish this topic in the next session spend an hour on this and just get it done.</t>
+    <t>finish the 2 quotations for transition and change 
+then start doing quotations for the characters</t>
   </si>
   <si>
     <t>Practise planning and writing essays for VFAB</t>
@@ -689,10 +683,13 @@
     <t>Do reading papers</t>
   </si>
   <si>
-    <t xml:space="preserve">Next session do this (should be a chill session):
-1. revise all tenses on thisisschool/conjugemos
-2. Keep on going with the reading paper, putting words you don't know in the quizlet
-3. In the last 10 mins do the quizlet. </t>
+    <t xml:space="preserve">Next session do this:
+1. finish reading paper while writing words we don't know in the quizlet
+2. at the end if time do the quizlet
+</t>
+  </si>
+  <si>
+    <t>After you finish that reading paper we are gonna do a writing paper and practise that.</t>
   </si>
   <si>
     <t>Do writing papers</t>
@@ -750,6 +747,54 @@
   </si>
   <si>
     <t>Edit the interval numbers in column C to change how often topics come back.</t>
+  </si>
+  <si>
+    <t>🗓️ Week 1 Timetable</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Session 1</t>
+  </si>
+  <si>
+    <t>Session 2</t>
+  </si>
+  <si>
+    <t>Session 3</t>
+  </si>
+  <si>
+    <t>Session 4</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>🗓️ Week 2 Timetable</t>
+  </si>
+  <si>
+    <t>🎯 Today's Focus</t>
   </si>
 </sst>
 </file>
@@ -759,7 +804,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,11 +863,6 @@
       <b/>
       <sz val="20"/>
       <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -934,8 +974,51 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1011,8 +1094,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F8FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1119,13 +1208,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDCDCDC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDCDCDC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1139,7 +1246,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1185,75 +1292,102 @@
     <xf numFmtId="14" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1275,53 +1409,18 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent5" xfId="2" builtinId="45"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="188">
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="190">
     <dxf>
       <font>
         <b/>
@@ -1384,9 +1483,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1448,9 +1544,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1512,28 +1605,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1595,37 +1666,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1687,28 +1727,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1770,37 +1788,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1862,28 +1849,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -1945,9 +1910,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -2009,37 +1971,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color rgb="FF9C0006"/>
@@ -2103,7 +2034,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2117,7 +2055,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2509,21 +2447,14 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFEBEBEB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2547,6 +2478,227 @@
           <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF86BC71"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF960000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2561,127 +2713,31 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDADD0AC-2F70-A95A-D139-C9C6B5368DDB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="561975" y="666750"/>
-          <a:ext cx="4572000" cy="2495550"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68536825-6B37-718E-E7FB-45ECF5C3C8CC}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EDADD0AC-2F70-A95A-D139-C9C6B5368DDB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="3810000"/>
-          <a:ext cx="4572000" cy="2476500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:F27" headerRowDxfId="117" dataDxfId="116" totalsRowDxfId="115">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:F27" headerRowDxfId="189" dataDxfId="188" totalsRowDxfId="187">
   <autoFilter ref="A3:F27" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="114"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="113"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="112"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="110"/>
-    <tableColumn id="5" xr3:uid="{F0BDA802-DA31-4BA7-81BA-FDB612DC37E1}" name="General Notes" dataDxfId="108" totalsRowDxfId="109"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="186"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="185"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="184"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="183"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="182"/>
+    <tableColumn id="5" xr3:uid="{F0BDA802-DA31-4BA7-81BA-FDB612DC37E1}" name="General Notes" dataDxfId="181" totalsRowDxfId="180"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="ComputerScienceTbl" displayName="ComputerScienceTbl" ref="A3:F18" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="ComputerScienceTbl" displayName="ComputerScienceTbl" ref="A3:F18" headerRowDxfId="135" dataDxfId="134" totalsRowDxfId="133">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Topic" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Status" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Confidence" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Last Revised" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Next Action" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{63D6C4F6-C7E6-4663-AE70-5CFDFF770C29}" name="General Notes" dataDxfId="0" totalsRowDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Topic" dataDxfId="132"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Status" dataDxfId="131"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Confidence" dataDxfId="130"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Last Revised" dataDxfId="129"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Next Action" dataDxfId="128"/>
+    <tableColumn id="5" xr3:uid="{63D6C4F6-C7E6-4663-AE70-5CFDFF770C29}" name="General Notes" dataDxfId="127" totalsRowDxfId="126"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2694,7 +2750,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="101"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="179"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{DB8974C0-4423-4F62-8CA0-D4A3FA4693EA}" name="General Notes"/>
   </tableColumns>
@@ -2703,75 +2759,75 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PhysicsTbl" displayName="PhysicsTbl" ref="A3:F18" dataDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PhysicsTbl" displayName="PhysicsTbl" ref="A3:F18" dataDxfId="178">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Topic" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Status" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Confidence" dataDxfId="91"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Last Revised" dataDxfId="90"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Next Action" dataDxfId="89"/>
-    <tableColumn id="5" xr3:uid="{2C5860E0-C42D-447A-99E8-019207F1E49B}" name="General Notes" dataDxfId="88"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Topic" dataDxfId="177"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Status" dataDxfId="176"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Confidence" dataDxfId="175"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Last Revised" dataDxfId="174"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Next Action" dataDxfId="173"/>
+    <tableColumn id="5" xr3:uid="{2C5860E0-C42D-447A-99E8-019207F1E49B}" name="General Notes" dataDxfId="172"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="MathematicsTbl" displayName="MathematicsTbl" ref="A3:F18" headerRowDxfId="81" dataDxfId="80" totalsRowDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="MathematicsTbl" displayName="MathematicsTbl" ref="A3:F18" headerRowDxfId="171" dataDxfId="170" totalsRowDxfId="169">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Topic" dataDxfId="78"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status" dataDxfId="77"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Confidence" dataDxfId="76"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Last Revised" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Next Action" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{902E25C2-558C-4568-81EE-02B6DDE3EEEE}" name="General Notes" dataDxfId="72" totalsRowDxfId="73"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Topic" dataDxfId="168"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status" dataDxfId="167"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Confidence" dataDxfId="166"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Last Revised" dataDxfId="165"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Next Action" dataDxfId="164"/>
+    <tableColumn id="5" xr3:uid="{902E25C2-558C-4568-81EE-02B6DDE3EEEE}" name="General Notes" dataDxfId="163" totalsRowDxfId="162"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EnglishLanguageTbl" displayName="EnglishLanguageTbl" ref="A3:F18" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EnglishLanguageTbl" displayName="EnglishLanguageTbl" ref="A3:F18" dataDxfId="161">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Topic" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Status" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Confidence" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Last Revised" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Next Action" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{75D1410F-47BB-4A48-905A-25CF74BDB786}" name="General Notes" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Topic" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Status" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Confidence" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Last Revised" dataDxfId="157"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Next Action" dataDxfId="156"/>
+    <tableColumn id="5" xr3:uid="{75D1410F-47BB-4A48-905A-25CF74BDB786}" name="General Notes" dataDxfId="155"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="EnglishLiteratureTbl" displayName="EnglishLiteratureTbl" ref="A3:F18" headerRowDxfId="52" dataDxfId="51" totalsRowDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="EnglishLiteratureTbl" displayName="EnglishLiteratureTbl" ref="A3:F18" headerRowDxfId="154" dataDxfId="153" totalsRowDxfId="152">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Topic" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Status" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Confidence" dataDxfId="47"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Last Revised" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Next Action" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{930CE764-AB02-4790-8724-F5622F11644B}" name="General Notes" dataDxfId="43" totalsRowDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Topic" dataDxfId="151"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Status" dataDxfId="150"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Confidence" dataDxfId="149"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Last Revised" dataDxfId="148"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Next Action" dataDxfId="147"/>
+    <tableColumn id="5" xr3:uid="{930CE764-AB02-4790-8724-F5622F11644B}" name="General Notes" dataDxfId="146" totalsRowDxfId="145"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="GeographyTbl" displayName="GeographyTbl" ref="A3:F18" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="GeographyTbl" displayName="GeographyTbl" ref="A3:F18" dataDxfId="144">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Topic" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Status" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Confidence" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Last Revised" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Next Action" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{27D2B179-C2A7-46A7-8BEB-752BF05A8E89}" name="General Notes" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Topic" dataDxfId="143"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Status" dataDxfId="142"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Confidence" dataDxfId="141"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Last Revised" dataDxfId="140"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Next Action" dataDxfId="139"/>
+    <tableColumn id="5" xr3:uid="{27D2B179-C2A7-46A7-8BEB-752BF05A8E89}" name="General Notes" dataDxfId="138"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2784,7 +2840,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Last Revised" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Last Revised" dataDxfId="137"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{28A5B818-9271-4E86-B3A0-50B7055F910C}" name="General Notes"/>
   </tableColumns>
@@ -2799,7 +2855,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Last Revised" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Last Revised" dataDxfId="136"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{7C8E7108-0749-49A2-855D-B734764E8E58}" name="General Notes"/>
   </tableColumns>
@@ -3092,18 +3148,286 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669FF182-A9DF-49CA-A197-60E29E93D9CE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+    <col min="7" max="11" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="J2" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="K2" s="43" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="44" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="H6" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="45" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="H8" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="K8" s="45" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="K9" s="44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -3112,43 +3436,43 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="115.5" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
@@ -3160,13 +3484,13 @@
         <v>46317</v>
       </c>
       <c r="E4" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="39"/>
+    </row>
+    <row r="5" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="F4" s="39"/>
-    </row>
-    <row r="5" spans="1:6" ht="42.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3174,9 +3498,9 @@
       <c r="E5" s="41"/>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="45.75" customHeight="1">
+    <row r="6" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3184,7 +3508,7 @@
       <c r="E6" s="41"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1">
+    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -3192,7 +3516,7 @@
       <c r="E7" s="41"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1">
+    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -3200,7 +3524,7 @@
       <c r="E8" s="41"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1">
+    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -3208,7 +3532,7 @@
       <c r="E9" s="41"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1">
+    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -3216,7 +3540,7 @@
       <c r="E10" s="41"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1">
+    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -3224,7 +3548,7 @@
       <c r="E11" s="41"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1">
+    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3232,7 +3556,7 @@
       <c r="E12" s="41"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1">
+    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3240,7 +3564,7 @@
       <c r="E13" s="41"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1">
+    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -3248,7 +3572,7 @@
       <c r="E14" s="41"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -3256,7 +3580,7 @@
       <c r="E15" s="41"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -3264,7 +3588,7 @@
       <c r="E16" s="41"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3272,7 +3596,7 @@
       <c r="E17" s="41"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -3285,24 +3609,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3330,7 +3654,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -3340,43 +3664,43 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="64" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="113.25" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
@@ -3385,14 +3709,16 @@
         <v>22</v>
       </c>
       <c r="D4" s="4">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="E4" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="F4" s="39"/>
-    </row>
-    <row r="5" spans="1:6" ht="45" customHeight="1">
+    </row>
+    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>115</v>
       </c>
@@ -3402,7 +3728,7 @@
       <c r="E5" s="41"/>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="37.5" customHeight="1">
+    <row r="6" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>116</v>
       </c>
@@ -3412,7 +3738,7 @@
       <c r="E6" s="41"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="40.5" customHeight="1">
+    <row r="7" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>117</v>
       </c>
@@ -3422,7 +3748,7 @@
       <c r="E7" s="41"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1">
+    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -3430,7 +3756,7 @@
       <c r="E8" s="41"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1">
+    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -3438,7 +3764,7 @@
       <c r="E9" s="41"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1">
+    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -3446,7 +3772,7 @@
       <c r="E10" s="41"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1">
+    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -3454,7 +3780,7 @@
       <c r="E11" s="41"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1">
+    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3462,7 +3788,7 @@
       <c r="E12" s="41"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1">
+    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3470,7 +3796,7 @@
       <c r="E13" s="41"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1">
+    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -3478,7 +3804,7 @@
       <c r="E14" s="41"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -3486,7 +3812,7 @@
       <c r="E15" s="41"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -3494,7 +3820,7 @@
       <c r="E16" s="41"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3502,7 +3828,7 @@
       <c r="E17" s="41"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -3515,24 +3841,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3560,7 +3886,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -3569,41 +3895,41 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="44.25" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>119</v>
       </c>
@@ -3613,7 +3939,7 @@
       <c r="E4" s="37"/>
       <c r="F4" s="39"/>
     </row>
-    <row r="5" spans="1:6" ht="43.5" customHeight="1">
+    <row r="5" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>120</v>
       </c>
@@ -3623,7 +3949,7 @@
       <c r="E5" s="37"/>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="48.75" customHeight="1">
+    <row r="6" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>121</v>
       </c>
@@ -3633,7 +3959,7 @@
       <c r="E6" s="37"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="45.75" customHeight="1">
+    <row r="7" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>122</v>
       </c>
@@ -3643,7 +3969,7 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="57" customHeight="1">
+    <row r="8" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>123</v>
       </c>
@@ -3653,7 +3979,7 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="90.75" customHeight="1">
+    <row r="9" spans="1:6" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>124</v>
       </c>
@@ -3671,7 +3997,7 @@
       </c>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="42" customHeight="1">
+    <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>126</v>
       </c>
@@ -3681,7 +4007,7 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="43.5" customHeight="1">
+    <row r="11" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>127</v>
       </c>
@@ -3691,7 +4017,7 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1">
+    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -3699,7 +4025,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1">
+    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -3707,7 +4033,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1">
+    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -3715,7 +4041,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -3723,7 +4049,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -3731,7 +4057,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -3739,7 +4065,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -3752,24 +4078,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3797,7 +4123,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B2:D12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -3805,29 +4131,29 @@
     <col min="4" max="4" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="28.5" customHeight="1">
-      <c r="B2" s="56" t="s">
+    <row r="2" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="66" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-    </row>
-    <row r="4" spans="2:4" ht="18.75" customHeight="1">
-      <c r="B4" s="53" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+    </row>
+    <row r="4" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-    </row>
-    <row r="6" spans="2:4" ht="15.75" customHeight="1">
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+    </row>
+    <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
         <v>14</v>
       </c>
@@ -3835,7 +4161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
         <v>13</v>
       </c>
@@ -3843,7 +4169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="15" t="s">
         <v>22</v>
       </c>
@@ -3851,7 +4177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
         <v>131</v>
       </c>
@@ -3859,12 +4185,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
-      <c r="B12" s="57" t="s">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="65" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3878,57 +4204,58 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AC28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="8" width="14.7109375" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="13" max="13" width="13" hidden="1" customWidth="1"/>
+    <col min="26" max="29" width="2.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
       <c r="M1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="8.1" customHeight="1">
+    <row r="2" spans="1:13" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="26.1" customHeight="1">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
       <c r="M3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
@@ -3945,37 +4272,37 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A6" s="46">
+    <row r="6" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="59">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*"))</f>
         <v>65</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="48">
+      <c r="B6" s="56"/>
+      <c r="C6" s="61">
         <f ca="1">A6-E6-G6</f>
-        <v>48</v>
-      </c>
-      <c r="D6" s="54"/>
-      <c r="E6" s="47">
+        <v>45</v>
+      </c>
+      <c r="D6" s="56"/>
+      <c r="E6" s="60">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"In Progress"))</f>
         <v>4</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="43">
+      <c r="F6" s="56"/>
+      <c r="G6" s="55">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"Completed"))</f>
-        <v>13</v>
-      </c>
-      <c r="H6" s="54"/>
+        <v>16</v>
+      </c>
+      <c r="H6" s="56"/>
       <c r="M6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
@@ -3986,44 +4313,44 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="38.1" customHeight="1">
-      <c r="A9" s="45">
+    <row r="9" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="58">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Amber"))</f>
-        <v>4</v>
-      </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="44">
+        <v>5</v>
+      </c>
+      <c r="B9" s="56"/>
+      <c r="C9" s="57">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Red"))</f>
-        <v>2</v>
-      </c>
-      <c r="D9" s="54"/>
+        <v>1</v>
+      </c>
+      <c r="D9" s="56"/>
       <c r="M9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="9.9499999999999993" customHeight="1">
+    <row r="11" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="26.1" customHeight="1">
-      <c r="A12" s="53" t="s">
+    <row r="12" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-    </row>
-    <row r="13" spans="1:13" ht="30" customHeight="1">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+    </row>
+    <row r="13" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>20</v>
       </c>
@@ -4052,7 +4379,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="24.95" customHeight="1">
+    <row r="14" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
         <v>2</v>
       </c>
@@ -4062,7 +4389,7 @@
       </c>
       <c r="C14" s="24">
         <f t="shared" ref="C14:C23" ca="1" si="0">B14-D14-E14</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!B4:B1000"),"In Progress"))</f>
@@ -4070,11 +4397,11 @@
       </c>
       <c r="E14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!B4:B1000"),"Completed"))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Green"))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Amber"))</f>
@@ -4089,7 +4416,7 @@
         <v>Yesterday</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="24.95" customHeight="1">
+    <row r="15" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>4</v>
       </c>
@@ -4099,7 +4426,7 @@
       </c>
       <c r="C15" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!B4:B1000"),"In Progress"))</f>
@@ -4107,11 +4434,11 @@
       </c>
       <c r="E15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!B4:B1000"),"Completed"))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Green"))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Amber"))</f>
@@ -4123,10 +4450,10 @@
       </c>
       <c r="I15" s="30" t="str">
         <f ca="1">IF(MAX(Chemistry!D4:D1000)=0, "N/A", IF(MAX(Chemistry!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Chemistry!D4:D1000)=1, "Yesterday", TODAY()-MAX(Chemistry!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="24.95" customHeight="1">
+        <v>Today</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
         <v>5</v>
       </c>
@@ -4160,10 +4487,10 @@
       </c>
       <c r="I16" s="29" t="str">
         <f ca="1">IF(MAX(Physics!D4:D1000)=0, "-", IF(MAX(Physics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Physics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Physics!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="24.95" customHeight="1">
+        <v>2 days ago</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>10</v>
       </c>
@@ -4197,10 +4524,10 @@
       </c>
       <c r="I17" s="30" t="str">
         <f ca="1">IF(MAX(Mathematics!D4:D1000)=0, "-", IF(MAX(Mathematics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Mathematics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Mathematics!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="24.95" customHeight="1">
+        <v>2 days ago</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
         <v>11</v>
       </c>
@@ -4234,10 +4561,10 @@
       </c>
       <c r="I18" s="29" t="str">
         <f ca="1">IF(MAX('English Language'!D4:D1000)=0, "-", IF(MAX('English Language'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Language'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Language'!D4:D1000) &amp; " days ago")))</f>
-        <v>Today</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="24.95" customHeight="1">
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>12</v>
       </c>
@@ -4263,18 +4590,18 @@
       </c>
       <c r="G19" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Amber"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Red"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="30" t="str">
         <f ca="1">IF(MAX('English Literature'!D4:D1000)=0, "-", IF(MAX('English Literature'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Literature'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Literature'!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="24.95" customHeight="1">
+        <v>Today</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
         <v>15</v>
       </c>
@@ -4308,10 +4635,10 @@
       </c>
       <c r="I20" s="29" t="str">
         <f ca="1">IF(MAX(Geography!D4:D1000)=0, "-", IF(MAX(Geography!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Geography!D4:D1000)=1, "Yesterday", TODAY()-MAX(Geography!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="24.95" customHeight="1">
+        <v>3 days ago</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>16</v>
       </c>
@@ -4345,10 +4672,10 @@
       </c>
       <c r="I21" s="30" t="str">
         <f ca="1">IF(MAX(History!D4:D1000)=0, "-", IF(MAX(History!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(History!D4:D1000)=1, "Yesterday", TODAY()-MAX(History!D4:D1000) &amp; " days ago")))</f>
-        <v>Today</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="24.95" customHeight="1">
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
         <v>17</v>
       </c>
@@ -4382,10 +4709,10 @@
       </c>
       <c r="I22" s="29" t="str">
         <f ca="1">IF(MAX(Spanish!D4:D1000)=0, "-", IF(MAX(Spanish!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Spanish!D4:D1000)=1, "Yesterday", TODAY()-MAX(Spanish!D4:D1000) &amp; " days ago")))</f>
-        <v>3 days ago</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="24.95" customHeight="1">
+        <v>Yesterday</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
         <v>18</v>
       </c>
@@ -4419,284 +4746,314 @@
       </c>
       <c r="I23" s="30" t="str">
         <f ca="1">IF(MAX('Computer Science'!D4:D1000)=0, "-", IF(MAX('Computer Science'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('Computer Science'!D4:D1000)=1, "Yesterday", TODAY()-MAX('Computer Science'!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A26" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="55" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
+        <v>3 days ago</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="42" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" s="48"/>
+    </row>
+    <row r="27" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="49" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)), "-")</f>
+        <v>Chemistry</v>
+      </c>
+      <c r="B27" s="51"/>
+      <c r="C27" s="49" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)), "-")</f>
+        <v>English Literature</v>
+      </c>
+      <c r="D27" s="51"/>
+      <c r="E27" s="49" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)), "-")</f>
+        <v>Computer Science</v>
+      </c>
+      <c r="F27" s="51"/>
+      <c r="G27" s="49" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)), "-")</f>
+        <v>Geography</v>
+      </c>
+      <c r="H27" s="50"/>
+      <c r="Z27" s="46" t="b">
+        <f ca="1">IFERROR(VLOOKUP(A27, $A$13:$I$23, 9, FALSE)="Today", FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="AA27" s="46" t="b">
+        <f ca="1">IFERROR(VLOOKUP(C27, $A$13:$I$23, 9, FALSE)="Today", FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="AB27" s="46" t="b">
+        <f ca="1">IFERROR(VLOOKUP(E27, $A$13:$I$23, 9, FALSE)="Today", FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="AC27" s="46" t="b">
+        <f ca="1">IFERROR(VLOOKUP(G27, $A$13:$I$23, 9, FALSE)="Today", FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A28" s="47" t="str">
+        <f ca="1">IF(COUNTIFS($A$13:$A$23, A27, $I$13:$I$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
+        <v>DONE</v>
+      </c>
+      <c r="C28" s="47" t="str">
+        <f ca="1">IF(COUNTIFS($A$13:$A$23, C27, $I$13:$I$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
+        <v>DONE</v>
+      </c>
+      <c r="E28" s="47" t="str">
+        <f ca="1">IF(COUNTIFS($A$13:$A$23, E27, $I$13:$I$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
+        <v>NOT DONE</v>
+      </c>
+      <c r="G28" s="47" t="str">
+        <f ca="1">IF(COUNTIFS($A$13:$A$23, G27, $I$13:$I$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
+        <v>NOT DONE</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="17">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A28:H28"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
   </mergeCells>
+  <conditionalFormatting sqref="A27:H27">
+    <cfRule type="cellIs" dxfId="125" priority="71" stopIfTrue="1" operator="equal">
+      <formula>"""NOT DONE"""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="72" stopIfTrue="1" operator="equal">
+      <formula>"""DONE"""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F14:F23">
-    <cfRule type="cellIs" dxfId="187" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="123" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:G23">
-    <cfRule type="cellIs" dxfId="186" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="122" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H23">
-    <cfRule type="cellIs" dxfId="185" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="121" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:I23">
-    <cfRule type="cellIs" dxfId="184" priority="4" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="6" stopIfTrue="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="119" priority="7" stopIfTrue="1" operator="equal">
+      <formula>"4 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="8" stopIfTrue="1" operator="equal">
+      <formula>"5 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="9" stopIfTrue="1" operator="equal">
+      <formula>"6 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="116" priority="10" stopIfTrue="1" operator="equal">
+      <formula>"7 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="11" stopIfTrue="1" operator="equal">
+      <formula>"8 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="12" stopIfTrue="1" operator="equal">
+      <formula>"9 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="113" priority="13" stopIfTrue="1" operator="equal">
+      <formula>"10 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="14" stopIfTrue="1" operator="equal">
+      <formula>"11 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="15" stopIfTrue="1" operator="equal">
+      <formula>"12 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="110" priority="16" stopIfTrue="1" operator="equal">
+      <formula>"13 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="17" stopIfTrue="1" operator="equal">
+      <formula>"14 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="18" stopIfTrue="1" operator="equal">
+      <formula>"15 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="107" priority="19" stopIfTrue="1" operator="equal">
+      <formula>"16 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="20" stopIfTrue="1" operator="equal">
+      <formula>"17 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="21" stopIfTrue="1" operator="equal">
+      <formula>"18 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="22" stopIfTrue="1" operator="equal">
+      <formula>"19 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="23" stopIfTrue="1" operator="equal">
+      <formula>"20 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="24" stopIfTrue="1" operator="equal">
+      <formula>"21 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="101" priority="25" stopIfTrue="1" operator="equal">
+      <formula>"22 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="26" stopIfTrue="1" operator="equal">
+      <formula>"23 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="27" stopIfTrue="1" operator="equal">
+      <formula>"24 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="28" stopIfTrue="1" operator="equal">
+      <formula>"25 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="29" stopIfTrue="1" operator="equal">
+      <formula>"26 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="30" stopIfTrue="1" operator="equal">
+      <formula>"27 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="95" priority="31" stopIfTrue="1" operator="equal">
+      <formula>"28 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="32" stopIfTrue="1" operator="equal">
+      <formula>"29 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="33" stopIfTrue="1" operator="equal">
+      <formula>"30 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="92" priority="34" stopIfTrue="1" operator="equal">
+      <formula>"31 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="35" stopIfTrue="1" operator="equal">
+      <formula>"32 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="36" stopIfTrue="1" operator="equal">
+      <formula>"33 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="89" priority="37" stopIfTrue="1" operator="equal">
+      <formula>"34 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="38" stopIfTrue="1" operator="equal">
+      <formula>"35 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="39" stopIfTrue="1" operator="equal">
+      <formula>"36 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="86" priority="40" stopIfTrue="1" operator="equal">
+      <formula>"37 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="41" stopIfTrue="1" operator="equal">
+      <formula>"38 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="42" stopIfTrue="1" operator="equal">
+      <formula>"39 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="43" stopIfTrue="1" operator="equal">
+      <formula>"40 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="44" stopIfTrue="1" operator="equal">
+      <formula>"41 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="45" stopIfTrue="1" operator="equal">
+      <formula>"42 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="46" stopIfTrue="1" operator="equal">
+      <formula>"43 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="47" stopIfTrue="1" operator="equal">
+      <formula>"44 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="48" stopIfTrue="1" operator="equal">
+      <formula>"45 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="77" priority="49" stopIfTrue="1" operator="equal">
+      <formula>"46 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="50" stopIfTrue="1" operator="equal">
+      <formula>"47 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="51" stopIfTrue="1" operator="equal">
+      <formula>"48 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="52" stopIfTrue="1" operator="equal">
+      <formula>"49 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="53" stopIfTrue="1" operator="equal">
+      <formula>"50 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="54" stopIfTrue="1" operator="equal">
+      <formula>"51 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="55" stopIfTrue="1" operator="equal">
+      <formula>"52 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="56" stopIfTrue="1" operator="equal">
+      <formula>"53 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="57" stopIfTrue="1" operator="equal">
+      <formula>"54 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="68" priority="58" stopIfTrue="1" operator="equal">
+      <formula>"55 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="59" stopIfTrue="1" operator="equal">
+      <formula>"56 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="60" stopIfTrue="1" operator="equal">
+      <formula>"57 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="61" stopIfTrue="1" operator="equal">
+      <formula>"58 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="62" stopIfTrue="1" operator="equal">
+      <formula>"59 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="63" stopIfTrue="1" operator="equal">
+      <formula>"2 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="64" stopIfTrue="1" operator="equal">
+      <formula>"3 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="4" stopIfTrue="1" operator="equal">
       <formula>"Today"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="5" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="5" stopIfTrue="1" operator="equal">
       <formula>"Yesterday"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="182" priority="6" stopIfTrue="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="7" stopIfTrue="1" operator="equal">
-      <formula>"4 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="8" stopIfTrue="1" operator="equal">
-      <formula>"5 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="9" stopIfTrue="1" operator="equal">
-      <formula>"6 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="10" stopIfTrue="1" operator="equal">
-      <formula>"7 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="11" stopIfTrue="1" operator="equal">
-      <formula>"8 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="176" priority="12" stopIfTrue="1" operator="equal">
-      <formula>"9 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="13" stopIfTrue="1" operator="equal">
-      <formula>"10 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="14" stopIfTrue="1" operator="equal">
-      <formula>"11 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="15" stopIfTrue="1" operator="equal">
-      <formula>"12 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="16" stopIfTrue="1" operator="equal">
-      <formula>"13 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="17" stopIfTrue="1" operator="equal">
-      <formula>"14 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="170" priority="18" stopIfTrue="1" operator="equal">
-      <formula>"15 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="19" stopIfTrue="1" operator="equal">
-      <formula>"16 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="20" stopIfTrue="1" operator="equal">
-      <formula>"17 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="167" priority="21" stopIfTrue="1" operator="equal">
-      <formula>"18 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="22" stopIfTrue="1" operator="equal">
-      <formula>"19 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="23" stopIfTrue="1" operator="equal">
-      <formula>"20 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="24" stopIfTrue="1" operator="equal">
-      <formula>"21 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="25" stopIfTrue="1" operator="equal">
-      <formula>"22 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="26" stopIfTrue="1" operator="equal">
-      <formula>"23 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="27" stopIfTrue="1" operator="equal">
-      <formula>"24 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="28" stopIfTrue="1" operator="equal">
-      <formula>"25 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="29" stopIfTrue="1" operator="equal">
-      <formula>"26 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="30" stopIfTrue="1" operator="equal">
-      <formula>"27 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="31" stopIfTrue="1" operator="equal">
-      <formula>"28 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="32" stopIfTrue="1" operator="equal">
-      <formula>"29 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="33" stopIfTrue="1" operator="equal">
-      <formula>"30 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="34" stopIfTrue="1" operator="equal">
-      <formula>"31 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="35" stopIfTrue="1" operator="equal">
-      <formula>"32 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="36" stopIfTrue="1" operator="equal">
-      <formula>"33 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="37" stopIfTrue="1" operator="equal">
-      <formula>"34 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="38" stopIfTrue="1" operator="equal">
-      <formula>"35 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="39" stopIfTrue="1" operator="equal">
-      <formula>"36 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="40" stopIfTrue="1" operator="equal">
-      <formula>"37 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="41" stopIfTrue="1" operator="equal">
-      <formula>"38 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="42" stopIfTrue="1" operator="equal">
-      <formula>"39 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="43" stopIfTrue="1" operator="equal">
-      <formula>"40 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="44" stopIfTrue="1" operator="equal">
-      <formula>"41 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="45" stopIfTrue="1" operator="equal">
-      <formula>"42 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="46" stopIfTrue="1" operator="equal">
-      <formula>"43 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="47" stopIfTrue="1" operator="equal">
-      <formula>"44 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="48" stopIfTrue="1" operator="equal">
-      <formula>"45 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="49" stopIfTrue="1" operator="equal">
-      <formula>"46 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="50" stopIfTrue="1" operator="equal">
-      <formula>"47 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="51" stopIfTrue="1" operator="equal">
-      <formula>"48 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="52" stopIfTrue="1" operator="equal">
-      <formula>"49 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="53" stopIfTrue="1" operator="equal">
-      <formula>"50 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="134" priority="54" stopIfTrue="1" operator="equal">
-      <formula>"51 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="55" stopIfTrue="1" operator="equal">
-      <formula>"52 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="56" stopIfTrue="1" operator="equal">
-      <formula>"53 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="57" stopIfTrue="1" operator="equal">
-      <formula>"54 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="58" stopIfTrue="1" operator="equal">
-      <formula>"55 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="59" stopIfTrue="1" operator="equal">
-      <formula>"56 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="60" stopIfTrue="1" operator="equal">
-      <formula>"57 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="61" stopIfTrue="1" operator="equal">
-      <formula>"58 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="62" stopIfTrue="1" operator="equal">
-      <formula>"59 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="63" stopIfTrue="1" operator="equal">
-      <formula>"2 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="64" stopIfTrue="1" operator="equal">
-      <formula>"3 days ago"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -4718,7 +5075,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.85546875" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4728,47 +5085,47 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="17"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="99.75" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>9</v>
@@ -4780,13 +5137,15 @@
         <v>46313</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="39"/>
-    </row>
-    <row r="5" spans="1:6" ht="71.25" customHeight="1">
+        <v>32</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>9</v>
@@ -4798,23 +5157,31 @@
         <v>46316</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="99" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="37"/>
+    <row r="6" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="11">
+        <v>46317</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>37</v>
+      </c>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="106.5" customHeight="1">
+    <row r="7" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -4822,9 +5189,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="108" customHeight="1">
+    <row r="8" spans="1:6" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -4832,9 +5199,9 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="66" customHeight="1">
+    <row r="9" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -4842,9 +5209,9 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="75" customHeight="1">
+    <row r="10" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -4852,9 +5219,9 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="99" customHeight="1">
+    <row r="11" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -4862,7 +5229,7 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="45.75" customHeight="1">
+    <row r="12" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -4870,7 +5237,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1">
+    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -4878,7 +5245,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1">
+    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -4886,7 +5253,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -4894,7 +5261,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -4902,7 +5269,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -4910,7 +5277,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -4918,7 +5285,7 @@
       <c r="E18" s="37"/>
       <c r="F18" s="38"/>
     </row>
-    <row r="19" spans="1:6" ht="24" customHeight="1">
+    <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -4926,7 +5293,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="24" customHeight="1">
+    <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -4934,7 +5301,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="24" customHeight="1">
+    <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -4942,7 +5309,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="24" customHeight="1">
+    <row r="22" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -4950,7 +5317,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" ht="24" customHeight="1">
+    <row r="23" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -4958,7 +5325,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" ht="24" customHeight="1">
+    <row r="24" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -4966,7 +5333,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="24" customHeight="1">
+    <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -4974,7 +5341,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" ht="24" customHeight="1">
+    <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -4982,7 +5349,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" ht="24" customHeight="1">
+    <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -4995,24 +5362,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="123" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="120" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5040,7 +5407,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -5049,43 +5416,43 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="42.75" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -5097,35 +5464,51 @@
         <v>46315</v>
       </c>
       <c r="E4" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46318</v>
+      </c>
+      <c r="E5" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="39"/>
-    </row>
-    <row r="5" spans="1:6" ht="84.75" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="F5" s="39"/>
+    </row>
+    <row r="6" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="37" t="s">
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46318</v>
+      </c>
+      <c r="E6" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="39"/>
-    </row>
-    <row r="6" spans="1:6" ht="35.25" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="F6" s="39"/>
+    </row>
+    <row r="7" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="39"/>
-    </row>
-    <row r="7" spans="1:6" ht="39.75" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -5133,9 +5516,9 @@
       <c r="E7" s="41"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="37.5" customHeight="1">
+    <row r="8" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5143,9 +5526,9 @@
       <c r="E8" s="41"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="33" customHeight="1">
+    <row r="9" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -5153,9 +5536,9 @@
       <c r="E9" s="41"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="33" customHeight="1">
+    <row r="10" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -5163,9 +5546,9 @@
       <c r="E10" s="41"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="39" customHeight="1">
+    <row r="11" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -5173,9 +5556,9 @@
       <c r="E11" s="41"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="36.75" customHeight="1">
+    <row r="12" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -5183,9 +5566,9 @@
       <c r="E12" s="41"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1">
+    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -5193,7 +5576,7 @@
       <c r="E13" s="41"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1">
+    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -5201,7 +5584,7 @@
       <c r="E14" s="41"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5209,7 +5592,7 @@
       <c r="E15" s="41"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -5217,7 +5600,7 @@
       <c r="E16" s="41"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5225,7 +5608,7 @@
       <c r="E17" s="41"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -5238,24 +5621,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="107" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="104" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5283,7 +5666,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -5292,43 +5675,43 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="63" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="76.5" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>9</v>
@@ -5340,15 +5723,15 @@
         <v>46314</v>
       </c>
       <c r="E4" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="39" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="50.25" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>9</v>
@@ -5360,13 +5743,13 @@
         <v>46316</v>
       </c>
       <c r="E5" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="39"/>
+    </row>
+    <row r="6" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="F5" s="39"/>
-    </row>
-    <row r="6" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>9</v>
@@ -5378,13 +5761,13 @@
         <v>46316</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="37.5" customHeight="1">
+    <row r="7" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -5392,9 +5775,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1">
+    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -5402,9 +5785,9 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="37.5" customHeight="1">
+    <row r="9" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -5412,9 +5795,9 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="52.5" customHeight="1">
+    <row r="10" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -5422,9 +5805,9 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="35.25" customHeight="1">
+    <row r="11" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -5432,9 +5815,9 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="38.25" customHeight="1">
+    <row r="12" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -5442,9 +5825,9 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="30.75" customHeight="1">
+    <row r="13" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -5452,9 +5835,9 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="33.75" customHeight="1">
+    <row r="14" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -5462,7 +5845,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -5470,7 +5853,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -5478,7 +5861,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -5486,7 +5869,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -5499,24 +5882,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="100" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="97" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5544,7 +5927,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
@@ -5554,43 +5937,43 @@
     <col min="6" max="6" width="73.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="130.5" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>8</v>
@@ -5602,13 +5985,13 @@
         <v>46316</v>
       </c>
       <c r="E4" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="39" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1">
+    </row>
+    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -5616,7 +5999,7 @@
       <c r="E5" s="37"/>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1">
+    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -5624,7 +6007,7 @@
       <c r="E6" s="37"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1">
+    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -5632,7 +6015,7 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1">
+    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -5640,7 +6023,7 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1">
+    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -5648,7 +6031,7 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1">
+    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -5656,7 +6039,7 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1">
+    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -5664,7 +6047,7 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1">
+    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -5672,7 +6055,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1">
+    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -5680,7 +6063,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1">
+    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -5688,7 +6071,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -5696,7 +6079,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -5704,7 +6087,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -5712,7 +6095,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -5725,24 +6108,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="87" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="84" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5770,7 +6153,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
@@ -5780,43 +6163,43 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="64" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="85.5" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>9</v>
@@ -5828,13 +6211,13 @@
         <v>46315</v>
       </c>
       <c r="E4" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="39"/>
+    </row>
+    <row r="5" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="F4" s="39"/>
-    </row>
-    <row r="5" spans="1:6" ht="74.25" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>9</v>
@@ -5847,12 +6230,12 @@
       </c>
       <c r="E5" s="37"/>
       <c r="F5" s="39" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="119.25" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>9</v>
@@ -5864,13 +6247,13 @@
         <v>46311</v>
       </c>
       <c r="E6" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="39"/>
+    </row>
+    <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="F6" s="39"/>
-    </row>
-    <row r="7" spans="1:6" ht="42.75" customHeight="1">
-      <c r="A7" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>9</v>
@@ -5884,9 +6267,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="76.5" customHeight="1">
+    <row r="8" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>9</v>
@@ -5900,9 +6283,9 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="54.75" customHeight="1">
+    <row r="9" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -5910,9 +6293,9 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="62.25" customHeight="1">
+    <row r="10" spans="1:6" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -5920,9 +6303,9 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="36" customHeight="1">
+    <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -5930,9 +6313,9 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="39.75" customHeight="1">
+    <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -5940,7 +6323,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="42" customHeight="1">
+    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -5948,7 +6331,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="49.5" customHeight="1">
+    <row r="14" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -5956,7 +6339,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -5964,7 +6347,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -5972,7 +6355,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -5980,7 +6363,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -5993,24 +6376,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="71" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="68" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6039,7 +6422,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -6048,43 +6431,43 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="49.5" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -6092,27 +6475,27 @@
       <c r="E4" s="37"/>
       <c r="F4" s="39"/>
     </row>
-    <row r="5" spans="1:6" ht="104.25" customHeight="1">
+    <row r="5" spans="1:6" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="22">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="E5" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="39"/>
+    </row>
+    <row r="6" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="F5" s="39"/>
-    </row>
-    <row r="6" spans="1:6" ht="41.25" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -6120,9 +6503,9 @@
       <c r="E6" s="37"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="71.25" customHeight="1">
+    <row r="7" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -6130,9 +6513,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="105.75" customHeight="1">
+    <row r="8" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -6140,9 +6523,9 @@
       <c r="E8" s="37"/>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="48.75" customHeight="1">
+    <row r="9" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -6150,7 +6533,7 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1">
+    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -6158,7 +6541,7 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1">
+    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -6166,7 +6549,7 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1">
+    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -6174,7 +6557,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1">
+    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -6182,7 +6565,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1">
+    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -6190,7 +6573,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -6198,7 +6581,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -6206,7 +6589,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -6214,7 +6597,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -6227,24 +6610,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="58" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6272,7 +6655,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -6281,55 +6664,55 @@
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
       <c r="E4" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="39"/>
+    </row>
+    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="F4" s="39"/>
-    </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>102</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -6337,9 +6720,9 @@
       <c r="E5" s="37"/>
       <c r="F5" s="39"/>
     </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1">
+    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -6347,9 +6730,9 @@
       <c r="E6" s="37"/>
       <c r="F6" s="39"/>
     </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1">
+    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -6357,9 +6740,9 @@
       <c r="E7" s="37"/>
       <c r="F7" s="39"/>
     </row>
-    <row r="8" spans="1:6" ht="154.5" customHeight="1">
+    <row r="8" spans="1:6" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>9</v>
@@ -6371,11 +6754,11 @@
         <v>46315</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F8" s="39"/>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1">
+    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -6383,7 +6766,7 @@
       <c r="E9" s="37"/>
       <c r="F9" s="39"/>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1">
+    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -6391,7 +6774,7 @@
       <c r="E10" s="37"/>
       <c r="F10" s="39"/>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1">
+    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -6399,7 +6782,7 @@
       <c r="E11" s="37"/>
       <c r="F11" s="39"/>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1">
+    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -6407,7 +6790,7 @@
       <c r="E12" s="37"/>
       <c r="F12" s="39"/>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1">
+    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -6415,7 +6798,7 @@
       <c r="E13" s="37"/>
       <c r="F13" s="39"/>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1">
+    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -6423,7 +6806,7 @@
       <c r="E14" s="37"/>
       <c r="F14" s="39"/>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -6431,7 +6814,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="39"/>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -6439,7 +6822,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="39"/>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -6447,7 +6830,7 @@
       <c r="E17" s="37"/>
       <c r="F17" s="39"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -6460,24 +6843,24 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="42" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C18">
-    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6742,6 +7125,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0fb2ba46-83e9-4d91-a985-8245aaf43e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6750,22 +7141,46 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0fb2ba46-83e9-4d91-a985-8245aaf43e5c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2D1D04-17F3-4DB1-A413-D2712C8E335E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2D1D04-17F3-4DB1-A413-D2712C8E335E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
+    <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9169F2-DC6F-440D-AA51-2EA02192DC48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9169F2-DC6F-440D-AA51-2EA02192DC48}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/revision tracker/Revision_Tracker.xlsx
+++ b/revision tracker/Revision_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/948b5d172b360b34/Python Stuff/revision tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="694" documentId="8_{44E14CDA-2C32-45B3-96A1-7C61FFBD3792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95403516-5279-4706-9A44-F53E00699725}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="8_{DFEBF892-2F2B-4BD5-A7A6-E815B59096B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3F96FF-E054-4AF0-AF3B-5A09D5009A2B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revision Timetable" sheetId="13" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="Settings" sheetId="12" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="Subjects">Dashboard!$M$2:$M$11</definedName>
+    <definedName name="Subjects">Dashboard!$N$2:$N$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +51,82 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="152">
+  <si>
+    <t>🗓️ Week 1 Timetable</t>
+  </si>
+  <si>
+    <t>🗓️ Week 2 Timetable</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Session 1</t>
+  </si>
+  <si>
+    <t>Session 2</t>
+  </si>
+  <si>
+    <t>Session 3</t>
+  </si>
+  <si>
+    <t>Session 4</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Physics</t>
+  </si>
+  <si>
+    <t>English Literature</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>Geography</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Chemistry</t>
+  </si>
+  <si>
+    <t>Computer Science</t>
+  </si>
+  <si>
+    <t>English Language</t>
+  </si>
+  <si>
+    <t>Biology</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
   <si>
     <t xml:space="preserve">  GCSE Revision Tracker — Dashboard</t>
   </si>
@@ -59,18 +134,9 @@
     <t>Subject list (helper)</t>
   </si>
   <si>
-    <t>Biology</t>
-  </si>
-  <si>
     <t>📊  Overall Progress</t>
   </si>
   <si>
-    <t>Chemistry</t>
-  </si>
-  <si>
-    <t>Physics</t>
-  </si>
-  <si>
     <t>Total topics</t>
   </si>
   <si>
@@ -83,33 +149,12 @@
     <t>Completed</t>
   </si>
   <si>
-    <t>Mathematics</t>
-  </si>
-  <si>
-    <t>English Language</t>
-  </si>
-  <si>
-    <t>English Literature</t>
-  </si>
-  <si>
     <t>Amber</t>
   </si>
   <si>
     <t>Red</t>
   </si>
   <si>
-    <t>Geography</t>
-  </si>
-  <si>
-    <t>History</t>
-  </si>
-  <si>
-    <t>Spanish</t>
-  </si>
-  <si>
-    <t>Computer Science</t>
-  </si>
-  <si>
     <t>📚  Progress by Subject</t>
   </si>
   <si>
@@ -123,6 +168,9 @@
   </si>
   <si>
     <t>Last Revised</t>
+  </si>
+  <si>
+    <t>🎯 Today's Focus</t>
   </si>
   <si>
     <t xml:space="preserve">  Biology</t>
@@ -643,7 +691,9 @@
     <t>Hazards</t>
   </si>
   <si>
-    <t>Your doing this next :)</t>
+    <t>1. Complete the third revision sheet on the geography oaks page
+2. Do two 8 markers on this topic.
+3. little chatgpt quiz on primary and secondary hazards/impacts if time (optional)</t>
   </si>
   <si>
     <t>Economic Activity &amp; energy</t>
@@ -722,12 +772,19 @@
     <t>1.6 - Ethical, legal, cultural and environmental impacts of digital technology</t>
   </si>
   <si>
-    <t>Okay so this topic isn't perfect so we're gonna have to come back to it in some time but i need to look at section 2.1 and 2.2 in the meanwhile tho.</t>
+    <t>Okay so this topic isn't perfect so we're gonna have to come back to it in some time.</t>
   </si>
   <si>
     <t>2.1 - Algorithms</t>
   </si>
   <si>
+    <t>1. finish learning merge sort
+2. remind your self of the file handling stuff
+3. do some questions from a pmt algorithms paper
+4. do some questions from a pmt programming fundamentals paper
+5. highlight any gaps in knowledge</t>
+  </si>
+  <si>
     <t>2.2 - Programming fundamentals</t>
   </si>
   <si>
@@ -749,52 +806,7 @@
     <t>Edit the interval numbers in column C to change how often topics come back.</t>
   </si>
   <si>
-    <t>🗓️ Week 1 Timetable</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Session 1</t>
-  </si>
-  <si>
-    <t>Session 2</t>
-  </si>
-  <si>
-    <t>Session 3</t>
-  </si>
-  <si>
-    <t>Session 4</t>
-  </si>
-  <si>
-    <t>Monday</t>
-  </si>
-  <si>
-    <t>Tuesday</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
-  </si>
-  <si>
-    <t>Thursday</t>
-  </si>
-  <si>
-    <t>Friday</t>
-  </si>
-  <si>
-    <t>Saturday</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>🗓️ Week 2 Timetable</t>
-  </si>
-  <si>
-    <t>🎯 Today's Focus</t>
+    <t>% Complete</t>
   </si>
 </sst>
 </file>
@@ -804,7 +816,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1017,6 +1029,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3B3B3B"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -1101,7 +1126,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1226,13 +1251,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDCDCDC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFDCDCDC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDCDCDC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDCDCDC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDCDCDC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDCDCDC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDCDCDC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDCDCDC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDCDCDC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1316,15 +1380,6 @@
     <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
@@ -1370,13 +1425,37 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1403,6 +1482,18 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2034,7 +2125,112 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2048,14 +2244,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2356,126 +2545,38 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+          <bgColor rgb="FFEBEBEB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8B6B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF960000"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEBEBEB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8B6B6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2488,16 +2589,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF86BC71"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF960000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3156,267 +3247,267 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>148</v>
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="I2" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="J2" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="K2" s="43" t="s">
-        <v>139</v>
+      <c r="A2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="40" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="44" t="s">
+      <c r="A3" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="44" t="s">
+    </row>
+    <row r="4" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="G4" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="44" t="s">
-        <v>140</v>
-      </c>
-      <c r="H3" s="44" t="s">
+      <c r="I4" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="44" t="s">
+      <c r="G7" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="44" t="s">
+    </row>
+    <row r="8" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="41" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="H4" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="45" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="H5" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="44" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
-        <v>143</v>
-      </c>
-      <c r="B6" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="45" t="s">
-        <v>143</v>
-      </c>
-      <c r="H6" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="45" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="44" t="s">
-        <v>144</v>
-      </c>
-      <c r="H7" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="K8" s="45" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="E9" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="G9" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="H9" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="K9" s="44" t="s">
-        <v>146</v>
+      <c r="J9" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="41" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3437,172 +3528,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="A1" s="73" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>25</v>
+      <c r="A2" s="31" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D4" s="4">
         <v>46317</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="39"/>
+      <c r="E4" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4" s="36"/>
     </row>
     <row r="5" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="39"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="39"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="39"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="39"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="39"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="39"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="39"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="39"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="39"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="39"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="39"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3665,176 +3756,176 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="A1" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>25</v>
+      <c r="A2" s="31" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D4" s="4">
         <v>46317</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>114</v>
+      <c r="E4" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="39"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="39"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="39"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="39"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="39"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="39"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="39"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="39"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="39"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="39"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="39"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3896,182 +3987,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="A1" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>25</v>
+      <c r="A2" s="31" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="39"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="36"/>
     </row>
     <row r="5" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="11"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="39"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="11"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="39"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="39"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D9" s="11">
         <v>46315</v>
       </c>
-      <c r="E9" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="F9" s="39"/>
-    </row>
-    <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="F9" s="36"/>
+    </row>
+    <row r="10" spans="1:6" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="39"/>
+        <v>142</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="11">
+        <v>46318</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="39"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="39"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="39"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="39"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="39"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="39"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="11"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4132,30 +4231,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="66" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
+      <c r="B2" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
     </row>
     <row r="4" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
+      <c r="B4" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
     </row>
     <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -4163,7 +4262,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3">
         <v>3</v>
@@ -4171,7 +4270,7 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="15" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3">
         <v>6</v>
@@ -4179,18 +4278,18 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="65" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
+      <c r="B12" s="74" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4204,184 +4303,188 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="13" max="13" width="13" hidden="1" customWidth="1"/>
-    <col min="26" max="29" width="2.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="13" hidden="1" customWidth="1"/>
+    <col min="27" max="30" width="2.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="M1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="52" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="M3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="N1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="N3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59">
+        <v>31</v>
+      </c>
+      <c r="N5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="64">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*"))</f>
         <v>65</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="61">
+      <c r="B6" s="61"/>
+      <c r="C6" s="66">
         <f ca="1">A6-E6-G6</f>
-        <v>45</v>
-      </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="60">
+        <v>43</v>
+      </c>
+      <c r="D6" s="61"/>
+      <c r="E6" s="65">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"In Progress"))</f>
-        <v>4</v>
-      </c>
-      <c r="F6" s="56"/>
-      <c r="G6" s="55">
+        <v>6</v>
+      </c>
+      <c r="F6" s="61"/>
+      <c r="G6" s="60">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"Completed"))</f>
         <v>16</v>
       </c>
-      <c r="H6" s="56"/>
-      <c r="M6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M7" t="s">
+      <c r="H6" s="61"/>
+      <c r="N6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="58">
+    <row r="9" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="63">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Amber"))</f>
         <v>5</v>
       </c>
-      <c r="B9" s="56"/>
-      <c r="C9" s="57">
+      <c r="B9" s="61"/>
+      <c r="C9" s="62">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Red"))</f>
         <v>1</v>
       </c>
-      <c r="D9" s="56"/>
-      <c r="M9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M10" t="s">
+      <c r="D9" s="61"/>
+      <c r="N9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+    </row>
+    <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="J13" s="48" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-    </row>
-    <row r="13" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
-        <v>2</v>
       </c>
       <c r="B14" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*"))</f>
@@ -4407,18 +4510,22 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="49">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I14" s="29" t="str">
+      <c r="I14" s="55">
+        <f t="shared" ref="I14:I23" ca="1" si="1">IFERROR(E14/B14, 0)</f>
+        <v>0.375</v>
+      </c>
+      <c r="J14" s="50" t="str">
         <f ca="1">IF(MAX(Biology!D4:D1000)=0, "-", IF(MAX(Biology!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Biology!D4:D1000)=1, "Yesterday", TODAY()-MAX(Biology!D4:D1000) &amp; " days ago")))</f>
         <v>Yesterday</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B15" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*"))</f>
@@ -4444,18 +4551,22 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="53">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="30" t="str">
+      <c r="I15" s="56">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="J15" s="54" t="str">
         <f ca="1">IF(MAX(Chemistry!D4:D1000)=0, "N/A", IF(MAX(Chemistry!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Chemistry!D4:D1000)=1, "Yesterday", TODAY()-MAX(Chemistry!D4:D1000) &amp; " days ago")))</f>
         <v>Today</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B16" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*"))</f>
@@ -4481,18 +4592,22 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="49">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I16" s="29" t="str">
+      <c r="I16" s="55">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="J16" s="50" t="str">
         <f ca="1">IF(MAX(Physics!D4:D1000)=0, "-", IF(MAX(Physics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Physics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Physics!D4:D1000) &amp; " days ago")))</f>
         <v>2 days ago</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B17" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*"))</f>
@@ -4518,18 +4633,22 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="53">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I17" s="30" t="str">
+      <c r="I17" s="56">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="54" t="str">
         <f ca="1">IF(MAX(Mathematics!D4:D1000)=0, "-", IF(MAX(Mathematics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Mathematics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Mathematics!D4:D1000) &amp; " days ago")))</f>
         <v>2 days ago</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B18" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*"))</f>
@@ -4555,18 +4674,22 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Amber"))</f>
         <v>3</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="49">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Red"))</f>
         <v>1</v>
       </c>
-      <c r="I18" s="29" t="str">
+      <c r="I18" s="55">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="J18" s="50" t="str">
         <f ca="1">IF(MAX('English Language'!D4:D1000)=0, "-", IF(MAX('English Language'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Language'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Language'!D4:D1000) &amp; " days ago")))</f>
         <v>Yesterday</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B19" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*"))</f>
@@ -4592,18 +4715,22 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Amber"))</f>
         <v>1</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="53">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I19" s="30" t="str">
+      <c r="I19" s="56">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="54" t="str">
         <f ca="1">IF(MAX('English Literature'!D4:D1000)=0, "-", IF(MAX('English Literature'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Literature'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Literature'!D4:D1000) &amp; " days ago")))</f>
         <v>Today</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*"))</f>
@@ -4611,11 +4738,11 @@
       </c>
       <c r="C20" s="24">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!B4:B1000"),"In Progress"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!B4:B1000"),"Completed"))</f>
@@ -4623,24 +4750,28 @@
       </c>
       <c r="F20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Green"))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="49">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I20" s="29" t="str">
+      <c r="I20" s="55">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="J20" s="50" t="str">
         <f ca="1">IF(MAX(Geography!D4:D1000)=0, "-", IF(MAX(Geography!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Geography!D4:D1000)=1, "Yesterday", TODAY()-MAX(Geography!D4:D1000) &amp; " days ago")))</f>
-        <v>3 days ago</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Today</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B21" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*"))</f>
@@ -4666,18 +4797,22 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="53">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I21" s="30" t="str">
+      <c r="I21" s="56">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="54" t="str">
         <f ca="1">IF(MAX(History!D4:D1000)=0, "-", IF(MAX(History!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(History!D4:D1000)=1, "Yesterday", TODAY()-MAX(History!D4:D1000) &amp; " days ago")))</f>
         <v>Yesterday</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B22" s="24">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*"))</f>
@@ -4703,18 +4838,22 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="49">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I22" s="29" t="str">
+      <c r="I22" s="55">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="50" t="str">
         <f ca="1">IF(MAX(Spanish!D4:D1000)=0, "-", IF(MAX(Spanish!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Spanish!D4:D1000)=1, "Yesterday", TODAY()-MAX(Spanish!D4:D1000) &amp; " days ago")))</f>
         <v>Yesterday</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*"))</f>
@@ -4722,11 +4861,11 @@
       </c>
       <c r="C23" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!B4:B1000"),"In Progress"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!B4:B1000"),"Completed"))</f>
@@ -4734,111 +4873,108 @@
       </c>
       <c r="F23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Green"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="26">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Amber"))</f>
         <v>1</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="53">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I23" s="30" t="str">
+      <c r="I23" s="52">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.125</v>
+      </c>
+      <c r="J23" s="54" t="str">
         <f ca="1">IF(MAX('Computer Science'!D4:D1000)=0, "-", IF(MAX('Computer Science'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('Computer Science'!D4:D1000)=1, "Yesterday", TODAY()-MAX('Computer Science'!D4:D1000) &amp; " days ago")))</f>
-        <v>3 days ago</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="H26" s="48"/>
-    </row>
-    <row r="27" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="str">
+        <v>Today</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="67"/>
+      <c r="C26" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="67"/>
+      <c r="G26" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="H26" s="67"/>
+      <c r="I26" s="45"/>
+    </row>
+    <row r="27" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="68" t="str">
         <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)), "-")</f>
         <v>Chemistry</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="49" t="str">
+      <c r="B27" s="70"/>
+      <c r="C27" s="68" t="str">
         <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)), "-")</f>
         <v>English Literature</v>
       </c>
-      <c r="D27" s="51"/>
-      <c r="E27" s="49" t="str">
+      <c r="D27" s="70"/>
+      <c r="E27" s="68" t="str">
         <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)), "-")</f>
         <v>Computer Science</v>
       </c>
-      <c r="F27" s="51"/>
-      <c r="G27" s="49" t="str">
+      <c r="F27" s="70"/>
+      <c r="G27" s="68" t="str">
         <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)), "-")</f>
         <v>Geography</v>
       </c>
-      <c r="H27" s="50"/>
-      <c r="Z27" s="46" t="b">
-        <f ca="1">IFERROR(VLOOKUP(A27, $A$13:$I$23, 9, FALSE)="Today", FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="AA27" s="46" t="b">
-        <f ca="1">IFERROR(VLOOKUP(C27, $A$13:$I$23, 9, FALSE)="Today", FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="AB27" s="46" t="b">
-        <f ca="1">IFERROR(VLOOKUP(E27, $A$13:$I$23, 9, FALSE)="Today", FALSE)</f>
+      <c r="H27" s="69"/>
+      <c r="I27" s="46"/>
+      <c r="AA27" s="43" t="b">
+        <f ca="1">IFERROR(VLOOKUP(A27, $A$13:$J$23, 9, FALSE)="Today", FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AC27" s="46" t="b">
-        <f ca="1">IFERROR(VLOOKUP(G27, $A$13:$I$23, 9, FALSE)="Today", FALSE)</f>
+      <c r="AB27" s="43" t="b">
+        <f ca="1">IFERROR(VLOOKUP(C27, $A$13:$J$23, 9, FALSE)="Today", FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" s="47" t="str">
-        <f ca="1">IF(COUNTIFS($A$13:$A$23, A27, $I$13:$I$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
+      <c r="AC27" s="43" t="b">
+        <f ca="1">IFERROR(VLOOKUP(E27, $A$13:$J$23, 9, FALSE)="Today", FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="43" t="b">
+        <f ca="1">IFERROR(VLOOKUP(G27, $A$13:$J$23, 9, FALSE)="Today", FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A28" s="44" t="str">
+        <f ca="1">IF(COUNTIFS($A$13:$A$23, A27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
         <v>DONE</v>
       </c>
-      <c r="C28" s="47" t="str">
-        <f ca="1">IF(COUNTIFS($A$13:$A$23, C27, $I$13:$I$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
+      <c r="C28" s="44" t="str">
+        <f ca="1">IF(COUNTIFS($A$13:$A$23, C27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
         <v>DONE</v>
       </c>
-      <c r="E28" s="47" t="str">
-        <f ca="1">IF(COUNTIFS($A$13:$A$23, E27, $I$13:$I$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
-        <v>NOT DONE</v>
-      </c>
-      <c r="G28" s="47" t="str">
-        <f ca="1">IF(COUNTIFS($A$13:$A$23, G27, $I$13:$I$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
-        <v>NOT DONE</v>
+      <c r="E28" s="44" t="str">
+        <f ca="1">IF(COUNTIFS($A$13:$A$23, E27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
+        <v>DONE</v>
+      </c>
+      <c r="G28" s="44" t="str">
+        <f ca="1">IF(COUNTIFS($A$13:$A$23, G27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
+        <v>DONE</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="A26:B26"/>
@@ -4847,13 +4983,22 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
-  <conditionalFormatting sqref="A27:H27">
-    <cfRule type="cellIs" dxfId="125" priority="71" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="A27:I27">
+    <cfRule type="cellIs" dxfId="125" priority="72" stopIfTrue="1" operator="equal">
+      <formula>"""DONE"""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="71" stopIfTrue="1" operator="equal">
       <formula>"""NOT DONE"""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="72" stopIfTrue="1" operator="equal">
-      <formula>"""DONE"""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F23">
@@ -4866,12 +5011,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H14:H23">
+  <conditionalFormatting sqref="H14:I23">
     <cfRule type="cellIs" dxfId="121" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:I23">
+  <conditionalFormatting sqref="J14:J23">
     <cfRule type="cellIs" dxfId="120" priority="6" stopIfTrue="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -5004,8 +5149,8 @@
     <cfRule type="cellIs" dxfId="77" priority="49" stopIfTrue="1" operator="equal">
       <formula>"46 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="50" stopIfTrue="1" operator="equal">
-      <formula>"47 days ago"</formula>
+    <cfRule type="cellIs" dxfId="76" priority="4" stopIfTrue="1" operator="equal">
+      <formula>"Today"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="75" priority="51" stopIfTrue="1" operator="equal">
       <formula>"48 days ago"</formula>
@@ -5028,8 +5173,8 @@
     <cfRule type="cellIs" dxfId="69" priority="57" stopIfTrue="1" operator="equal">
       <formula>"54 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="58" stopIfTrue="1" operator="equal">
-      <formula>"55 days ago"</formula>
+    <cfRule type="cellIs" dxfId="68" priority="50" stopIfTrue="1" operator="equal">
+      <formula>"47 days ago"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="67" priority="59" stopIfTrue="1" operator="equal">
       <formula>"56 days ago"</formula>
@@ -5049,11 +5194,11 @@
     <cfRule type="cellIs" dxfId="62" priority="64" stopIfTrue="1" operator="equal">
       <formula>"3 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="4" stopIfTrue="1" operator="equal">
-      <formula>"Today"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="5" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="5" stopIfTrue="1" operator="equal">
       <formula>"Yesterday"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="58" stopIfTrue="1" operator="equal">
+      <formula>"55 days ago"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -5086,17 +5231,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="A1" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>25</v>
+      <c r="A2" s="29" t="s">
+        <v>41</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5105,185 +5250,185 @@
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>9</v>
-      </c>
       <c r="C4" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D4" s="11">
         <v>46313</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>33</v>
+      <c r="E4" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
-        <v>34</v>
+      <c r="A5" s="32" t="s">
+        <v>50</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D5" s="11">
         <v>46316</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="39"/>
+      <c r="E5" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
-        <v>36</v>
+      <c r="A6" s="32" t="s">
+        <v>52</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D6" s="11">
         <v>46317</v>
       </c>
-      <c r="E6" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="39"/>
+      <c r="E6" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="39"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="11"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="39"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="39"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="39"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="39"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="39"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="39"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="39"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="39"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="11"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
     </row>
     <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
@@ -5417,204 +5562,204 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="A1" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
-        <v>25</v>
+      <c r="A2" s="30" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D4" s="4">
         <v>46315</v>
       </c>
-      <c r="E4" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>46</v>
+      <c r="E4" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D5" s="4">
         <v>46318</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="39"/>
+      <c r="E5" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4">
         <v>46318</v>
       </c>
-      <c r="E6" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="39"/>
+      <c r="E6" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="39"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="39"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="39"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="39"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="39"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="39"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="39"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="39"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="39"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="39"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5676,206 +5821,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="A1" s="72" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>25</v>
+      <c r="A2" s="31" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D4" s="11">
         <v>46314</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>61</v>
+      <c r="E4" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D5" s="11">
         <v>46316</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="39"/>
+      <c r="E5" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D6" s="11">
         <v>46316</v>
       </c>
-      <c r="E6" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="39"/>
+      <c r="E6" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="39"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="11"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="39"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="39"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="39"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="39"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="39"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="39"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="39"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="39"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="11"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5938,57 +6083,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="A1" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>25</v>
+      <c r="A2" s="31" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D4" s="11">
         <v>46316</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>76</v>
+      <c r="E4" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5996,112 +6141,112 @@
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="11"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="39"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="11"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="39"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="39"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="11"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="39"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="39"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="39"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="39"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="39"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="39"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="39"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="39"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="11"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6164,212 +6309,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="A1" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>25</v>
+      <c r="A2" s="31" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
-        <v>78</v>
+      <c r="A4" s="32" t="s">
+        <v>94</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D4" s="11">
         <v>46315</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="39"/>
+      <c r="E4" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="36"/>
     </row>
     <row r="5" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D5" s="11">
         <v>46317</v>
       </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="39" t="s">
-        <v>81</v>
+      <c r="E5" s="34"/>
+      <c r="F5" s="36" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D6" s="11">
         <v>46311</v>
       </c>
-      <c r="E6" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="39"/>
+      <c r="E6" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D7" s="11">
         <v>46315</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D8" s="11">
         <v>46315</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="39"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="11"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="39"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="39"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
-        <v>88</v>
+      <c r="A11" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="39"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="39"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="39"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="39"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="39"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="39"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="11"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6432,178 +6577,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="A1" s="72" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>25</v>
+      <c r="A2" s="31" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="39"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="36"/>
     </row>
     <row r="5" spans="1:6" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D5" s="22">
         <v>46318</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="39"/>
+      <c r="E5" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="11"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="39"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="39"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="11"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="39"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="39"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="39"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="39"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="39"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="39"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="39"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="39"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="11"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6665,178 +6810,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="A1" s="72" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>25</v>
+      <c r="A2" s="31" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" s="39"/>
+      <c r="C4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46318</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="36"/>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="11"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="39"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="11"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="39"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="39"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D8" s="11">
         <v>46315</v>
       </c>
-      <c r="E8" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="39"/>
+      <c r="E8" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="11"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="39"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="39"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="36"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="39"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="39"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="39"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="39"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="39"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="39"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="11"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6886,6 +7037,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0fb2ba46-83e9-4d91-a985-8245aaf43e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006E3655B0D4A3F946B2B182A2452821C6" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7a9e24b6dc8563a5b2c5318cfdd77097">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0fb2ba46-83e9-4d91-a985-8245aaf43e5c" xmlns:ns4="ed8dfb7b-01af-4433-b4cc-631574050608" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b443fa188f0c7e58c89b943786fc45fd" ns3:_="" ns4:_="">
     <xsd:import namespace="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
@@ -7124,24 +7292,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0fb2ba46-83e9-4d91-a985-8245aaf43e5c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9169F2-DC6F-440D-AA51-2EA02192DC48}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2D1D04-17F3-4DB1-A413-D2712C8E335E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7158,29 +7334,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9169F2-DC6F-440D-AA51-2EA02192DC48}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/revision tracker/Revision_Tracker.xlsx
+++ b/revision tracker/Revision_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/948b5d172b360b34/Python Stuff/revision tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="8_{DFEBF892-2F2B-4BD5-A7A6-E815B59096B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3F96FF-E054-4AF0-AF3B-5A09D5009A2B}"/>
+  <xr:revisionPtr revIDLastSave="315" documentId="8_{900DBA63-C4C7-4070-82C1-769B6A063F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55022C41-3E89-4F86-B1DF-3F3293683817}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11565" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revision Timetable" sheetId="13" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="145">
   <si>
     <t>🗓️ Week 1 Timetable</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>Green</t>
+  </si>
+  <si>
+    <t>% Complete</t>
   </si>
   <si>
     <t>Last Revised</t>
@@ -224,7 +227,7 @@
     <t>Alright we are done. First Bit of bio revision done :)</t>
   </si>
   <si>
-    <t>next up do a chatgpt go over of group 4 and group 7. Then do a chatgpt quiz</t>
+    <t>Next session we are doing group 5 should be easy tho. Good luck</t>
   </si>
   <si>
     <r>
@@ -286,25 +289,26 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Group 4:</t>
+      <t xml:space="preserve">Group 4:
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">
-Respiration
+      <t>Respiration
 Gas exchange in humans</t>
     </r>
+  </si>
+  <si>
+    <t>very easy. Bio mocks are gonna be free :) :) :)</t>
   </si>
   <si>
     <r>
@@ -381,6 +385,9 @@
 Inheritance
 </t>
     </r>
+  </si>
+  <si>
+    <t>EASY BRO. THIS WAS FREE</t>
   </si>
   <si>
     <r>
@@ -413,91 +420,340 @@
     <t xml:space="preserve">  Chemistry</t>
   </si>
   <si>
-    <t>Principals of Chemistry  1a - 1e</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 1:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Principals of Chemistry  1a - 1e</t>
+    </r>
   </si>
   <si>
     <t>Complete</t>
   </si>
   <si>
-    <t>Next session you will complete inorganics part 2 and energetics</t>
-  </si>
-  <si>
-    <t>Bonding  1f - 1h</t>
+    <t>Next session is GROUP 5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 2: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bonding  1f - 1h</t>
+    </r>
   </si>
   <si>
     <t>SO easy very chill</t>
   </si>
   <si>
-    <t>Inorganic Chem part 1 - 1a - 1d</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 3:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Inorganic Chem part 1 - 1a - 1d</t>
+    </r>
   </si>
   <si>
     <t>calm. i know this stuff</t>
   </si>
   <si>
-    <t>Inorganic Chem part 2 - 1e - 1g</t>
-  </si>
-  <si>
-    <t>Energetics</t>
-  </si>
-  <si>
-    <t>Rates of Reaction</t>
-  </si>
-  <si>
-    <t>Reversible reaction and equilbria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">y10 Organics </t>
-  </si>
-  <si>
-    <t>y11 Organics</t>
-  </si>
-  <si>
-    <t>Full Mock Past Papers</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 4:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Inorganic Chem part 2 - 1e - 1g
+Rates of Reaction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 5:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Energetics
+Reversible reaction and equilbria</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 6:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rates of Reaction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 7:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>y10 Organics 
+Y11 Organics</t>
+    </r>
+  </si>
+  <si>
+    <t>Full mock past papers</t>
   </si>
   <si>
     <t xml:space="preserve">  Physics</t>
   </si>
   <si>
-    <t>9.1 Measuring waves + 10.1 Properties of waves &amp; EM Spectrum</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 1:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 9.1 Measuring waves
+ 10.1 Properties of waves &amp; EM Spectrum</t>
+    </r>
   </si>
   <si>
     <t>When doing a review session just do a little chatgpt quiz to finish up the rest of this topic.</t>
   </si>
   <si>
-    <t>Lets try do 9.5, 10.3, 10.7 next. All revise using chatgpt. Go over content then do big practise quiz with chatgtt. We are trying to get through all the content early so we can specialise later</t>
-  </si>
-  <si>
-    <t>9.2 Electrostatics and electrical current</t>
+    <t>Lets do GROUP 4 NEXT. HOPEFULLY ITS CHILL SPEND 1 HOUR ON THIS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 2:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 9.2 Electrostatics and electrical current</t>
+    </r>
   </si>
   <si>
     <t>Practise examination questions</t>
   </si>
   <si>
-    <t>9.3 Mains electricity + 10.4 Electrical circuits</t>
-  </si>
-  <si>
-    <t>9.4 Astronomy</t>
-  </si>
-  <si>
-    <t>9.5 Measuring motion + 10.3 Unbalanced forces and acceleration</t>
-  </si>
-  <si>
-    <t>9.6 Magnetism and electromagnets + 10.6 Electromagnetism</t>
-  </si>
-  <si>
-    <t>9.7 Energy types and energy resources + 10.2 Energy transfer, work and power</t>
-  </si>
-  <si>
-    <t>9.8 Density and pressure + 10.5 Pressure in Liquids and Ideal Gases</t>
-  </si>
-  <si>
-    <t>10.7 Thermal energy and Change of State</t>
-  </si>
-  <si>
-    <t>11.1 Radioactivity</t>
-  </si>
-  <si>
-    <t>11.2 Forces, Momentum &amp; Moments</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 3:
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+      </rPr>
+      <t>9.3 Mains electricity
+ 10.4 Electrical circuits</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 4: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>9.7 Energy types and energy resources
+10.2 Energy transfer, work and power
+9.4 Astronomy</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 5: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>9.5 Measuring motion
+10.3 Unbalanced forces and acceleration
+10.7 Thermal energy and Change of State</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 6: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>9.6 Magnetism and electromagnets
+10.6 Electromagnetism
+11.2 Forces, Momentum &amp; Moments</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 7: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>9.8 Density and pressure
+10.5 Pressure in Liquids and Ideal Gases
+11.1 Radioactivity</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">  Mathematics</t>
@@ -506,12 +762,8 @@
     <t>Do Lots of Past Papers</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Finish of doing summer 2012 paper 1 on onenote
-2. Mark it
-</t>
-  </si>
-  <si>
-    <t>Your next task will to be a chatgpt test on all the topics using the list of topics here. This will be the task for the lesson after next lesson: https://sevenoaksschool.fireflycloud.net/resource.aspx?id=1354099</t>
+    <t xml:space="preserve"> Do the reasoning paper on onenote and make sure you know all the topics
+SHOULD BE A VERY LIGHT SESSION</t>
   </si>
   <si>
     <t xml:space="preserve">  English Language</t>
@@ -754,28 +1006,120 @@
     <t xml:space="preserve">  Computer Science</t>
   </si>
   <si>
-    <t>1.1 - Systems Architecture</t>
-  </si>
-  <si>
-    <t>1.2 - Memory and storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3 - Computer networks, connections and protocols </t>
-  </si>
-  <si>
-    <t>1.4 - Network security</t>
-  </si>
-  <si>
-    <t>1.5 - Systems software</t>
-  </si>
-  <si>
-    <t>1.6 - Ethical, legal, cultural and environmental impacts of digital technology</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 1:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.1 - Systems Architecture
+1.2 - Memory and storage</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 2:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.3 - Computer networks, connections and protocols 
+1.4 - Network security</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 3:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.5 - Systems software</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 4:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.6 - Ethical, legal, cultural and environmental impacts of digital technology</t>
+    </r>
   </si>
   <si>
     <t>Okay so this topic isn't perfect so we're gonna have to come back to it in some time.</t>
   </si>
   <si>
-    <t>2.1 - Algorithms</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 5 :
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.1 - Algorithms
+2.2 - Programming fundamentals</t>
+    </r>
   </si>
   <si>
     <t>1. finish learning merge sort
@@ -785,7 +1129,26 @@
 5. highlight any gaps in knowledge</t>
   </si>
   <si>
-    <t>2.2 - Programming fundamentals</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GROUP 6:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Full exam papers</t>
+    </r>
   </si>
   <si>
     <t>⚙  Settings</t>
@@ -804,9 +1167,6 @@
   </si>
   <si>
     <t>Edit the interval numbers in column C to change how often topics come back.</t>
-  </si>
-  <si>
-    <t>% Complete</t>
   </si>
 </sst>
 </file>
@@ -816,7 +1176,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -876,11 +1236,6 @@
       <sz val="20"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1042,6 +1397,34 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -1121,7 +1504,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F8FF"/>
+        <fgColor rgb="FFD9EAD3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1238,24 +1621,6 @@
         <color rgb="FFDCDCDC"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFDCDCDC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDCDCDC"/>
-      </left>
-      <right/>
       <top style="thin">
         <color rgb="FFDCDCDC"/>
       </top>
@@ -1290,13 +1655,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1309,9 +1700,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1356,106 +1744,125 @@
     <xf numFmtId="14" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="31" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="32" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="31" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="32" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="31" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="32" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1482,25 +1889,13 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1511,7 +1906,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="190">
+  <dxfs count="192">
     <dxf>
       <font>
         <b/>
@@ -2132,6 +2527,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEBEBEB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFD9EAD3"/>
         </patternFill>
       </fill>
@@ -2173,6 +2582,13 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
@@ -2236,13 +2652,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill>
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
@@ -2537,6 +2946,27 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8B6B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
@@ -2545,38 +2975,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFEBEBEB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8B6B6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF960000"/>
-      </font>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2805,30 +3211,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:F27" headerRowDxfId="189" dataDxfId="188" totalsRowDxfId="187">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:F27" headerRowDxfId="191" dataDxfId="190" totalsRowDxfId="189">
   <autoFilter ref="A3:F27" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="186"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="185"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="184"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="183"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="182"/>
-    <tableColumn id="5" xr3:uid="{F0BDA802-DA31-4BA7-81BA-FDB612DC37E1}" name="General Notes" dataDxfId="181" totalsRowDxfId="180"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="188"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="187"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="186"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="185"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="184"/>
+    <tableColumn id="5" xr3:uid="{F0BDA802-DA31-4BA7-81BA-FDB612DC37E1}" name="General Notes" dataDxfId="183" totalsRowDxfId="182"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="ComputerScienceTbl" displayName="ComputerScienceTbl" ref="A3:F18" headerRowDxfId="135" dataDxfId="134" totalsRowDxfId="133">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="ComputerScienceTbl" displayName="ComputerScienceTbl" ref="A3:F18" headerRowDxfId="137" dataDxfId="136" totalsRowDxfId="135">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Topic" dataDxfId="132"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Status" dataDxfId="131"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Confidence" dataDxfId="130"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Last Revised" dataDxfId="129"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Next Action" dataDxfId="128"/>
-    <tableColumn id="5" xr3:uid="{63D6C4F6-C7E6-4663-AE70-5CFDFF770C29}" name="General Notes" dataDxfId="127" totalsRowDxfId="126"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Topic" dataDxfId="134"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Status" dataDxfId="133"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Confidence" dataDxfId="132"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Last Revised" dataDxfId="131"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Next Action" dataDxfId="130"/>
+    <tableColumn id="5" xr3:uid="{63D6C4F6-C7E6-4663-AE70-5CFDFF770C29}" name="General Notes" dataDxfId="129" totalsRowDxfId="128"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2841,7 +3247,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="179"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="181"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{DB8974C0-4423-4F62-8CA0-D4A3FA4693EA}" name="General Notes"/>
   </tableColumns>
@@ -2850,75 +3256,75 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PhysicsTbl" displayName="PhysicsTbl" ref="A3:F18" dataDxfId="178">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PhysicsTbl" displayName="PhysicsTbl" ref="A3:F18" dataDxfId="180">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Topic" dataDxfId="177"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Status" dataDxfId="176"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Confidence" dataDxfId="175"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Last Revised" dataDxfId="174"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Next Action" dataDxfId="173"/>
-    <tableColumn id="5" xr3:uid="{2C5860E0-C42D-447A-99E8-019207F1E49B}" name="General Notes" dataDxfId="172"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Topic" dataDxfId="179"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Status" dataDxfId="178"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Confidence" dataDxfId="177"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Last Revised" dataDxfId="176"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Next Action" dataDxfId="175"/>
+    <tableColumn id="5" xr3:uid="{2C5860E0-C42D-447A-99E8-019207F1E49B}" name="General Notes" dataDxfId="174"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="MathematicsTbl" displayName="MathematicsTbl" ref="A3:F18" headerRowDxfId="171" dataDxfId="170" totalsRowDxfId="169">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="MathematicsTbl" displayName="MathematicsTbl" ref="A3:F18" headerRowDxfId="173" dataDxfId="172" totalsRowDxfId="171">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Topic" dataDxfId="168"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status" dataDxfId="167"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Confidence" dataDxfId="166"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Last Revised" dataDxfId="165"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Next Action" dataDxfId="164"/>
-    <tableColumn id="5" xr3:uid="{902E25C2-558C-4568-81EE-02B6DDE3EEEE}" name="General Notes" dataDxfId="163" totalsRowDxfId="162"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Topic" dataDxfId="170"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status" dataDxfId="169"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Confidence" dataDxfId="168"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Last Revised" dataDxfId="167"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Next Action" dataDxfId="166"/>
+    <tableColumn id="5" xr3:uid="{902E25C2-558C-4568-81EE-02B6DDE3EEEE}" name="General Notes" dataDxfId="165" totalsRowDxfId="164"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EnglishLanguageTbl" displayName="EnglishLanguageTbl" ref="A3:F18" dataDxfId="161">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EnglishLanguageTbl" displayName="EnglishLanguageTbl" ref="A3:F18" dataDxfId="163">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Topic" dataDxfId="160"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Status" dataDxfId="159"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Confidence" dataDxfId="158"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Last Revised" dataDxfId="157"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Next Action" dataDxfId="156"/>
-    <tableColumn id="5" xr3:uid="{75D1410F-47BB-4A48-905A-25CF74BDB786}" name="General Notes" dataDxfId="155"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Topic" dataDxfId="162"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Status" dataDxfId="161"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Confidence" dataDxfId="160"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Last Revised" dataDxfId="159"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Next Action" dataDxfId="158"/>
+    <tableColumn id="5" xr3:uid="{75D1410F-47BB-4A48-905A-25CF74BDB786}" name="General Notes" dataDxfId="157"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="EnglishLiteratureTbl" displayName="EnglishLiteratureTbl" ref="A3:F18" headerRowDxfId="154" dataDxfId="153" totalsRowDxfId="152">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="EnglishLiteratureTbl" displayName="EnglishLiteratureTbl" ref="A3:F18" headerRowDxfId="156" dataDxfId="155" totalsRowDxfId="154">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Topic" dataDxfId="151"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Status" dataDxfId="150"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Confidence" dataDxfId="149"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Last Revised" dataDxfId="148"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Next Action" dataDxfId="147"/>
-    <tableColumn id="5" xr3:uid="{930CE764-AB02-4790-8724-F5622F11644B}" name="General Notes" dataDxfId="146" totalsRowDxfId="145"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Topic" dataDxfId="153"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Status" dataDxfId="152"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Confidence" dataDxfId="151"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Last Revised" dataDxfId="150"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Next Action" dataDxfId="149"/>
+    <tableColumn id="5" xr3:uid="{930CE764-AB02-4790-8724-F5622F11644B}" name="General Notes" dataDxfId="148" totalsRowDxfId="147"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="GeographyTbl" displayName="GeographyTbl" ref="A3:F18" dataDxfId="144">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="GeographyTbl" displayName="GeographyTbl" ref="A3:F18" dataDxfId="146">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Topic" dataDxfId="143"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Status" dataDxfId="142"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Confidence" dataDxfId="141"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Last Revised" dataDxfId="140"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Next Action" dataDxfId="139"/>
-    <tableColumn id="5" xr3:uid="{27D2B179-C2A7-46A7-8BEB-752BF05A8E89}" name="General Notes" dataDxfId="138"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Topic" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Status" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Confidence" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Last Revised" dataDxfId="142"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Next Action" dataDxfId="141"/>
+    <tableColumn id="5" xr3:uid="{27D2B179-C2A7-46A7-8BEB-752BF05A8E89}" name="General Notes" dataDxfId="140"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2931,7 +3337,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Last Revised" dataDxfId="137"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Last Revised" dataDxfId="139"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{28A5B818-9271-4E86-B3A0-50B7055F910C}" name="General Notes"/>
   </tableColumns>
@@ -2946,7 +3352,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Last Revised" dataDxfId="136"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Last Revised" dataDxfId="138"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{7C8E7108-0749-49A2-855D-B734764E8E58}" name="General Notes"/>
   </tableColumns>
@@ -3247,266 +3653,266 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="38" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="39" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="40" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="42" t="s">
+      <c r="I4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="42" t="s">
+      <c r="J4" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="42" t="s">
+      <c r="K4" s="41" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="41" t="s">
+      <c r="J5" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="41" t="s">
+      <c r="K5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="42" t="s">
+      <c r="I6" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="42" t="s">
+      <c r="J6" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="42" t="s">
+      <c r="K6" s="41" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="41" t="s">
+      <c r="G7" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="41" t="s">
+      <c r="K7" s="40" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="42" t="s">
+      <c r="G8" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="H8" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="42" t="s">
+      <c r="I8" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="42" t="s">
+      <c r="J8" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="42" t="s">
+      <c r="K8" s="41" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="40" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3522,48 +3928,48 @@
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="19" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="18" customWidth="1"/>
     <col min="5" max="5" width="43.5703125" customWidth="1"/>
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="A1" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>41</v>
+      <c r="A2" s="30" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="D3" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>46</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
@@ -3574,126 +3980,126 @@
       <c r="D4" s="4">
         <v>46317</v>
       </c>
-      <c r="E4" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="F4" s="36"/>
+      <c r="E4" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="35"/>
     </row>
     <row r="5" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="36"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="36"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="36"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="36"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="36"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="36"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="36"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="36"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="36"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="36"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="36"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="36"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="36"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="35"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3750,48 +4156,48 @@
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="21.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" style="19" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" style="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>127</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="A1" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>41</v>
+      <c r="A2" s="30" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="D3" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>46</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
@@ -3802,130 +4208,130 @@
       <c r="D4" s="4">
         <v>46317</v>
       </c>
-      <c r="E4" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>130</v>
+      <c r="E4" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="36"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="36"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="36"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="36"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="36"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="36"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="36"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="36"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="36"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="36"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="36"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="36"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="36"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="35"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3981,196 +4387,192 @@
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15" style="19" customWidth="1"/>
+    <col min="4" max="4" width="15" style="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="76" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="35"/>
+    </row>
+    <row r="5" spans="1:6" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="56" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="35"/>
+    </row>
+    <row r="6" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="35"/>
+    </row>
+    <row r="7" spans="1:6" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="B7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="10">
+        <v>46315</v>
+      </c>
+      <c r="E7" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="36"/>
-    </row>
-    <row r="5" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="F7" s="35"/>
+    </row>
+    <row r="8" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="36"/>
-    </row>
-    <row r="6" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="B8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="10">
+        <v>46318</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="36"/>
-    </row>
-    <row r="7" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="F8" s="35"/>
+    </row>
+    <row r="9" spans="1:6" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="36"/>
-    </row>
-    <row r="8" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="36"/>
-    </row>
-    <row r="9" spans="1:6" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="11">
-        <v>46315</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="F9" s="36"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="11">
-        <v>46318</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="F10" s="36"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="36"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="36"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="36"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="36"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="36"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="36"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="36"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4231,29 +4633,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="75" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
+      <c r="B2" s="79" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
     </row>
     <row r="4" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
+      <c r="B4" s="65" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
     </row>
     <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>147</v>
+      <c r="B6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="3">
@@ -4261,7 +4663,7 @@
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="3">
@@ -4269,7 +4671,7 @@
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="3">
@@ -4277,19 +4679,19 @@
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
-        <v>148</v>
+      <c r="B10" s="15" t="s">
+        <v>142</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="74" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
+      <c r="B12" s="78" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4303,31 +4705,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD28"/>
+  <dimension ref="A1:AD100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="9" width="14.7109375" customWidth="1"/>
+    <col min="2" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
     <col min="10" max="10" width="18.7109375" customWidth="1"/>
     <col min="14" max="14" width="13" hidden="1" customWidth="1"/>
     <col min="27" max="30" width="2.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
       <c r="N1" t="s">
         <v>26</v>
       </c>
@@ -4338,14 +4741,14 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
       <c r="N3" t="s">
         <v>14</v>
       </c>
@@ -4356,16 +4759,16 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>31</v>
       </c>
       <c r="N5" t="s">
@@ -4373,26 +4776,26 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="64">
+      <c r="A6" s="72">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*"))</f>
-        <v>65</v>
-      </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="66">
+        <v>57</v>
+      </c>
+      <c r="B6" s="69"/>
+      <c r="C6" s="74">
         <f ca="1">A6-E6-G6</f>
-        <v>43</v>
-      </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="65">
+        <v>33</v>
+      </c>
+      <c r="D6" s="69"/>
+      <c r="E6" s="73">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"In Progress"))</f>
         <v>6</v>
       </c>
-      <c r="F6" s="61"/>
-      <c r="G6" s="60">
+      <c r="F6" s="69"/>
+      <c r="G6" s="68">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"Completed"))</f>
-        <v>16</v>
-      </c>
-      <c r="H6" s="61"/>
+        <v>18</v>
+      </c>
+      <c r="H6" s="69"/>
       <c r="N6" t="s">
         <v>16</v>
       </c>
@@ -4403,10 +4806,10 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>33</v>
       </c>
       <c r="N8" t="s">
@@ -4414,16 +4817,16 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="63">
+      <c r="A9" s="71">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Amber"))</f>
         <v>5</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="62">
+      <c r="B9" s="69"/>
+      <c r="C9" s="70">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Red"))</f>
         <v>1</v>
       </c>
-      <c r="D9" s="61"/>
+      <c r="D9" s="69"/>
       <c r="N9" t="s">
         <v>10</v>
       </c>
@@ -4439,550 +4842,564 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
     </row>
     <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="47" t="s">
+      <c r="H13" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="J13" s="48" t="s">
+      <c r="I13" s="48" t="s">
         <v>38</v>
       </c>
+      <c r="J13" s="45" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*"))</f>
         <v>8</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="23">
         <f t="shared" ref="C14:C23" ca="1" si="0">B14-D14-E14</f>
-        <v>5</v>
-      </c>
-      <c r="D14" s="24">
+        <v>3</v>
+      </c>
+      <c r="D14" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!B4:B1000"),"In Progress"))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!B4:B1000"),"Completed"))</f>
-        <v>3</v>
-      </c>
-      <c r="F14" s="24">
+        <v>5</v>
+      </c>
+      <c r="F14" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Green"))</f>
-        <v>3</v>
-      </c>
-      <c r="G14" s="24">
+        <v>5</v>
+      </c>
+      <c r="G14" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="49">
+      <c r="H14" s="46">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I14" s="55">
+      <c r="I14" s="52">
         <f t="shared" ref="I14:I23" ca="1" si="1">IFERROR(E14/B14, 0)</f>
-        <v>0.375</v>
-      </c>
-      <c r="J14" s="50" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="J14" s="47" t="str">
         <f ca="1">IF(MAX(Biology!D4:D1000)=0, "-", IF(MAX(Biology!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Biology!D4:D1000)=1, "Yesterday", TODAY()-MAX(Biology!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
+        <v>Today</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*"))</f>
-        <v>10</v>
-      </c>
-      <c r="C15" s="26">
+        <v>8</v>
+      </c>
+      <c r="C15" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="D15" s="26">
+        <v>5</v>
+      </c>
+      <c r="D15" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!B4:B1000"),"In Progress"))</f>
         <v>0</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!B4:B1000"),"Completed"))</f>
         <v>3</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Green"))</f>
         <v>3</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="53">
+      <c r="H15" s="50">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="56">
+      <c r="I15" s="53">
         <f t="shared" ca="1" si="1"/>
-        <v>0.3</v>
-      </c>
-      <c r="J15" s="54" t="str">
+        <v>0.375</v>
+      </c>
+      <c r="J15" s="51" t="str">
         <f ca="1">IF(MAX(Chemistry!D4:D1000)=0, "N/A", IF(MAX(Chemistry!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Chemistry!D4:D1000)=1, "Yesterday", TODAY()-MAX(Chemistry!D4:D1000) &amp; " days ago")))</f>
-        <v>Today</v>
+        <v>Yesterday</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*"))</f>
-        <v>11</v>
-      </c>
-      <c r="C16" s="24">
+        <v>7</v>
+      </c>
+      <c r="C16" s="23">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="D16" s="24">
+        <v>4</v>
+      </c>
+      <c r="D16" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!B4:B1000"),"In Progress"))</f>
         <v>0</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!B4:B1000"),"Completed"))</f>
         <v>3</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Green"))</f>
         <v>3</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="49">
+      <c r="H16" s="46">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I16" s="55">
+      <c r="I16" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="J16" s="50" t="str">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="J16" s="47" t="str">
         <f ca="1">IF(MAX(Physics!D4:D1000)=0, "-", IF(MAX(Physics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Physics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Physics!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*"))</f>
         <v>1</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="25">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!C4:C1000"),"Green"))</f>
         <v>1</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H17" s="53">
+      <c r="H17" s="50">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="53">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="54" t="str">
+      <c r="J17" s="51" t="str">
         <f ca="1">IF(MAX(Mathematics!D4:D1000)=0, "-", IF(MAX(Mathematics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Mathematics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Mathematics!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
+        <v>Today</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*"))</f>
         <v>9</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="23">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!B4:B1000"),"In Progress"))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!B4:B1000"),"Completed"))</f>
         <v>5</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Green"))</f>
         <v>1</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Amber"))</f>
         <v>3</v>
       </c>
-      <c r="H18" s="49">
+      <c r="H18" s="46">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Red"))</f>
         <v>1</v>
       </c>
-      <c r="I18" s="55">
+      <c r="I18" s="52">
         <f t="shared" ca="1" si="1"/>
         <v>0.55555555555555558</v>
       </c>
-      <c r="J18" s="50" t="str">
+      <c r="J18" s="47" t="str">
         <f ca="1">IF(MAX('English Language'!D4:D1000)=0, "-", IF(MAX('English Language'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Language'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Language'!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
+        <v>2 days ago</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*"))</f>
         <v>6</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="25">
         <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Green"))</f>
         <v>0</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Amber"))</f>
         <v>1</v>
       </c>
-      <c r="H19" s="53">
+      <c r="H19" s="50">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I19" s="56">
+      <c r="I19" s="53">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="54" t="str">
+      <c r="J19" s="51" t="str">
         <f ca="1">IF(MAX('English Literature'!D4:D1000)=0, "-", IF(MAX('English Literature'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Literature'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Literature'!D4:D1000) &amp; " days ago")))</f>
-        <v>Today</v>
+        <v>Yesterday</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*"))</f>
         <v>5</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="23">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!B4:B1000"),"Completed"))</f>
         <v>1</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Green"))</f>
         <v>2</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="49">
+      <c r="H20" s="46">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I20" s="55">
+      <c r="I20" s="52">
         <f t="shared" ca="1" si="1"/>
         <v>0.2</v>
       </c>
-      <c r="J20" s="50" t="str">
+      <c r="J20" s="47" t="str">
         <f ca="1">IF(MAX(Geography!D4:D1000)=0, "-", IF(MAX(Geography!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Geography!D4:D1000)=1, "Yesterday", TODAY()-MAX(Geography!D4:D1000) &amp; " days ago")))</f>
-        <v>Today</v>
+        <v>Yesterday</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*"))</f>
         <v>3</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!C4:C1000"),"Green"))</f>
         <v>1</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="53">
+      <c r="H21" s="50">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I21" s="56">
+      <c r="I21" s="53">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="54" t="str">
+      <c r="J21" s="51" t="str">
         <f ca="1">IF(MAX(History!D4:D1000)=0, "-", IF(MAX(History!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(History!D4:D1000)=1, "Yesterday", TODAY()-MAX(History!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
+        <v>2 days ago</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*"))</f>
         <v>4</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="23">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!B4:B1000"),"Completed"))</f>
         <v>0</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!C4:C1000"),"Green"))</f>
         <v>1</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="49">
+      <c r="H22" s="46">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I22" s="55">
+      <c r="I22" s="52">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="50" t="str">
+      <c r="J22" s="47" t="str">
         <f ca="1">IF(MAX(Spanish!D4:D1000)=0, "-", IF(MAX(Spanish!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Spanish!D4:D1000)=1, "Yesterday", TODAY()-MAX(Spanish!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
+        <v>2 days ago</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*"))</f>
-        <v>8</v>
-      </c>
-      <c r="C23" s="26">
+        <v>6</v>
+      </c>
+      <c r="C23" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D23" s="26">
+        <v>4</v>
+      </c>
+      <c r="D23" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!B4:B1000"),"In Progress"))</f>
         <v>1</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!B4:B1000"),"Completed"))</f>
         <v>1</v>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Green"))</f>
         <v>1</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Amber"))</f>
         <v>1</v>
       </c>
-      <c r="H23" s="53">
+      <c r="H23" s="50">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I23" s="52">
+      <c r="I23" s="49">
         <f t="shared" ca="1" si="1"/>
-        <v>0.125</v>
-      </c>
-      <c r="J23" s="54" t="str">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="J23" s="51" t="str">
         <f ca="1">IF(MAX('Computer Science'!D4:D1000)=0, "-", IF(MAX('Computer Science'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('Computer Science'!D4:D1000)=1, "Yesterday", TODAY()-MAX('Computer Science'!D4:D1000) &amp; " days ago")))</f>
-        <v>Today</v>
+        <v>Yesterday</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39" t="s">
-        <v>39</v>
+      <c r="A25" s="38" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="67" t="s">
+      <c r="A26" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="67"/>
-      <c r="C26" s="67" t="s">
+      <c r="B26" s="62"/>
+      <c r="C26" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67" t="s">
+      <c r="D26" s="62"/>
+      <c r="E26" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="67"/>
-      <c r="G26" s="67" t="s">
+      <c r="F26" s="62"/>
+      <c r="G26" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H26" s="67"/>
-      <c r="I26" s="45"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="43"/>
     </row>
     <row r="27" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="68" t="str">
+      <c r="A27" s="64" t="str">
         <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)), "-")</f>
-        <v>Chemistry</v>
-      </c>
-      <c r="B27" s="70"/>
-      <c r="C27" s="68" t="str">
+        <v>Biology</v>
+      </c>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64" t="str">
         <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)), "-")</f>
-        <v>English Literature</v>
-      </c>
-      <c r="D27" s="70"/>
-      <c r="E27" s="68" t="str">
+        <v>Mathematics</v>
+      </c>
+      <c r="D27" s="64"/>
+      <c r="E27" s="63" t="str">
         <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)), "-")</f>
-        <v>Computer Science</v>
-      </c>
-      <c r="F27" s="70"/>
-      <c r="G27" s="68" t="str">
+        <v>-</v>
+      </c>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63" t="str">
         <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)), "-")</f>
-        <v>Geography</v>
-      </c>
-      <c r="H27" s="69"/>
-      <c r="I27" s="46"/>
-      <c r="AA27" s="43" t="b">
+        <v>-</v>
+      </c>
+      <c r="H27" s="63"/>
+      <c r="AA27" s="42" t="b">
         <f ca="1">IFERROR(VLOOKUP(A27, $A$13:$J$23, 9, FALSE)="Today", FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AB27" s="43" t="b">
+      <c r="AB27" s="42" t="b">
         <f ca="1">IFERROR(VLOOKUP(C27, $A$13:$J$23, 9, FALSE)="Today", FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AC27" s="43" t="b">
+      <c r="AC27" s="42" t="b">
         <f ca="1">IFERROR(VLOOKUP(E27, $A$13:$J$23, 9, FALSE)="Today", FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AD27" s="43" t="b">
+      <c r="AD27" s="42" t="b">
         <f ca="1">IFERROR(VLOOKUP(G27, $A$13:$J$23, 9, FALSE)="Today", FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" s="44" t="str">
+      <c r="A28" s="58" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, A27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
         <v>DONE</v>
       </c>
-      <c r="C28" s="44" t="str">
+      <c r="B28" s="59"/>
+      <c r="C28" s="58" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, C27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
         <v>DONE</v>
       </c>
-      <c r="E28" s="44" t="str">
+      <c r="D28" s="59"/>
+      <c r="E28" s="60" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, E27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
-        <v>DONE</v>
-      </c>
-      <c r="G28" s="44" t="str">
+        <v>NOT DONE</v>
+      </c>
+      <c r="F28" s="61"/>
+      <c r="G28" s="60" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, G27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
-        <v>DONE</v>
+        <v>NOT DONE</v>
+      </c>
+      <c r="H28" s="61"/>
+    </row>
+    <row r="99" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" t="str">
+        <f ca="1">IFERROR(INDEX($J$6:$J$15, MATCH(A27, $A$6:$A$15, 0)), "-")</f>
+        <v>Today</v>
+      </c>
+      <c r="C100" t="str">
+        <f ca="1">IFERROR(INDEX($J$6:$J$15, MATCH(C27, $A$6:$A$15, 0)), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="E100" t="str">
+        <f ca="1">IFERROR(INDEX($J$6:$J$15, MATCH(E27, $A$6:$A$15, 0)), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="G100" t="str">
+        <f ca="1">IFERROR(INDEX($J$6:$J$15, MATCH(G27, $A$6:$A$15, 0)), "-")</f>
+        <v>-</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A3:F3"/>
@@ -4992,13 +5409,29 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
   </mergeCells>
-  <conditionalFormatting sqref="A27:I27">
-    <cfRule type="cellIs" dxfId="125" priority="72" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="A27">
+    <cfRule type="cellIs" dxfId="127" priority="72" stopIfTrue="1" operator="equal">
       <formula>"""DONE"""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="71" stopIfTrue="1" operator="equal">
-      <formula>"""NOT DONE"""</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:H28">
+    <cfRule type="expression" dxfId="126" priority="75" stopIfTrue="1">
+      <formula>A100="-"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="125" priority="73" stopIfTrue="1">
+      <formula>A100="Today"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="124" priority="74" stopIfTrue="1">
+      <formula>AND(A100&lt;&gt;"Today", A100&lt;&gt;"-")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F23">
@@ -5017,188 +5450,188 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14:J23">
-    <cfRule type="cellIs" dxfId="120" priority="6" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="8" stopIfTrue="1" operator="equal">
+      <formula>"5 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="119" priority="9" stopIfTrue="1" operator="equal">
+      <formula>"6 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="10" stopIfTrue="1" operator="equal">
+      <formula>"7 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="11" stopIfTrue="1" operator="equal">
+      <formula>"8 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="116" priority="12" stopIfTrue="1" operator="equal">
+      <formula>"9 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="13" stopIfTrue="1" operator="equal">
+      <formula>"10 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="14" stopIfTrue="1" operator="equal">
+      <formula>"11 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="113" priority="15" stopIfTrue="1" operator="equal">
+      <formula>"12 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="16" stopIfTrue="1" operator="equal">
+      <formula>"13 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="17" stopIfTrue="1" operator="equal">
+      <formula>"14 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="110" priority="18" stopIfTrue="1" operator="equal">
+      <formula>"15 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="19" stopIfTrue="1" operator="equal">
+      <formula>"16 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="20" stopIfTrue="1" operator="equal">
+      <formula>"17 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="107" priority="21" stopIfTrue="1" operator="equal">
+      <formula>"18 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="22" stopIfTrue="1" operator="equal">
+      <formula>"19 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="23" stopIfTrue="1" operator="equal">
+      <formula>"20 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="24" stopIfTrue="1" operator="equal">
+      <formula>"21 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="25" stopIfTrue="1" operator="equal">
+      <formula>"22 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="26" stopIfTrue="1" operator="equal">
+      <formula>"23 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="101" priority="27" stopIfTrue="1" operator="equal">
+      <formula>"24 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="28" stopIfTrue="1" operator="equal">
+      <formula>"25 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="29" stopIfTrue="1" operator="equal">
+      <formula>"26 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="30" stopIfTrue="1" operator="equal">
+      <formula>"27 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="31" stopIfTrue="1" operator="equal">
+      <formula>"28 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="32" stopIfTrue="1" operator="equal">
+      <formula>"29 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="95" priority="33" stopIfTrue="1" operator="equal">
+      <formula>"30 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="34" stopIfTrue="1" operator="equal">
+      <formula>"31 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="35" stopIfTrue="1" operator="equal">
+      <formula>"32 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="92" priority="36" stopIfTrue="1" operator="equal">
+      <formula>"33 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="37" stopIfTrue="1" operator="equal">
+      <formula>"34 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="38" stopIfTrue="1" operator="equal">
+      <formula>"35 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="89" priority="39" stopIfTrue="1" operator="equal">
+      <formula>"36 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="40" stopIfTrue="1" operator="equal">
+      <formula>"37 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="41" stopIfTrue="1" operator="equal">
+      <formula>"38 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="86" priority="42" stopIfTrue="1" operator="equal">
+      <formula>"39 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="43" stopIfTrue="1" operator="equal">
+      <formula>"40 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="44" stopIfTrue="1" operator="equal">
+      <formula>"41 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="45" stopIfTrue="1" operator="equal">
+      <formula>"42 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="46" stopIfTrue="1" operator="equal">
+      <formula>"43 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="47" stopIfTrue="1" operator="equal">
+      <formula>"44 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="48" stopIfTrue="1" operator="equal">
+      <formula>"45 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="49" stopIfTrue="1" operator="equal">
+      <formula>"46 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="50" stopIfTrue="1" operator="equal">
+      <formula>"47 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="77" priority="51" stopIfTrue="1" operator="equal">
+      <formula>"48 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="52" stopIfTrue="1" operator="equal">
+      <formula>"49 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="53" stopIfTrue="1" operator="equal">
+      <formula>"50 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="54" stopIfTrue="1" operator="equal">
+      <formula>"51 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="55" stopIfTrue="1" operator="equal">
+      <formula>"52 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="56" stopIfTrue="1" operator="equal">
+      <formula>"53 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="57" stopIfTrue="1" operator="equal">
+      <formula>"54 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="58" stopIfTrue="1" operator="equal">
+      <formula>"55 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="4" stopIfTrue="1" operator="equal">
+      <formula>"Today"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="68" priority="60" stopIfTrue="1" operator="equal">
+      <formula>"57 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="61" stopIfTrue="1" operator="equal">
+      <formula>"58 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="62" stopIfTrue="1" operator="equal">
+      <formula>"59 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="63" stopIfTrue="1" operator="equal">
+      <formula>"2 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="64" stopIfTrue="1" operator="equal">
+      <formula>"3 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="5" stopIfTrue="1" operator="equal">
+      <formula>"Yesterday"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="6" stopIfTrue="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="7" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="7" stopIfTrue="1" operator="equal">
       <formula>"4 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="8" stopIfTrue="1" operator="equal">
-      <formula>"5 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="9" stopIfTrue="1" operator="equal">
-      <formula>"6 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="10" stopIfTrue="1" operator="equal">
-      <formula>"7 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="11" stopIfTrue="1" operator="equal">
-      <formula>"8 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="12" stopIfTrue="1" operator="equal">
-      <formula>"9 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="13" stopIfTrue="1" operator="equal">
-      <formula>"10 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="14" stopIfTrue="1" operator="equal">
-      <formula>"11 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="15" stopIfTrue="1" operator="equal">
-      <formula>"12 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="16" stopIfTrue="1" operator="equal">
-      <formula>"13 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="17" stopIfTrue="1" operator="equal">
-      <formula>"14 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="18" stopIfTrue="1" operator="equal">
-      <formula>"15 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="19" stopIfTrue="1" operator="equal">
-      <formula>"16 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="20" stopIfTrue="1" operator="equal">
-      <formula>"17 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="21" stopIfTrue="1" operator="equal">
-      <formula>"18 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="22" stopIfTrue="1" operator="equal">
-      <formula>"19 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="23" stopIfTrue="1" operator="equal">
-      <formula>"20 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="24" stopIfTrue="1" operator="equal">
-      <formula>"21 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="25" stopIfTrue="1" operator="equal">
-      <formula>"22 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="26" stopIfTrue="1" operator="equal">
-      <formula>"23 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="27" stopIfTrue="1" operator="equal">
-      <formula>"24 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="28" stopIfTrue="1" operator="equal">
-      <formula>"25 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="29" stopIfTrue="1" operator="equal">
-      <formula>"26 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="30" stopIfTrue="1" operator="equal">
-      <formula>"27 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="31" stopIfTrue="1" operator="equal">
-      <formula>"28 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="32" stopIfTrue="1" operator="equal">
-      <formula>"29 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="33" stopIfTrue="1" operator="equal">
-      <formula>"30 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="34" stopIfTrue="1" operator="equal">
-      <formula>"31 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="35" stopIfTrue="1" operator="equal">
-      <formula>"32 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="36" stopIfTrue="1" operator="equal">
-      <formula>"33 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="37" stopIfTrue="1" operator="equal">
-      <formula>"34 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="38" stopIfTrue="1" operator="equal">
-      <formula>"35 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="39" stopIfTrue="1" operator="equal">
-      <formula>"36 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="40" stopIfTrue="1" operator="equal">
-      <formula>"37 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="41" stopIfTrue="1" operator="equal">
-      <formula>"38 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="42" stopIfTrue="1" operator="equal">
-      <formula>"39 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="43" stopIfTrue="1" operator="equal">
-      <formula>"40 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="44" stopIfTrue="1" operator="equal">
-      <formula>"41 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="45" stopIfTrue="1" operator="equal">
-      <formula>"42 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="46" stopIfTrue="1" operator="equal">
-      <formula>"43 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="47" stopIfTrue="1" operator="equal">
-      <formula>"44 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="48" stopIfTrue="1" operator="equal">
-      <formula>"45 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="49" stopIfTrue="1" operator="equal">
-      <formula>"46 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="4" stopIfTrue="1" operator="equal">
-      <formula>"Today"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="51" stopIfTrue="1" operator="equal">
-      <formula>"48 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="52" stopIfTrue="1" operator="equal">
-      <formula>"49 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="53" stopIfTrue="1" operator="equal">
-      <formula>"50 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="54" stopIfTrue="1" operator="equal">
-      <formula>"51 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="55" stopIfTrue="1" operator="equal">
-      <formula>"52 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="56" stopIfTrue="1" operator="equal">
-      <formula>"53 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="57" stopIfTrue="1" operator="equal">
-      <formula>"54 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="50" stopIfTrue="1" operator="equal">
-      <formula>"47 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="59" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="59" stopIfTrue="1" operator="equal">
       <formula>"56 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="60" stopIfTrue="1" operator="equal">
-      <formula>"57 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="61" stopIfTrue="1" operator="equal">
-      <formula>"58 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="62" stopIfTrue="1" operator="equal">
-      <formula>"59 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="63" stopIfTrue="1" operator="equal">
-      <formula>"2 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="64" stopIfTrue="1" operator="equal">
-      <formula>"3 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="5" stopIfTrue="1" operator="equal">
-      <formula>"Yesterday"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="58" stopIfTrue="1" operator="equal">
-      <formula>"55 days ago"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -5225,210 +5658,226 @@
     <col min="1" max="1" width="30.85546875" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" style="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="A1" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
-        <v>41</v>
+      <c r="A2" s="28" t="s">
+        <v>42</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="17"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="D3" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>46</v>
       </c>
+      <c r="F3" s="32" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>46313</v>
       </c>
-      <c r="E4" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="36" t="s">
+      <c r="E4" s="33" t="s">
         <v>49</v>
       </c>
+      <c r="F4" s="35" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>46316</v>
       </c>
-      <c r="E5" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="36"/>
+      <c r="E5" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>46317</v>
       </c>
-      <c r="E6" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="36"/>
+      <c r="E6" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="36"/>
+      <c r="A7" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="10">
+        <v>46319</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="36"/>
+      <c r="A8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="36"/>
+      <c r="A9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="36"/>
+      <c r="A10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="10">
+        <v>46319</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="36"/>
+      <c r="A11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="36"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="36"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="36"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="36"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="36"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="36"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
     </row>
     <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
@@ -5556,48 +6005,48 @@
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15" style="19" customWidth="1"/>
+    <col min="4" max="4" width="15" style="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="A1" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
-        <v>41</v>
+      <c r="A2" s="29" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="D3" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="F3" s="6" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>60</v>
+      <c r="A4" s="55" t="s">
+        <v>63</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -5608,16 +6057,16 @@
       <c r="D4" s="4">
         <v>46315</v>
       </c>
-      <c r="E4" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>62</v>
+      <c r="E4" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>63</v>
+      <c r="A5" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
@@ -5628,14 +6077,14 @@
       <c r="D5" s="4">
         <v>46318</v>
       </c>
-      <c r="E5" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="36"/>
+      <c r="E5" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
+      <c r="A6" s="31" t="s">
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
@@ -5646,120 +6095,116 @@
       <c r="D6" s="4">
         <v>46318</v>
       </c>
-      <c r="E6" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="36"/>
-    </row>
-    <row r="7" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>67</v>
+      <c r="E6" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="35"/>
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
+        <v>70</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="36"/>
-    </row>
-    <row r="8" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>68</v>
+      <c r="E7" s="37"/>
+      <c r="F7" s="35"/>
+    </row>
+    <row r="8" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
+        <v>71</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="36"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>69</v>
+      <c r="A9" s="31" t="s">
+        <v>72</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="36"/>
-    </row>
-    <row r="10" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>70</v>
+      <c r="E9" s="37"/>
+      <c r="F9" s="35"/>
+    </row>
+    <row r="10" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="56" t="s">
+        <v>73</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="36"/>
-    </row>
-    <row r="11" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>71</v>
+      <c r="E10" s="37"/>
+      <c r="F10" s="35"/>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="57" t="s">
+        <v>74</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="36"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="36"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="36"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="36"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="36"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="36"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="36"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="36"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5815,212 +6260,204 @@
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" style="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="A1" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>41</v>
+      <c r="A2" s="30" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="D3" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="F3" s="36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>46314</v>
       </c>
-      <c r="E4" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="36" t="s">
+      <c r="E4" s="33" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="F4" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="10" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>46316</v>
       </c>
-      <c r="E5" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="36"/>
-    </row>
-    <row r="6" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="E5" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="F5" s="35"/>
+    </row>
+    <row r="6" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>46316</v>
       </c>
-      <c r="E6" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="36"/>
-    </row>
-    <row r="7" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="36"/>
-    </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="E6" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="35"/>
+    </row>
+    <row r="7" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="36"/>
-    </row>
-    <row r="9" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="35"/>
+    </row>
+    <row r="8" spans="1:6" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="36"/>
-    </row>
-    <row r="10" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="35"/>
+    </row>
+    <row r="9" spans="1:6" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="36"/>
-    </row>
-    <row r="11" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="35"/>
+    </row>
+    <row r="10" spans="1:6" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="36"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="35"/>
+    </row>
+    <row r="11" spans="1:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="55"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="36"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="36"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="36"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="36"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="36"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="36"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6077,176 +6514,174 @@
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="20" style="19" customWidth="1"/>
+    <col min="4" max="4" width="20" style="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="73.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="A1" s="76" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>41</v>
+      <c r="A2" s="30" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="D3" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>46</v>
       </c>
+      <c r="F3" s="32" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="11">
-        <v>46316</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>92</v>
-      </c>
+      <c r="D4" s="10">
+        <v>46319</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="35"/>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="36"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="36"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="36"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="36"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="36"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="36"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="36"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="36"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="36"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="36"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="36"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="36"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="36"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6303,218 +6738,218 @@
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21" style="19" customWidth="1"/>
+    <col min="4" max="4" width="21" style="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46315</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="35"/>
+    </row>
+    <row r="5" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="10">
+        <v>46317</v>
+      </c>
+      <c r="E5" s="33"/>
+      <c r="F5" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="37" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="10">
+        <v>46311</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="35"/>
+    </row>
+    <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D7" s="10">
         <v>46315</v>
       </c>
-      <c r="E4" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="36"/>
-    </row>
-    <row r="5" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="E7" s="33"/>
+      <c r="F7" s="35"/>
+    </row>
+    <row r="8" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="11">
-        <v>46317</v>
-      </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="C8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="10">
+        <v>46315</v>
+      </c>
+      <c r="E8" s="33"/>
+      <c r="F8" s="35"/>
+    </row>
+    <row r="9" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="11">
-        <v>46311</v>
-      </c>
-      <c r="E6" s="34" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="35"/>
+    </row>
+    <row r="10" spans="1:6" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="36"/>
-    </row>
-    <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="35"/>
+    </row>
+    <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="11">
-        <v>46315</v>
-      </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="36"/>
-    </row>
-    <row r="8" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="35"/>
+    </row>
+    <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="11">
-        <v>46315</v>
-      </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="36"/>
-    </row>
-    <row r="9" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="36"/>
-    </row>
-    <row r="10" spans="1:6" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="36"/>
-    </row>
-    <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="36"/>
-    </row>
-    <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="36"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="36"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="36"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="36"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="36"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="36"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6571,184 +7006,184 @@
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" style="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="35"/>
+    </row>
+    <row r="5" spans="1:6" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="21">
+        <v>46318</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="35"/>
+    </row>
+    <row r="6" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="35"/>
+    </row>
+    <row r="7" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="36"/>
-    </row>
-    <row r="5" spans="1:6" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="35"/>
+    </row>
+    <row r="8" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="22">
-        <v>46318</v>
-      </c>
-      <c r="E5" s="34" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="35"/>
+    </row>
+    <row r="9" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="36"/>
-    </row>
-    <row r="6" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="36"/>
-    </row>
-    <row r="7" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="36"/>
-    </row>
-    <row r="8" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="36"/>
-    </row>
-    <row r="9" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="36"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="36"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="36"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="36"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="36"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="36"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="36"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="36"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="36"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6804,190 +7239,190 @@
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15" style="19" customWidth="1"/>
+    <col min="4" max="4" width="15" style="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="76" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46318</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="35"/>
+    </row>
+    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="35"/>
+    </row>
+    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="37" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="35"/>
+    </row>
+    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="35"/>
+    </row>
+    <row r="8" spans="1:6" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="11">
-        <v>46318</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="F4" s="36"/>
-    </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="D8" s="10">
+        <v>46315</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="36"/>
-    </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="36"/>
-    </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="36"/>
-    </row>
-    <row r="8" spans="1:6" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="11">
-        <v>46315</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="36"/>
+      <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="36"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="36"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="36"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="36"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="36"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="36"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="36"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="36"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="36"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7037,20 +7472,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0fb2ba46-83e9-4d91-a985-8245aaf43e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0fb2ba46-83e9-4d91-a985-8245aaf43e5c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7293,26 +7728,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9169F2-DC6F-440D-AA51-2EA02192DC48}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9169F2-DC6F-440D-AA51-2EA02192DC48}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/revision tracker/Revision_Tracker.xlsx
+++ b/revision tracker/Revision_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/948b5d172b360b34/Python Stuff/revision tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="315" documentId="8_{900DBA63-C4C7-4070-82C1-769B6A063F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55022C41-3E89-4F86-B1DF-3F3293683817}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{A39F0FEA-A077-4C04-94C8-53C0990EE409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{840672CC-BDBA-438B-819D-9155F731428A}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11565" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revision Timetable" sheetId="13" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="149">
   <si>
     <t>🗓️ Week 1 Timetable</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>Completed</t>
+  </si>
+  <si>
+    <t>Overall  %  Complete</t>
   </si>
   <si>
     <t>Amber</t>
@@ -443,7 +446,7 @@
     <t>Complete</t>
   </si>
   <si>
-    <t>Next session is GROUP 5</t>
+    <t>Next session is GROUP 4</t>
   </si>
   <si>
     <r>
@@ -912,14 +915,17 @@
     <t>Quotations and meaning for VFAB Characters - Eddie, Alfieri, Catherine, Rodolfo</t>
   </si>
   <si>
+    <t>1. finish of the quotations for Catherine and Rodolfo
+2. then get a quick overview on R+J and then revise the themes</t>
+  </si>
+  <si>
     <t>VFAB - Themes:  
 1. Different views of loyalty and honour
 2. Different views of justice
 3. Transition and change</t>
   </si>
   <si>
-    <t>finish the 2 quotations for transition and change 
-then start doing quotations for the characters</t>
+    <t>Just pray we get this 7 in english lit</t>
   </si>
   <si>
     <t>Practise planning and writing essays for VFAB</t>
@@ -943,9 +949,18 @@
     <t>Hazards</t>
   </si>
   <si>
-    <t>1. Complete the third revision sheet on the geography oaks page
-2. Do two 8 markers on this topic.
-3. little chatgpt quiz on primary and secondary hazards/impacts if time (optional)</t>
+    <t>1. breifly look at weaknesses
+2. complete 8 marker on hazards
+2. Complete coast section
+3. highlight weaknesses in coasts section and then go over them
+4. if time do the coasts 8 marker (I highly doubt we will get to this)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+WEAKNESSES:
+1. Tropical storm formation
+2. eathquakes forming tsunamis
+3. just take a brief look at vulnerabilty but its chill</t>
   </si>
   <si>
     <t>Economic Activity &amp; energy</t>
@@ -1168,6 +1183,9 @@
   <si>
     <t>Edit the interval numbers in column C to change how often topics come back.</t>
   </si>
+  <si>
+    <t>Current Week:</t>
+  </si>
 </sst>
 </file>
 
@@ -1176,7 +1194,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1425,8 +1443,31 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1504,12 +1545,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFF0F8FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1621,6 +1668,24 @@
         <color rgb="FFDCDCDC"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDCDCDC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDCDCDC"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FFDCDCDC"/>
       </top>
@@ -1656,28 +1721,50 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFD4EA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFBFD4EA"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFBFD4EA"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFBFD4EA"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFBFD4EA"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFD4EA"/>
+      </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFD4EA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F4E78"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1687,7 +1774,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1809,37 +1896,38 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="31" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="31" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="31" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="31" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="31" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1852,18 +1940,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1873,10 +1952,11 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1887,6 +1967,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="37" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="37" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1906,7 +2010,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="192">
+  <dxfs count="190">
     <dxf>
       <font>
         <b/>
@@ -2527,6 +2631,412 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
@@ -2540,449 +3050,32 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8B6B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF960000"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8B6B6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3211,30 +3304,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:F27" headerRowDxfId="191" dataDxfId="190" totalsRowDxfId="189">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:F27" headerRowDxfId="189" dataDxfId="188" totalsRowDxfId="187">
   <autoFilter ref="A3:F27" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="188"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="187"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="186"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="185"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="184"/>
-    <tableColumn id="5" xr3:uid="{F0BDA802-DA31-4BA7-81BA-FDB612DC37E1}" name="General Notes" dataDxfId="183" totalsRowDxfId="182"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="186"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="185"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="184"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="183"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="182"/>
+    <tableColumn id="5" xr3:uid="{F0BDA802-DA31-4BA7-81BA-FDB612DC37E1}" name="General Notes" dataDxfId="181" totalsRowDxfId="180"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="ComputerScienceTbl" displayName="ComputerScienceTbl" ref="A3:F18" headerRowDxfId="137" dataDxfId="136" totalsRowDxfId="135">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="ComputerScienceTbl" displayName="ComputerScienceTbl" ref="A3:F18" headerRowDxfId="135" dataDxfId="134" totalsRowDxfId="133">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Topic" dataDxfId="134"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Status" dataDxfId="133"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Confidence" dataDxfId="132"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Last Revised" dataDxfId="131"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Next Action" dataDxfId="130"/>
-    <tableColumn id="5" xr3:uid="{63D6C4F6-C7E6-4663-AE70-5CFDFF770C29}" name="General Notes" dataDxfId="129" totalsRowDxfId="128"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Topic" dataDxfId="132"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Status" dataDxfId="131"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Confidence" dataDxfId="130"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Last Revised" dataDxfId="129"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Next Action" dataDxfId="128"/>
+    <tableColumn id="5" xr3:uid="{63D6C4F6-C7E6-4663-AE70-5CFDFF770C29}" name="General Notes" dataDxfId="127" totalsRowDxfId="126"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3247,7 +3340,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="181"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="179"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{DB8974C0-4423-4F62-8CA0-D4A3FA4693EA}" name="General Notes"/>
   </tableColumns>
@@ -3256,75 +3349,75 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PhysicsTbl" displayName="PhysicsTbl" ref="A3:F18" dataDxfId="180">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PhysicsTbl" displayName="PhysicsTbl" ref="A3:F18" dataDxfId="178">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Topic" dataDxfId="179"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Status" dataDxfId="178"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Confidence" dataDxfId="177"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Last Revised" dataDxfId="176"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Next Action" dataDxfId="175"/>
-    <tableColumn id="5" xr3:uid="{2C5860E0-C42D-447A-99E8-019207F1E49B}" name="General Notes" dataDxfId="174"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Topic" dataDxfId="177"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Status" dataDxfId="176"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Confidence" dataDxfId="175"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Last Revised" dataDxfId="174"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Next Action" dataDxfId="173"/>
+    <tableColumn id="5" xr3:uid="{2C5860E0-C42D-447A-99E8-019207F1E49B}" name="General Notes" dataDxfId="172"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="MathematicsTbl" displayName="MathematicsTbl" ref="A3:F18" headerRowDxfId="173" dataDxfId="172" totalsRowDxfId="171">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="MathematicsTbl" displayName="MathematicsTbl" ref="A3:F18" headerRowDxfId="171" dataDxfId="170" totalsRowDxfId="169">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Topic" dataDxfId="170"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status" dataDxfId="169"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Confidence" dataDxfId="168"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Last Revised" dataDxfId="167"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Next Action" dataDxfId="166"/>
-    <tableColumn id="5" xr3:uid="{902E25C2-558C-4568-81EE-02B6DDE3EEEE}" name="General Notes" dataDxfId="165" totalsRowDxfId="164"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Topic" dataDxfId="168"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status" dataDxfId="167"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Confidence" dataDxfId="166"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Last Revised" dataDxfId="165"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Next Action" dataDxfId="164"/>
+    <tableColumn id="5" xr3:uid="{902E25C2-558C-4568-81EE-02B6DDE3EEEE}" name="General Notes" dataDxfId="163" totalsRowDxfId="162"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EnglishLanguageTbl" displayName="EnglishLanguageTbl" ref="A3:F18" dataDxfId="163">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="EnglishLanguageTbl" displayName="EnglishLanguageTbl" ref="A3:F18" dataDxfId="161">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Topic" dataDxfId="162"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Status" dataDxfId="161"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Confidence" dataDxfId="160"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Last Revised" dataDxfId="159"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Next Action" dataDxfId="158"/>
-    <tableColumn id="5" xr3:uid="{75D1410F-47BB-4A48-905A-25CF74BDB786}" name="General Notes" dataDxfId="157"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Topic" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Status" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Confidence" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Last Revised" dataDxfId="157"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Next Action" dataDxfId="156"/>
+    <tableColumn id="5" xr3:uid="{75D1410F-47BB-4A48-905A-25CF74BDB786}" name="General Notes" dataDxfId="155"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="EnglishLiteratureTbl" displayName="EnglishLiteratureTbl" ref="A3:F18" headerRowDxfId="156" dataDxfId="155" totalsRowDxfId="154">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="EnglishLiteratureTbl" displayName="EnglishLiteratureTbl" ref="A3:F18" headerRowDxfId="154" dataDxfId="153" totalsRowDxfId="152">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Topic" dataDxfId="153"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Status" dataDxfId="152"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Confidence" dataDxfId="151"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Last Revised" dataDxfId="150"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Next Action" dataDxfId="149"/>
-    <tableColumn id="5" xr3:uid="{930CE764-AB02-4790-8724-F5622F11644B}" name="General Notes" dataDxfId="148" totalsRowDxfId="147"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Topic" dataDxfId="151"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Status" dataDxfId="150"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Confidence" dataDxfId="149"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Last Revised" dataDxfId="148"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Next Action" dataDxfId="147"/>
+    <tableColumn id="5" xr3:uid="{930CE764-AB02-4790-8724-F5622F11644B}" name="General Notes" dataDxfId="146" totalsRowDxfId="145"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="GeographyTbl" displayName="GeographyTbl" ref="A3:F18" dataDxfId="146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="GeographyTbl" displayName="GeographyTbl" ref="A3:F18" dataDxfId="144">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Topic" dataDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Status" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Confidence" dataDxfId="143"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Last Revised" dataDxfId="142"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Next Action" dataDxfId="141"/>
-    <tableColumn id="5" xr3:uid="{27D2B179-C2A7-46A7-8BEB-752BF05A8E89}" name="General Notes" dataDxfId="140"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Topic" dataDxfId="143"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Status" dataDxfId="142"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Confidence" dataDxfId="141"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Last Revised" dataDxfId="140"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Next Action" dataDxfId="139"/>
+    <tableColumn id="5" xr3:uid="{27D2B179-C2A7-46A7-8BEB-752BF05A8E89}" name="General Notes" dataDxfId="138"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3337,7 +3430,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Last Revised" dataDxfId="139"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Last Revised" dataDxfId="137"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{28A5B818-9271-4E86-B3A0-50B7055F910C}" name="General Notes"/>
   </tableColumns>
@@ -3352,7 +3445,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Topic"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Status"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Last Revised" dataDxfId="138"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Last Revised" dataDxfId="136"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Next Action"/>
     <tableColumn id="5" xr3:uid="{7C8E7108-0749-49A2-855D-B734764E8E58}" name="General Notes"/>
   </tableColumns>
@@ -3934,60 +4027,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="4">
         <v>46317</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F4" s="35"/>
     </row>
     <row r="5" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3997,7 +4090,7 @@
     </row>
     <row r="6" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4162,62 +4255,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="82" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="4">
         <v>46317</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -4227,7 +4320,7 @@
     </row>
     <row r="6" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4237,7 +4330,7 @@
     </row>
     <row r="7" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -4393,42 +4486,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="81" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -4437,8 +4530,8 @@
       <c r="F4" s="35"/>
     </row>
     <row r="5" spans="1:6" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
-        <v>132</v>
+      <c r="A5" s="57" t="s">
+        <v>135</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -4447,8 +4540,8 @@
       <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
-        <v>133</v>
+      <c r="A6" s="57" t="s">
+        <v>136</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -4457,44 +4550,44 @@
       <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="56" t="s">
-        <v>134</v>
+      <c r="A7" s="57" t="s">
+        <v>137</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="10">
         <v>46315</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="10">
         <v>46318</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -4633,30 +4726,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="79" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
+      <c r="B2" s="84" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
     </row>
     <row r="4" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="65" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
+      <c r="B4" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
     </row>
     <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -4664,7 +4757,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3">
         <v>3</v>
@@ -4672,7 +4765,7 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3">
         <v>6</v>
@@ -4680,18 +4773,18 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="78" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
+      <c r="B12" s="83" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4705,32 +4798,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD100"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="14" max="14" width="13" hidden="1" customWidth="1"/>
     <col min="27" max="30" width="2.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
       <c r="N1" t="s">
         <v>26</v>
       </c>
@@ -4741,14 +4834,14 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
       <c r="N3" t="s">
         <v>14</v>
       </c>
@@ -4758,7 +4851,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -4771,31 +4864,40 @@
       <c r="G5" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="I5" s="72" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="73"/>
       <c r="N5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="72">
+    <row r="6" spans="1:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="69">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*"))</f>
         <v>57</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="74">
+      <c r="B6" s="67"/>
+      <c r="C6" s="71">
         <f ca="1">A6-E6-G6</f>
-        <v>33</v>
-      </c>
-      <c r="D6" s="69"/>
-      <c r="E6" s="73">
+        <v>32</v>
+      </c>
+      <c r="D6" s="67"/>
+      <c r="E6" s="70">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"In Progress"))</f>
         <v>6</v>
       </c>
-      <c r="F6" s="69"/>
-      <c r="G6" s="68">
+      <c r="F6" s="67"/>
+      <c r="G6" s="64">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"Completed"))</f>
-        <v>18</v>
-      </c>
-      <c r="H6" s="69"/>
+        <v>19</v>
+      </c>
+      <c r="H6" s="65"/>
+      <c r="I6" s="74">
+        <f t="shared" ref="I6" ca="1" si="0">IFERROR(SUM(G6)/SUM(A6), 0)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J6" s="75"/>
       <c r="N6" t="s">
         <v>16</v>
       </c>
@@ -4807,26 +4909,26 @@
     </row>
     <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="71">
+      <c r="A9" s="68">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Amber"))</f>
-        <v>5</v>
-      </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="70">
+        <v>6</v>
+      </c>
+      <c r="B9" s="67"/>
+      <c r="C9" s="66">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Red"))</f>
         <v>1</v>
       </c>
-      <c r="D9" s="69"/>
+      <c r="D9" s="67"/>
       <c r="N9" t="s">
         <v>10</v>
       </c>
@@ -4842,23 +4944,23 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="65" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
+      <c r="A12" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
     </row>
     <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>29</v>
@@ -4870,19 +4972,19 @@
         <v>31</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" s="45" t="s">
+      <c r="H13" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="49" t="s">
         <v>39</v>
+      </c>
+      <c r="J13" s="46" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4894,7 +4996,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="23">
-        <f t="shared" ref="C14:C23" ca="1" si="0">B14-D14-E14</f>
+        <f t="shared" ref="C14:C23" ca="1" si="1">B14-D14-E14</f>
         <v>3</v>
       </c>
       <c r="D14" s="23">
@@ -4913,17 +5015,17 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="47">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*",INDIRECT("'Biology'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I14" s="52">
-        <f t="shared" ref="I14:I23" ca="1" si="1">IFERROR(E14/B14, 0)</f>
+      <c r="I14" s="53">
+        <f t="shared" ref="I14:I23" ca="1" si="2">IFERROR(E14/B14, 0)</f>
         <v>0.625</v>
       </c>
-      <c r="J14" s="47" t="str">
+      <c r="J14" s="48" t="str">
         <f ca="1">IF(MAX(Biology!D4:D1000)=0, "-", IF(MAX(Biology!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Biology!D4:D1000)=1, "Yesterday", TODAY()-MAX(Biology!D4:D1000) &amp; " days ago")))</f>
-        <v>Today</v>
+        <v>3 days ago</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4935,7 +5037,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="25">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
       <c r="D15" s="25">
@@ -4954,17 +5056,17 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H15" s="50">
+      <c r="H15" s="51">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="53">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I15" s="54">
+        <f t="shared" ca="1" si="2"/>
         <v>0.375</v>
       </c>
-      <c r="J15" s="51" t="str">
+      <c r="J15" s="52" t="str">
         <f ca="1">IF(MAX(Chemistry!D4:D1000)=0, "N/A", IF(MAX(Chemistry!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Chemistry!D4:D1000)=1, "Yesterday", TODAY()-MAX(Chemistry!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
+        <v>4 days ago</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4976,7 +5078,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="23">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
       <c r="D16" s="23">
@@ -4995,17 +5097,17 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H16" s="46">
+      <c r="H16" s="47">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I16" s="52">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I16" s="53">
+        <f t="shared" ca="1" si="2"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="J16" s="47" t="str">
+      <c r="J16" s="48" t="str">
         <f ca="1">IF(MAX(Physics!D4:D1000)=0, "-", IF(MAX(Physics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Physics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Physics!D4:D1000) &amp; " days ago")))</f>
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5017,7 +5119,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="25">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="D17" s="25">
@@ -5036,17 +5138,17 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H17" s="50">
+      <c r="H17" s="51">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Mathematics'!A4:A1000"),"?*",INDIRECT("'Mathematics'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I17" s="53">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I17" s="54">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="J17" s="51" t="str">
+      <c r="J17" s="52" t="str">
         <f ca="1">IF(MAX(Mathematics!D4:D1000)=0, "-", IF(MAX(Mathematics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Mathematics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Mathematics!D4:D1000) &amp; " days ago")))</f>
-        <v>Today</v>
+        <v>3 days ago</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5058,7 +5160,7 @@
         <v>9</v>
       </c>
       <c r="C18" s="23">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
       <c r="D18" s="23">
@@ -5077,17 +5179,17 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Amber"))</f>
         <v>3</v>
       </c>
-      <c r="H18" s="46">
+      <c r="H18" s="47">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Red"))</f>
         <v>1</v>
       </c>
-      <c r="I18" s="52">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I18" s="53">
+        <f t="shared" ca="1" si="2"/>
         <v>0.55555555555555558</v>
       </c>
-      <c r="J18" s="47" t="str">
+      <c r="J18" s="48" t="str">
         <f ca="1">IF(MAX('English Language'!D4:D1000)=0, "-", IF(MAX('English Language'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Language'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Language'!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5099,8 +5201,8 @@
         <v>6</v>
       </c>
       <c r="C19" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
       </c>
       <c r="D19" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!B4:B1000"),"In Progress"))</f>
@@ -5108,7 +5210,7 @@
       </c>
       <c r="E19" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!B4:B1000"),"Completed"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Green"))</f>
@@ -5116,17 +5218,17 @@
       </c>
       <c r="G19" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Amber"))</f>
-        <v>1</v>
-      </c>
-      <c r="H19" s="50">
+        <v>2</v>
+      </c>
+      <c r="H19" s="51">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Literature'!A4:A1000"),"?*",INDIRECT("'English Literature'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I19" s="53">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="51" t="str">
+      <c r="I19" s="54">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="J19" s="52" t="str">
         <f ca="1">IF(MAX('English Literature'!D4:D1000)=0, "-", IF(MAX('English Literature'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Literature'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Literature'!D4:D1000) &amp; " days ago")))</f>
         <v>Yesterday</v>
       </c>
@@ -5140,7 +5242,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="23">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>3</v>
       </c>
       <c r="D20" s="23">
@@ -5159,17 +5261,17 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H20" s="46">
+      <c r="H20" s="47">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Geography'!A4:A1000"),"?*",INDIRECT("'Geography'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I20" s="52">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I20" s="53">
+        <f t="shared" ca="1" si="2"/>
         <v>0.2</v>
       </c>
-      <c r="J20" s="47" t="str">
+      <c r="J20" s="48" t="str">
         <f ca="1">IF(MAX(Geography!D4:D1000)=0, "-", IF(MAX(Geography!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Geography!D4:D1000)=1, "Yesterday", TODAY()-MAX(Geography!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
+        <v>Today</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5181,7 +5283,7 @@
         <v>3</v>
       </c>
       <c r="C21" s="25">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
       <c r="D21" s="25">
@@ -5200,17 +5302,17 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="50">
+      <c r="H21" s="51">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'History'!A4:A1000"),"?*",INDIRECT("'History'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I21" s="53">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I21" s="54">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="51" t="str">
+      <c r="J21" s="52" t="str">
         <f ca="1">IF(MAX(History!D4:D1000)=0, "-", IF(MAX(History!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(History!D4:D1000)=1, "Yesterday", TODAY()-MAX(History!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5222,7 +5324,7 @@
         <v>4</v>
       </c>
       <c r="C22" s="23">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>3</v>
       </c>
       <c r="D22" s="23">
@@ -5241,17 +5343,17 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!C4:C1000"),"Amber"))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="46">
+      <c r="H22" s="47">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Spanish'!A4:A1000"),"?*",INDIRECT("'Spanish'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I22" s="52">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I22" s="53">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="J22" s="47" t="str">
+      <c r="J22" s="48" t="str">
         <f ca="1">IF(MAX(Spanish!D4:D1000)=0, "-", IF(MAX(Spanish!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Spanish!D4:D1000)=1, "Yesterday", TODAY()-MAX(Spanish!D4:D1000) &amp; " days ago")))</f>
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5263,7 +5365,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="25">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
       <c r="D23" s="25">
@@ -5282,64 +5384,72 @@
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Amber"))</f>
         <v>1</v>
       </c>
-      <c r="H23" s="50">
+      <c r="H23" s="51">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Red"))</f>
         <v>0</v>
       </c>
-      <c r="I23" s="49">
-        <f t="shared" ca="1" si="1"/>
+      <c r="I23" s="50">
+        <f t="shared" ca="1" si="2"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="J23" s="51" t="str">
+      <c r="J23" s="52" t="str">
         <f ca="1">IF(MAX('Computer Science'!D4:D1000)=0, "-", IF(MAX('Computer Science'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('Computer Science'!D4:D1000)=1, "Yesterday", TODAY()-MAX('Computer Science'!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
+        <v>4 days ago</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A24" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="60">
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="62" t="s">
+      <c r="A26" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62" t="s">
+      <c r="B26" s="76"/>
+      <c r="C26" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62" t="s">
+      <c r="D26" s="76"/>
+      <c r="E26" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62" t="s">
+      <c r="F26" s="76"/>
+      <c r="G26" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="H26" s="62"/>
-      <c r="I26" s="43"/>
+      <c r="H26" s="76"/>
+      <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="64" t="str">
-        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)), "-")</f>
+      <c r="A27" s="77" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)), "-")</f>
         <v>Biology</v>
       </c>
-      <c r="B27" s="64"/>
-      <c r="C27" s="64" t="str">
-        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)), "-")</f>
-        <v>Mathematics</v>
-      </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="63" t="str">
-        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63" t="str">
-        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)&amp;"'!A4", INDEX('Revision Timetable'!B2:E8, MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="H27" s="63"/>
+      <c r="B27" s="79"/>
+      <c r="C27" s="77" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)), "-")</f>
+        <v>English Language</v>
+      </c>
+      <c r="D27" s="79"/>
+      <c r="E27" s="77" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)), "-")</f>
+        <v>Chemistry</v>
+      </c>
+      <c r="F27" s="79"/>
+      <c r="G27" s="77" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)), "-")</f>
+        <v>Spanish</v>
+      </c>
+      <c r="H27" s="78"/>
       <c r="AA27" s="42" t="b">
         <f ca="1">IFERROR(VLOOKUP(A27, $A$13:$J$23, 9, FALSE)="Today", FALSE)</f>
         <v>0</v>
@@ -5358,48 +5468,33 @@
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" s="58" t="str">
+      <c r="A28" s="43" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, A27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
-        <v>DONE</v>
-      </c>
-      <c r="B28" s="59"/>
-      <c r="C28" s="58" t="str">
+        <v>NOT DONE</v>
+      </c>
+      <c r="C28" s="43" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, C27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
-        <v>DONE</v>
-      </c>
-      <c r="D28" s="59"/>
-      <c r="E28" s="60" t="str">
+        <v>NOT DONE</v>
+      </c>
+      <c r="E28" s="43" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, E27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
         <v>NOT DONE</v>
       </c>
-      <c r="F28" s="61"/>
-      <c r="G28" s="60" t="str">
+      <c r="G28" s="43" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, G27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
         <v>NOT DONE</v>
       </c>
-      <c r="H28" s="61"/>
-    </row>
-    <row r="99" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" t="str">
-        <f ca="1">IFERROR(INDEX($J$6:$J$15, MATCH(A27, $A$6:$A$15, 0)), "-")</f>
-        <v>Today</v>
-      </c>
-      <c r="C100" t="str">
-        <f ca="1">IFERROR(INDEX($J$6:$J$15, MATCH(C27, $A$6:$A$15, 0)), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="E100" t="str">
-        <f ca="1">IFERROR(INDEX($J$6:$J$15, MATCH(E27, $A$6:$A$15, 0)), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="G100" t="str">
-        <f ca="1">IFERROR(INDEX($J$6:$J$15, MATCH(G27, $A$6:$A$15, 0)), "-")</f>
-        <v>-</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A3:F3"/>
@@ -5409,29 +5504,15 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
   </mergeCells>
-  <conditionalFormatting sqref="A27">
-    <cfRule type="cellIs" dxfId="127" priority="72" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="A27:H27">
+    <cfRule type="cellIs" dxfId="125" priority="72" stopIfTrue="1" operator="equal">
       <formula>"""DONE"""</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27:H28">
-    <cfRule type="expression" dxfId="126" priority="75" stopIfTrue="1">
-      <formula>A100="-"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="125" priority="73" stopIfTrue="1">
-      <formula>A100="Today"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="124" priority="74" stopIfTrue="1">
-      <formula>AND(A100&lt;&gt;"Today", A100&lt;&gt;"-")</formula>
+    <cfRule type="cellIs" dxfId="124" priority="71" stopIfTrue="1" operator="equal">
+      <formula>"""NOT DONE"""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F23">
@@ -5450,190 +5531,195 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14:J23">
-    <cfRule type="cellIs" dxfId="120" priority="8" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="6" stopIfTrue="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="119" priority="7" stopIfTrue="1" operator="equal">
+      <formula>"4 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="8" stopIfTrue="1" operator="equal">
       <formula>"5 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="9" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="9" stopIfTrue="1" operator="equal">
       <formula>"6 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="10" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="10" stopIfTrue="1" operator="equal">
       <formula>"7 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="11" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="11" stopIfTrue="1" operator="equal">
       <formula>"8 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="12" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="12" stopIfTrue="1" operator="equal">
       <formula>"9 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="13" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="13" stopIfTrue="1" operator="equal">
       <formula>"10 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="14" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="14" stopIfTrue="1" operator="equal">
       <formula>"11 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="15" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="15" stopIfTrue="1" operator="equal">
       <formula>"12 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="16" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="16" stopIfTrue="1" operator="equal">
       <formula>"13 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="17" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="17" stopIfTrue="1" operator="equal">
       <formula>"14 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="18" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="18" stopIfTrue="1" operator="equal">
       <formula>"15 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="19" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="19" stopIfTrue="1" operator="equal">
       <formula>"16 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="20" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="20" stopIfTrue="1" operator="equal">
       <formula>"17 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="21" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="21" stopIfTrue="1" operator="equal">
       <formula>"18 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="22" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="22" stopIfTrue="1" operator="equal">
       <formula>"19 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="23" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="23" stopIfTrue="1" operator="equal">
       <formula>"20 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="24" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="24" stopIfTrue="1" operator="equal">
       <formula>"21 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="25" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="25" stopIfTrue="1" operator="equal">
       <formula>"22 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="26" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="26" stopIfTrue="1" operator="equal">
       <formula>"23 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="27" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="27" stopIfTrue="1" operator="equal">
       <formula>"24 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="28" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="28" stopIfTrue="1" operator="equal">
       <formula>"25 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="29" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="29" stopIfTrue="1" operator="equal">
       <formula>"26 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="30" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="30" stopIfTrue="1" operator="equal">
       <formula>"27 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="31" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="31" stopIfTrue="1" operator="equal">
       <formula>"28 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="32" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="32" stopIfTrue="1" operator="equal">
       <formula>"29 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="33" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="33" stopIfTrue="1" operator="equal">
       <formula>"30 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="34" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="34" stopIfTrue="1" operator="equal">
       <formula>"31 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="35" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="35" stopIfTrue="1" operator="equal">
       <formula>"32 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="36" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="36" stopIfTrue="1" operator="equal">
       <formula>"33 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="37" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="37" stopIfTrue="1" operator="equal">
       <formula>"34 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="38" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="38" stopIfTrue="1" operator="equal">
       <formula>"35 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="39" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="39" stopIfTrue="1" operator="equal">
       <formula>"36 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="40" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="40" stopIfTrue="1" operator="equal">
       <formula>"37 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="41" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="41" stopIfTrue="1" operator="equal">
       <formula>"38 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="42" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="42" stopIfTrue="1" operator="equal">
       <formula>"39 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="43" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="43" stopIfTrue="1" operator="equal">
       <formula>"40 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="44" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="44" stopIfTrue="1" operator="equal">
       <formula>"41 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="45" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="45" stopIfTrue="1" operator="equal">
       <formula>"42 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="46" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="46" stopIfTrue="1" operator="equal">
       <formula>"43 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="47" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="47" stopIfTrue="1" operator="equal">
       <formula>"44 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="48" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="48" stopIfTrue="1" operator="equal">
       <formula>"45 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="49" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="49" stopIfTrue="1" operator="equal">
       <formula>"46 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="50" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="4" stopIfTrue="1" operator="equal">
+      <formula>"Today"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="51" stopIfTrue="1" operator="equal">
+      <formula>"48 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="52" stopIfTrue="1" operator="equal">
+      <formula>"49 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="53" stopIfTrue="1" operator="equal">
+      <formula>"50 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="54" stopIfTrue="1" operator="equal">
+      <formula>"51 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="55" stopIfTrue="1" operator="equal">
+      <formula>"52 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="56" stopIfTrue="1" operator="equal">
+      <formula>"53 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="57" stopIfTrue="1" operator="equal">
+      <formula>"54 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="68" priority="50" stopIfTrue="1" operator="equal">
       <formula>"47 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="51" stopIfTrue="1" operator="equal">
-      <formula>"48 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="52" stopIfTrue="1" operator="equal">
-      <formula>"49 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="53" stopIfTrue="1" operator="equal">
-      <formula>"50 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="54" stopIfTrue="1" operator="equal">
-      <formula>"51 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="55" stopIfTrue="1" operator="equal">
-      <formula>"52 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="56" stopIfTrue="1" operator="equal">
-      <formula>"53 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="57" stopIfTrue="1" operator="equal">
-      <formula>"54 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="58" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="59" stopIfTrue="1" operator="equal">
+      <formula>"56 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="60" stopIfTrue="1" operator="equal">
+      <formula>"57 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="61" stopIfTrue="1" operator="equal">
+      <formula>"58 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="62" stopIfTrue="1" operator="equal">
+      <formula>"59 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="63" stopIfTrue="1" operator="equal">
+      <formula>"2 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="64" stopIfTrue="1" operator="equal">
+      <formula>"3 days ago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="5" stopIfTrue="1" operator="equal">
+      <formula>"Yesterday"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="58" stopIfTrue="1" operator="equal">
       <formula>"55 days ago"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="4" stopIfTrue="1" operator="equal">
-      <formula>"Today"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="60" stopIfTrue="1" operator="equal">
-      <formula>"57 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="61" stopIfTrue="1" operator="equal">
-      <formula>"58 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="62" stopIfTrue="1" operator="equal">
-      <formula>"59 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="63" stopIfTrue="1" operator="equal">
-      <formula>"2 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="64" stopIfTrue="1" operator="equal">
-      <formula>"3 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="5" stopIfTrue="1" operator="equal">
-      <formula>"Yesterday"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="6" stopIfTrue="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="7" stopIfTrue="1" operator="equal">
-      <formula>"4 days ago"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="59" stopIfTrue="1" operator="equal">
-      <formula>"56 days ago"</formula>
-    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24" xr:uid="{85B2A4AA-0944-47D2-80C2-DA47B61323AE}">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="A14" location="'Biology'!A4" display="Biology" xr:uid="{0349109F-4BAF-4BDF-8B1C-9AE599A8D6EC}"/>
     <hyperlink ref="A15" location="'Chemistry'!A4" display="Chemistry" xr:uid="{E53CEB35-8360-4491-9D51-BE05A96C3677}"/>
@@ -5647,6 +5733,7 @@
     <hyperlink ref="A23" location="'Computer Science'!A4" display="Computer Science" xr:uid="{3C3204D2-FCC7-4B44-8E31-E949073AD937}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5664,17 +5751,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="80" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5683,101 +5770,101 @@
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="10">
         <v>46313</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="10">
         <v>46316</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="10">
         <v>46317</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="10">
         <v>46319</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -5787,7 +5874,7 @@
     </row>
     <row r="9" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -5797,25 +5884,25 @@
     </row>
     <row r="10" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="10">
         <v>46319</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -6011,98 +6098,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="81" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="55" t="s">
-        <v>63</v>
+      <c r="A4" s="56" t="s">
+        <v>64</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="4">
         <v>46315</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="4">
         <v>46318</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="4">
         <v>46318</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -6112,7 +6199,7 @@
     </row>
     <row r="8" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -6122,7 +6209,7 @@
     </row>
     <row r="9" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -6131,8 +6218,8 @@
       <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="56" t="s">
-        <v>73</v>
+      <c r="A10" s="57" t="s">
+        <v>74</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -6141,8 +6228,8 @@
       <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="57" t="s">
-        <v>74</v>
+      <c r="A11" s="58" t="s">
+        <v>75</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -6266,98 +6353,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="10">
         <v>46314</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="10">
         <v>46316</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="54" t="s">
-        <v>81</v>
+      <c r="A6" s="55" t="s">
+        <v>82</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="10">
         <v>46316</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
-        <v>82</v>
+      <c r="A7" s="56" t="s">
+        <v>83</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -6366,8 +6453,8 @@
       <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="55" t="s">
-        <v>83</v>
+      <c r="A8" s="56" t="s">
+        <v>84</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -6376,8 +6463,8 @@
       <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
-        <v>84</v>
+      <c r="A9" s="56" t="s">
+        <v>85</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -6386,8 +6473,8 @@
       <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="55" t="s">
-        <v>85</v>
+      <c r="A10" s="56" t="s">
+        <v>86</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -6396,7 +6483,7 @@
       <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
+      <c r="A11" s="56"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="10"/>
@@ -6520,54 +6607,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="81" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="10">
         <v>46319</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F4" s="35"/>
     </row>
@@ -6744,102 +6831,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="82" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="10">
         <v>46315</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F4" s="35"/>
     </row>
     <row r="5" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="10">
         <v>46317</v>
       </c>
       <c r="E5" s="33"/>
       <c r="F5" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="10">
         <v>46311</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="10">
         <v>46315</v>
@@ -6849,13 +6936,13 @@
     </row>
     <row r="8" spans="1:6" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="10">
         <v>46315</v>
@@ -6865,7 +6952,7 @@
     </row>
     <row r="9" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -6875,7 +6962,7 @@
     </row>
     <row r="10" spans="1:6" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -6885,7 +6972,7 @@
     </row>
     <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -6895,7 +6982,7 @@
     </row>
     <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -7012,70 +7099,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="81" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="33"/>
+        <v>104</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46321</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>105</v>
+      </c>
       <c r="F4" s="35"/>
     </row>
     <row r="5" spans="1:6" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="21">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -7085,7 +7180,7 @@
     </row>
     <row r="7" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -7095,7 +7190,7 @@
     </row>
     <row r="8" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -7105,7 +7200,7 @@
     </row>
     <row r="9" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -7245,60 +7340,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="81" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="10">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="F4" s="35"/>
+        <v>114</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -7308,7 +7405,7 @@
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -7318,7 +7415,7 @@
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -7328,19 +7425,19 @@
     </row>
     <row r="8" spans="1:6" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="10">
         <v>46315</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F8" s="35"/>
     </row>
@@ -7472,23 +7569,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0fb2ba46-83e9-4d91-a985-8245aaf43e5c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006E3655B0D4A3F946B2B182A2452821C6" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7a9e24b6dc8563a5b2c5318cfdd77097">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0fb2ba46-83e9-4d91-a985-8245aaf43e5c" xmlns:ns4="ed8dfb7b-01af-4433-b4cc-631574050608" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b443fa188f0c7e58c89b943786fc45fd" ns3:_="" ns4:_="">
     <xsd:import namespace="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
@@ -7727,32 +7807,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9169F2-DC6F-440D-AA51-2EA02192DC48}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0fb2ba46-83e9-4d91-a985-8245aaf43e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2D1D04-17F3-4DB1-A413-D2712C8E335E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7769,4 +7841,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9169F2-DC6F-440D-AA51-2EA02192DC48}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
+    <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/revision tracker/Revision_Tracker.xlsx
+++ b/revision tracker/Revision_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/948b5d172b360b34/Python Stuff/revision tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{A39F0FEA-A077-4C04-94C8-53C0990EE409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{840672CC-BDBA-438B-819D-9155F731428A}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{DA7A25D8-0A89-48D5-BAF7-5DAE5CAD8422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D375555B-8178-4D67-80B0-879BEDF53A20}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revision Timetable" sheetId="13" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="154">
   <si>
     <t>🗓️ Week 1 Timetable</t>
   </si>
@@ -104,12 +104,12 @@
     <t>English Language</t>
   </si>
   <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
     <t>Biology</t>
   </si>
   <si>
-    <t>Wednesday</t>
-  </si>
-  <si>
     <t>Mathematics</t>
   </si>
   <si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>Last Revised</t>
+  </si>
+  <si>
+    <t>Current Week:</t>
   </si>
   <si>
     <t>🎯 Today's Focus</t>
@@ -446,9 +449,6 @@
     <t>Complete</t>
   </si>
   <si>
-    <t>Next session is GROUP 4</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -517,9 +517,11 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Inorganic Chem part 2 - 1e - 1g
-Rates of Reaction</t>
+      <t>Inorganic Chem part 2 - 1e - 1g</t>
     </r>
+  </si>
+  <si>
+    <t>chill. there was a little friction but i smoothed it out and know the topic well</t>
   </si>
   <si>
     <r>
@@ -622,7 +624,7 @@
     <t>When doing a review session just do a little chatgpt quiz to finish up the rest of this topic.</t>
   </si>
   <si>
-    <t>Lets do GROUP 4 NEXT. HOPEFULLY ITS CHILL SPEND 1 HOUR ON THIS</t>
+    <t>Lets do GROUP 5 NEXT. HOPEFULLY ITS CHILL SPEND 1 HOUR ON THIS</t>
   </si>
   <si>
     <r>
@@ -693,6 +695,9 @@
     </r>
   </si>
   <si>
+    <t>It was chill just when you have time do some exam questions on it</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -791,10 +796,6 @@
       </rPr>
       <t xml:space="preserve"> Annotation and practise questions</t>
     </r>
-  </si>
-  <si>
-    <t>1. Do a couple of questions for each anthology
-2. Do a past language paper on firefly. Go to the english page then go to paper 1 overviews</t>
   </si>
   <si>
     <r>
@@ -820,8 +821,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Next task:
-Do january 2022 paper on firefly:
+    <t xml:space="preserve">
 </t>
   </si>
   <si>
@@ -848,9 +848,6 @@
     </r>
   </si>
   <si>
-    <t>Man this was not easy. Try use chatgpt to show you how to answer these questions and then try to actually get better answers. Complete 1 question from each section then move onto a new topic. Man this ain't easy.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -909,6 +906,13 @@
     <t>Transactional Writing Practise: Letter</t>
   </si>
   <si>
+    <t>Past paper practise</t>
+  </si>
+  <si>
+    <t>1. plan that 22 marker. Use chatgpt for help
+2. then write the 22 marker</t>
+  </si>
+  <si>
     <t xml:space="preserve">  English Literature</t>
   </si>
   <si>
@@ -984,11 +988,17 @@
     <t>America 1918 - 1941</t>
   </si>
   <si>
-    <t xml:space="preserve">read up on the whole of Section 3 and 4. Just spend the whole session catching up on that its very likely you won't do any questions on it
-</t>
+    <t>1. Do the 8 marker on the New Deal
+2. Do the 6 marker on Huey Long
+3. MOVE ON TO CIVIL RIGHTS</t>
   </si>
   <si>
     <t>US Civil Rights</t>
+  </si>
+  <si>
+    <t>BLITZ THROUGH THE WHOLE CIVIL RIGHTS ON CHATGPT.
+NO QUESTIONS JUST PURE KNOWLEDGE ABSORBTION
+YOU MUST COMPLETE THIS IN THE NEXT SESSION</t>
   </si>
   <si>
     <t>History of Medicine</t>
@@ -1044,6 +1054,10 @@
     </r>
   </si>
   <si>
+    <t>Next up we are doing group 1 and group 3. 
+Read up notes on pmt or chatgpt. then do a big chatgpt quiz. Shouldn't be too difficult</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1137,11 +1151,12 @@
     </r>
   </si>
   <si>
-    <t>1. finish learning merge sort
-2. remind your self of the file handling stuff
-3. do some questions from a pmt algorithms paper
-4. do some questions from a pmt programming fundamentals paper
-5. highlight any gaps in knowledge</t>
+    <t>coding stuff is fine. just nearer to the exam make sure you're good on merge and insertion sort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Otherwise all good.
+and also make sure you know what abstraction and decomposition are</t>
   </si>
   <si>
     <r>
@@ -1184,7 +1199,8 @@
     <t>Edit the interval numbers in column C to change how often topics come back.</t>
   </si>
   <si>
-    <t>Current Week:</t>
+    <t>Next session is GROUP 5. you need to get this section done in whole. Doesn't matter if you go over an hour just finish it.
+1. Read the notes for both on onenote then bang out questions for them also on onenote. Should be chill</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1210,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1466,8 +1482,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1555,8 +1579,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1768,13 +1816,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF1F4E78"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF1F4E78"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1939,10 +2005,12 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1953,16 +2021,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1979,6 +2047,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="37" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2004,13 +2078,22 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="20" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent5" xfId="2" builtinId="45"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="190">
+  <dxfs count="196">
     <dxf>
       <font>
         <b/>
@@ -3257,7 +3340,26 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -3304,15 +3406,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:F27" headerRowDxfId="189" dataDxfId="188" totalsRowDxfId="187">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BiologyTbl" displayName="BiologyTbl" ref="A3:F27" headerRowDxfId="195" dataDxfId="194" totalsRowDxfId="193">
   <autoFilter ref="A3:F27" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="186"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="185"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="184"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="183"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="182"/>
-    <tableColumn id="5" xr3:uid="{F0BDA802-DA31-4BA7-81BA-FDB612DC37E1}" name="General Notes" dataDxfId="181" totalsRowDxfId="180"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Topic" dataDxfId="192"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Status" dataDxfId="191"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Confidence" dataDxfId="190"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Revised" dataDxfId="189"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Next Action" dataDxfId="188"/>
+    <tableColumn id="5" xr3:uid="{F0BDA802-DA31-4BA7-81BA-FDB612DC37E1}" name="General Notes" dataDxfId="187" totalsRowDxfId="186"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3334,15 +3436,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ChemistryTbl" displayName="ChemistryTbl" ref="A3:F18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ChemistryTbl" displayName="ChemistryTbl" ref="A3:F18" dataDxfId="185">
   <autoFilter ref="A3:F18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Topic"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Status"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Confidence"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="179"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Next Action"/>
-    <tableColumn id="5" xr3:uid="{DB8974C0-4423-4F62-8CA0-D4A3FA4693EA}" name="General Notes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Topic" dataDxfId="184"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Status" dataDxfId="183"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Confidence" dataDxfId="182"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Last Revised" dataDxfId="181"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Next Action" dataDxfId="180"/>
+    <tableColumn id="5" xr3:uid="{DB8974C0-4423-4F62-8CA0-D4A3FA4693EA}" name="General Notes" dataDxfId="179"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3837,24 +3939,24 @@
         <v>13</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4" s="41" t="s">
         <v>14</v>
       </c>
       <c r="K4" s="41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="40" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>17</v>
       </c>
       <c r="C5" s="40" t="s">
         <v>9</v>
@@ -3866,19 +3968,19 @@
         <v>8</v>
       </c>
       <c r="G5" s="40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H5" s="40" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J5" s="40" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K5" s="40" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3892,7 +3994,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="41" t="s">
         <v>11</v>
@@ -3904,7 +4006,7 @@
         <v>16</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="41" t="s">
         <v>11</v>
@@ -3950,7 +4052,7 @@
         <v>22</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>19</v>
@@ -3965,7 +4067,7 @@
         <v>22</v>
       </c>
       <c r="H8" s="41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="41" t="s">
         <v>12</v>
@@ -4027,8 +4129,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
-        <v>121</v>
+      <c r="A1" s="84" t="s">
+        <v>123</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -4037,32 +4139,32 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
@@ -4071,26 +4173,28 @@
         <v>38</v>
       </c>
       <c r="D4" s="4">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F4" s="35"/>
     </row>
-    <row r="5" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="114" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="37"/>
+      <c r="E5" s="33" t="s">
+        <v>127</v>
+      </c>
       <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4255,8 +4359,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
-        <v>126</v>
+      <c r="A1" s="84" t="s">
+        <v>129</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -4265,32 +4369,32 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
@@ -4302,15 +4406,15 @@
         <v>46317</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -4320,7 +4424,7 @@
     </row>
     <row r="6" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4330,7 +4434,7 @@
     </row>
     <row r="7" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -4486,8 +4590,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
-        <v>133</v>
+      <c r="A1" s="83" t="s">
+        <v>136</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -4496,42 +4600,44 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
       <c r="E4" s="33"/>
-      <c r="F4" s="35"/>
+      <c r="F4" s="35" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="57" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -4541,7 +4647,7 @@
     </row>
     <row r="6" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="57" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -4551,7 +4657,7 @@
     </row>
     <row r="7" spans="1:6" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="57" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>31</v>
@@ -4563,31 +4669,33 @@
         <v>46315</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="10">
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="F8" s="35"/>
+        <v>144</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -4726,25 +4834,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="84" t="s">
-        <v>142</v>
+      <c r="B2" s="86" t="s">
+        <v>147</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
     </row>
     <row r="4" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="61" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
     </row>
     <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
@@ -4773,15 +4881,15 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="83" t="s">
-        <v>147</v>
+      <c r="B12" s="85" t="s">
+        <v>152</v>
       </c>
       <c r="C12" s="62"/>
       <c r="D12" s="62"/>
@@ -4830,7 +4938,7 @@
     </row>
     <row r="2" spans="1:14" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4873,29 +4981,29 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="69">
+      <c r="A6" s="68">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*"))</f>
-        <v>57</v>
-      </c>
-      <c r="B6" s="67"/>
+        <v>58</v>
+      </c>
+      <c r="B6" s="69"/>
       <c r="C6" s="71">
         <f ca="1">A6-E6-G6</f>
-        <v>32</v>
-      </c>
-      <c r="D6" s="67"/>
+        <v>30</v>
+      </c>
+      <c r="D6" s="69"/>
       <c r="E6" s="70">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"In Progress"))</f>
         <v>6</v>
       </c>
-      <c r="F6" s="67"/>
+      <c r="F6" s="69"/>
       <c r="G6" s="64">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!B4:B1000"),"Completed"))</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H6" s="65"/>
       <c r="I6" s="74">
         <f t="shared" ref="I6" ca="1" si="0">IFERROR(SUM(G6)/SUM(A6), 0)</f>
-        <v>0.33333333333333331</v>
+        <v>0.37931034482758619</v>
       </c>
       <c r="J6" s="75"/>
       <c r="N6" t="s">
@@ -4907,28 +5015,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="76"/>
+      <c r="E8" s="76" t="s">
         <v>34</v>
       </c>
+      <c r="F8" s="76"/>
       <c r="N8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="68">
+    <row r="9" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="87">
+        <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Green"))</f>
+        <v>21</v>
+      </c>
+      <c r="B9" s="67"/>
+      <c r="C9" s="88">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Amber"))</f>
         <v>6</v>
       </c>
-      <c r="B9" s="67"/>
-      <c r="C9" s="66">
+      <c r="D9" s="66"/>
+      <c r="E9" s="89">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'"&amp;Subjects&amp;"'!A4:A1000"),"?*",INDIRECT("'"&amp;Subjects&amp;"'!C4:C1000"),"Red"))</f>
         <v>1</v>
       </c>
-      <c r="D9" s="67"/>
+      <c r="F9" s="77"/>
       <c r="N9" t="s">
         <v>10</v>
       </c>
@@ -4989,7 +5108,7 @@
     </row>
     <row r="14" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Biology'!A4:A1000"),"?*"))</f>
@@ -5025,7 +5144,7 @@
       </c>
       <c r="J14" s="48" t="str">
         <f ca="1">IF(MAX(Biology!D4:D1000)=0, "-", IF(MAX(Biology!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Biology!D4:D1000)=1, "Yesterday", TODAY()-MAX(Biology!D4:D1000) &amp; " days ago")))</f>
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5038,7 +5157,7 @@
       </c>
       <c r="C15" s="25">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!B4:B1000"),"In Progress"))</f>
@@ -5046,11 +5165,11 @@
       </c>
       <c r="E15" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!B4:B1000"),"Completed"))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Green"))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Chemistry'!A4:A1000"),"?*",INDIRECT("'Chemistry'!C4:C1000"),"Amber"))</f>
@@ -5062,11 +5181,11 @@
       </c>
       <c r="I15" s="54">
         <f t="shared" ca="1" si="2"/>
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="J15" s="52" t="str">
         <f ca="1">IF(MAX(Chemistry!D4:D1000)=0, "N/A", IF(MAX(Chemistry!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Chemistry!D4:D1000)=1, "Yesterday", TODAY()-MAX(Chemistry!D4:D1000) &amp; " days ago")))</f>
-        <v>4 days ago</v>
+        <v>Today</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5079,7 +5198,7 @@
       </c>
       <c r="C16" s="23">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!B4:B1000"),"In Progress"))</f>
@@ -5087,11 +5206,11 @@
       </c>
       <c r="E16" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!B4:B1000"),"Completed"))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Green"))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Physics'!A4:A1000"),"?*",INDIRECT("'Physics'!C4:C1000"),"Amber"))</f>
@@ -5103,11 +5222,11 @@
       </c>
       <c r="I16" s="53">
         <f t="shared" ca="1" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="J16" s="48" t="str">
         <f ca="1">IF(MAX(Physics!D4:D1000)=0, "-", IF(MAX(Physics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Physics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Physics!D4:D1000) &amp; " days ago")))</f>
-        <v>6 days ago</v>
+        <v>Yesterday</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5148,7 +5267,7 @@
       </c>
       <c r="J17" s="52" t="str">
         <f ca="1">IF(MAX(Mathematics!D4:D1000)=0, "-", IF(MAX(Mathematics!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Mathematics!D4:D1000)=1, "Yesterday", TODAY()-MAX(Mathematics!D4:D1000) &amp; " days ago")))</f>
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5157,7 +5276,7 @@
       </c>
       <c r="B18" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*"))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" s="23">
         <f t="shared" ca="1" si="1"/>
@@ -5165,7 +5284,7 @@
       </c>
       <c r="D18" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!B4:B1000"),"In Progress"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!B4:B1000"),"Completed"))</f>
@@ -5173,7 +5292,7 @@
       </c>
       <c r="F18" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Green"))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="23">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'English Language'!A4:A1000"),"?*",INDIRECT("'English Language'!C4:C1000"),"Amber"))</f>
@@ -5185,11 +5304,11 @@
       </c>
       <c r="I18" s="53">
         <f t="shared" ca="1" si="2"/>
-        <v>0.55555555555555558</v>
+        <v>0.5</v>
       </c>
       <c r="J18" s="48" t="str">
         <f ca="1">IF(MAX('English Language'!D4:D1000)=0, "-", IF(MAX('English Language'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Language'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Language'!D4:D1000) &amp; " days ago")))</f>
-        <v>5 days ago</v>
+        <v>Today</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5230,7 +5349,7 @@
       </c>
       <c r="J19" s="52" t="str">
         <f ca="1">IF(MAX('English Literature'!D4:D1000)=0, "-", IF(MAX('English Literature'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('English Literature'!D4:D1000)=1, "Yesterday", TODAY()-MAX('English Literature'!D4:D1000) &amp; " days ago")))</f>
-        <v>Yesterday</v>
+        <v>2 days ago</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5271,7 +5390,7 @@
       </c>
       <c r="J20" s="48" t="str">
         <f ca="1">IF(MAX(Geography!D4:D1000)=0, "-", IF(MAX(Geography!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Geography!D4:D1000)=1, "Yesterday", TODAY()-MAX(Geography!D4:D1000) &amp; " days ago")))</f>
-        <v>Today</v>
+        <v>Yesterday</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5312,7 +5431,7 @@
       </c>
       <c r="J21" s="52" t="str">
         <f ca="1">IF(MAX(History!D4:D1000)=0, "-", IF(MAX(History!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(History!D4:D1000)=1, "Yesterday", TODAY()-MAX(History!D4:D1000) &amp; " days ago")))</f>
-        <v>5 days ago</v>
+        <v>Yesterday</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5353,7 +5472,7 @@
       </c>
       <c r="J22" s="48" t="str">
         <f ca="1">IF(MAX(Spanish!D4:D1000)=0, "-", IF(MAX(Spanish!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX(Spanish!D4:D1000)=1, "Yesterday", TODAY()-MAX(Spanish!D4:D1000) &amp; " days ago")))</f>
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5370,11 +5489,11 @@
       </c>
       <c r="D23" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!B4:B1000"),"In Progress"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!B4:B1000"),"Completed"))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="25">
         <f ca="1">SUMPRODUCT(COUNTIFS(INDIRECT("'Computer Science'!A4:A1000"),"?*",INDIRECT("'Computer Science'!C4:C1000"),"Green"))</f>
@@ -5390,66 +5509,66 @@
       </c>
       <c r="I23" s="50">
         <f t="shared" ca="1" si="2"/>
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J23" s="52" t="str">
         <f ca="1">IF(MAX('Computer Science'!D4:D1000)=0, "-", IF(MAX('Computer Science'!D4:D1000)=TODAY(), "Today", IF(TODAY()-MAX('Computer Science'!D4:D1000)=1, "Yesterday", TODAY()-MAX('Computer Science'!D4:D1000) &amp; " days ago")))</f>
-        <v>4 days ago</v>
+        <v>Yesterday</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="60">
+      <c r="A24" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="59">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="76" t="s">
+      <c r="A26" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="76"/>
-      <c r="C26" s="76" t="s">
+      <c r="B26" s="78"/>
+      <c r="C26" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76" t="s">
+      <c r="D26" s="78"/>
+      <c r="E26" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76" t="s">
+      <c r="F26" s="78"/>
+      <c r="G26" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="H26" s="76"/>
+      <c r="H26" s="78"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="77" t="str">
+      <c r="A27" s="79" t="str">
         <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 1)), "-")</f>
+        <v>Mathematics</v>
+      </c>
+      <c r="B27" s="81"/>
+      <c r="C27" s="79" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)), "-")</f>
+        <v>Chemistry</v>
+      </c>
+      <c r="D27" s="81"/>
+      <c r="E27" s="79" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)), "-")</f>
+        <v>English Language</v>
+      </c>
+      <c r="F27" s="81"/>
+      <c r="G27" s="79" t="str">
+        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)), "-")</f>
         <v>Biology</v>
       </c>
-      <c r="B27" s="79"/>
-      <c r="C27" s="77" t="str">
-        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 2)), "-")</f>
-        <v>English Language</v>
-      </c>
-      <c r="D27" s="79"/>
-      <c r="E27" s="77" t="str">
-        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 3)), "-")</f>
-        <v>Chemistry</v>
-      </c>
-      <c r="F27" s="79"/>
-      <c r="G27" s="77" t="str">
-        <f ca="1">IFERROR(HYPERLINK("#'"&amp;INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)&amp;"'!A4", INDEX(IF($B$24=1, 'Revision Timetable'!B2:E8, 'Revision Timetable'!H2:K8), MATCH(TEXT(TODAY(),"dddd"), 'Revision Timetable'!A2:A8, 0), 4)), "-")</f>
-        <v>Spanish</v>
-      </c>
-      <c r="H27" s="78"/>
+      <c r="H27" s="80"/>
       <c r="AA27" s="42" t="b">
         <f ca="1">IFERROR(VLOOKUP(A27, $A$13:$J$23, 9, FALSE)="Today", FALSE)</f>
         <v>0</v>
@@ -5474,11 +5593,11 @@
       </c>
       <c r="C28" s="43" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, C27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
-        <v>NOT DONE</v>
+        <v>DONE</v>
       </c>
       <c r="E28" s="43" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, E27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
-        <v>NOT DONE</v>
+        <v>DONE</v>
       </c>
       <c r="G28" s="43" t="str">
         <f ca="1">IF(COUNTIFS($A$13:$A$23, G27, $J$13:$J$23, "Today")&gt;0, "DONE", "NOT DONE")</f>
@@ -5486,7 +5605,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="23">
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="A26:B26"/>
@@ -5506,6 +5625,10 @@
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="I6:J6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
   </mergeCells>
   <conditionalFormatting sqref="A27:H27">
     <cfRule type="cellIs" dxfId="125" priority="72" stopIfTrue="1" operator="equal">
@@ -5751,8 +5874,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
-        <v>42</v>
+      <c r="A1" s="82" t="s">
+        <v>43</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -5761,7 +5884,7 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5770,27 +5893,27 @@
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>31</v>
@@ -5802,15 +5925,15 @@
         <v>46313</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>31</v>
@@ -5822,13 +5945,13 @@
         <v>46316</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>31</v>
@@ -5840,13 +5963,13 @@
         <v>46317</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>31</v>
@@ -5858,13 +5981,13 @@
         <v>46319</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -5874,7 +5997,7 @@
     </row>
     <row r="9" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -5884,7 +6007,7 @@
     </row>
     <row r="10" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>31</v>
@@ -5896,13 +6019,13 @@
         <v>46319</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -6098,8 +6221,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
-        <v>63</v>
+      <c r="A1" s="83" t="s">
+        <v>64</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -6108,60 +6231,60 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="56" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="10">
         <v>46315</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>65</v>
+      <c r="E4" s="33" t="s">
+        <v>66</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="10">
         <v>46318</v>
       </c>
       <c r="E5" s="33" t="s">
@@ -6173,16 +6296,16 @@
       <c r="A6" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="10">
         <v>46318</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="33" t="s">
         <v>70</v>
       </c>
       <c r="F6" s="35"/>
@@ -6191,106 +6314,114 @@
       <c r="A7" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="37"/>
+      <c r="B7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10">
+        <v>46323</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>72</v>
+      </c>
       <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="37"/>
+        <v>73</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="37"/>
+        <v>74</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="33"/>
       <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="57" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="37"/>
+        <v>75</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="37"/>
+      <c r="A11" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="33"/>
       <c r="F11" s="35"/>
     </row>
     <row r="12" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="37"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="33"/>
       <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="37"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="33"/>
       <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="37"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="35"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="37"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="33"/>
       <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="37"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="37"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="33"/>
       <c r="F17" s="35"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="37"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="35"/>
     </row>
   </sheetData>
@@ -6353,8 +6484,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
-        <v>76</v>
+      <c r="A1" s="83" t="s">
+        <v>77</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -6363,32 +6494,32 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>31</v>
@@ -6400,15 +6531,15 @@
         <v>46314</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>31</v>
@@ -6420,13 +6551,13 @@
         <v>46316</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>31</v>
@@ -6438,23 +6569,31 @@
         <v>46316</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="33"/>
+        <v>84</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="10">
+        <v>46322</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>85</v>
+      </c>
       <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="56" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -6464,7 +6603,7 @@
     </row>
     <row r="9" spans="1:6" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -6474,7 +6613,7 @@
     </row>
     <row r="10" spans="1:6" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="56" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -6607,8 +6746,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
-        <v>87</v>
+      <c r="A1" s="83" t="s">
+        <v>89</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -6617,32 +6756,32 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>30</v>
@@ -6654,7 +6793,7 @@
         <v>46319</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F4" s="35"/>
     </row>
@@ -6831,8 +6970,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
-        <v>90</v>
+      <c r="A1" s="84" t="s">
+        <v>92</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -6841,32 +6980,32 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>31</v>
@@ -6877,14 +7016,12 @@
       <c r="D4" s="10">
         <v>46315</v>
       </c>
-      <c r="E4" s="33" t="s">
-        <v>92</v>
-      </c>
+      <c r="E4" s="33"/>
       <c r="F4" s="35"/>
     </row>
     <row r="5" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>31</v>
@@ -6897,12 +7034,12 @@
       </c>
       <c r="E5" s="33"/>
       <c r="F5" s="35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>31</v>
@@ -6913,9 +7050,7 @@
       <c r="D6" s="10">
         <v>46311</v>
       </c>
-      <c r="E6" s="33" t="s">
-        <v>96</v>
-      </c>
+      <c r="E6" s="33"/>
       <c r="F6" s="35"/>
     </row>
     <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6991,11 +7126,21 @@
       <c r="F12" s="35"/>
     </row>
     <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="33"/>
+      <c r="A13" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="10">
+        <v>46323</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>104</v>
+      </c>
       <c r="F13" s="35"/>
     </row>
     <row r="14" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7099,8 +7244,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
-        <v>103</v>
+      <c r="A1" s="83" t="s">
+        <v>105</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -7109,32 +7254,32 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>30</v>
@@ -7146,13 +7291,13 @@
         <v>46321</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F4" s="35"/>
     </row>
     <row r="5" spans="1:6" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>31</v>
@@ -7164,13 +7309,13 @@
         <v>46321</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -7180,7 +7325,7 @@
     </row>
     <row r="7" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -7190,7 +7335,7 @@
     </row>
     <row r="8" spans="1:6" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -7200,7 +7345,7 @@
     </row>
     <row r="9" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -7340,8 +7485,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
-        <v>112</v>
+      <c r="A1" s="83" t="s">
+        <v>114</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -7350,32 +7495,32 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>30</v>
@@ -7387,15 +7532,15 @@
         <v>46322</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -7405,7 +7550,7 @@
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -7415,7 +7560,7 @@
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -7425,7 +7570,7 @@
     </row>
     <row r="8" spans="1:6" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>31</v>
@@ -7437,7 +7582,7 @@
         <v>46315</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F8" s="35"/>
     </row>
@@ -7854,14 +7999,14 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783C6A1E-EF8C-4F8F-AF56-34A608ED7025}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="ed8dfb7b-01af-4433-b4cc-631574050608"/>
     <ds:schemaRef ds:uri="0fb2ba46-83e9-4d91-a985-8245aaf43e5c"/>
   </ds:schemaRefs>
